--- a/docs/amharic-review.xlsx
+++ b/docs/amharic-review.xlsx
@@ -6796,10 +6796,10 @@
     <t>sms.sendThis</t>
   </si>
   <si>
-    <t>Send this message</t>
-  </si>
-  <si>
-    <t>ይህን መልዕክት ላክ</t>
+    <t>Send this message automatically</t>
+  </si>
+  <si>
+    <t>ይህን መልዕክት በራስ-ሰር ላክ</t>
   </si>
   <si>
     <t>sms.sendTo</t>

--- a/docs/amharic-review.xlsx
+++ b/docs/amharic-review.xlsx
@@ -6214,6 +6214,15 @@
     <t>0 ገደብ የለም ማለት ነው። ማስታወቂያዎችና ሙከራዎች አይቆጠሩም።</t>
   </si>
   <si>
+    <t>sms.daysBefore</t>
+  </si>
+  <si>
+    <t>days before</t>
+  </si>
+  <si>
+    <t>ቀን በፊት</t>
+  </si>
+  <si>
     <t>sms.daysLate</t>
   </si>
   <si>
@@ -6526,6 +6535,15 @@
     <t>ያለፉ ደረሰኞችን ከዚህ በኋላ አስታውስ</t>
   </si>
   <si>
+    <t>sms.perDay</t>
+  </si>
+  <si>
+    <t>per day</t>
+  </si>
+  <si>
+    <t>በቀን</t>
+  </si>
+  <si>
     <t>sms.ph.amount</t>
   </si>
   <si>
@@ -6719,6 +6737,33 @@
   </si>
   <si>
     <t>ያልተሳኩትን ሁሉ እንደገና ሞክር</t>
+  </si>
+  <si>
+    <t>sms.ruleBeforeTitle</t>
+  </si>
+  <si>
+    <t>Reminder before the due date</t>
+  </si>
+  <si>
+    <t>ከመክፈያ ቀን በፊት ማስታወሻ</t>
+  </si>
+  <si>
+    <t>sms.ruleExtrasTitle</t>
+  </si>
+  <si>
+    <t>Other messages</t>
+  </si>
+  <si>
+    <t>ሌሎች መልዕክቶች</t>
+  </si>
+  <si>
+    <t>sms.ruleQuietTitle</t>
+  </si>
+  <si>
+    <t>Quiet hours</t>
+  </si>
+  <si>
+    <t>የዝምታ ሰዓት</t>
   </si>
   <si>
     <t>sms.rulesApprover</t>
@@ -17878,10 +17923,10 @@
         <v>2126</v>
       </c>
       <c r="C743" t="s">
-        <v>925</v>
+        <v>2127</v>
       </c>
       <c r="D743" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="744">
@@ -17889,10 +17934,10 @@
         <v>1594</v>
       </c>
       <c r="B744" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="C744" t="s">
-        <v>2129</v>
+        <v>925</v>
       </c>
       <c r="D744" t="s">
         <v>2130</v>
@@ -18130,10 +18175,10 @@
         <v>2179</v>
       </c>
       <c r="C761" t="s">
-        <v>306</v>
+        <v>2180</v>
       </c>
       <c r="D761" t="s">
-        <v>307</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="762">
@@ -18141,13 +18186,13 @@
         <v>1594</v>
       </c>
       <c r="B762" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="C762" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="D762" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="763">
@@ -18155,13 +18200,13 @@
         <v>1594</v>
       </c>
       <c r="B763" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="C763" t="s">
-        <v>2184</v>
+        <v>306</v>
       </c>
       <c r="D763" t="s">
-        <v>2185</v>
+        <v>307</v>
       </c>
     </row>
     <row r="764">
@@ -18200,10 +18245,10 @@
         <v>2192</v>
       </c>
       <c r="C766" t="s">
-        <v>503</v>
+        <v>2193</v>
       </c>
       <c r="D766" t="s">
-        <v>504</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="767">
@@ -18211,13 +18256,13 @@
         <v>1594</v>
       </c>
       <c r="B767" t="s">
-        <v>2193</v>
+        <v>2195</v>
       </c>
       <c r="C767" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="D767" t="s">
-        <v>2195</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="768">
@@ -18225,13 +18270,13 @@
         <v>1594</v>
       </c>
       <c r="B768" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="C768" t="s">
-        <v>2197</v>
+        <v>503</v>
       </c>
       <c r="D768" t="s">
-        <v>2198</v>
+        <v>504</v>
       </c>
     </row>
     <row r="769">
@@ -18242,10 +18287,10 @@
         <v>2199</v>
       </c>
       <c r="C769" t="s">
-        <v>744</v>
+        <v>2200</v>
       </c>
       <c r="D769" t="s">
-        <v>745</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="770">
@@ -18253,13 +18298,13 @@
         <v>1594</v>
       </c>
       <c r="B770" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="C770" t="s">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="D770" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="771">
@@ -18267,13 +18312,13 @@
         <v>1594</v>
       </c>
       <c r="B771" t="s">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="C771" t="s">
-        <v>2204</v>
+        <v>744</v>
       </c>
       <c r="D771" t="s">
-        <v>2205</v>
+        <v>745</v>
       </c>
     </row>
     <row r="772">
@@ -18399,7 +18444,7 @@
         <v>2231</v>
       </c>
       <c r="D780" t="s">
-        <v>733</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="781">
@@ -18407,13 +18452,13 @@
         <v>1594</v>
       </c>
       <c r="B781" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="C781" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="D781" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="782">
@@ -18421,13 +18466,13 @@
         <v>1594</v>
       </c>
       <c r="B782" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="C782" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
       <c r="D782" t="s">
-        <v>2237</v>
+        <v>733</v>
       </c>
     </row>
     <row r="783">
@@ -18483,7 +18528,7 @@
         <v>2248</v>
       </c>
       <c r="D786" t="s">
-        <v>142</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="787">
@@ -18491,13 +18536,13 @@
         <v>1594</v>
       </c>
       <c r="B787" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="C787" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="D787" t="s">
-        <v>1557</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="788">
@@ -18505,13 +18550,13 @@
         <v>1594</v>
       </c>
       <c r="B788" t="s">
-        <v>2251</v>
+        <v>2253</v>
       </c>
       <c r="C788" t="s">
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="D788" t="s">
-        <v>1557</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="789">
@@ -18519,13 +18564,13 @@
         <v>1594</v>
       </c>
       <c r="B789" t="s">
-        <v>2253</v>
+        <v>2256</v>
       </c>
       <c r="C789" t="s">
-        <v>2254</v>
+        <v>2257</v>
       </c>
       <c r="D789" t="s">
-        <v>2255</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="790">
@@ -18533,13 +18578,13 @@
         <v>1594</v>
       </c>
       <c r="B790" t="s">
-        <v>2256</v>
+        <v>2259</v>
       </c>
       <c r="C790" t="s">
-        <v>2257</v>
+        <v>2260</v>
       </c>
       <c r="D790" t="s">
-        <v>2258</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="791">
@@ -18547,13 +18592,13 @@
         <v>1594</v>
       </c>
       <c r="B791" t="s">
-        <v>2259</v>
+        <v>2262</v>
       </c>
       <c r="C791" t="s">
-        <v>2260</v>
+        <v>2263</v>
       </c>
       <c r="D791" t="s">
-        <v>2261</v>
+        <v>142</v>
       </c>
     </row>
     <row r="792">
@@ -18561,13 +18606,13 @@
         <v>1594</v>
       </c>
       <c r="B792" t="s">
-        <v>2262</v>
+        <v>2264</v>
       </c>
       <c r="C792" t="s">
-        <v>2263</v>
+        <v>2265</v>
       </c>
       <c r="D792" t="s">
-        <v>2264</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="793">
@@ -18575,13 +18620,13 @@
         <v>1594</v>
       </c>
       <c r="B793" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="C793" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="D793" t="s">
-        <v>2267</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="794">
@@ -18732,10 +18777,10 @@
         <v>2298</v>
       </c>
       <c r="C804" t="s">
-        <v>2106</v>
+        <v>2299</v>
       </c>
       <c r="D804" t="s">
-        <v>2107</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="805">
@@ -18743,13 +18788,13 @@
         <v>1594</v>
       </c>
       <c r="B805" t="s">
-        <v>2299</v>
+        <v>2301</v>
       </c>
       <c r="C805" t="s">
-        <v>2300</v>
+        <v>2302</v>
       </c>
       <c r="D805" t="s">
-        <v>2301</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="806">
@@ -18757,13 +18802,13 @@
         <v>1594</v>
       </c>
       <c r="B806" t="s">
-        <v>2302</v>
+        <v>2304</v>
       </c>
       <c r="C806" t="s">
-        <v>2115</v>
+        <v>2305</v>
       </c>
       <c r="D806" t="s">
-        <v>2116</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="807">
@@ -18771,13 +18816,13 @@
         <v>1594</v>
       </c>
       <c r="B807" t="s">
-        <v>2303</v>
+        <v>2307</v>
       </c>
       <c r="C807" t="s">
-        <v>2304</v>
+        <v>2308</v>
       </c>
       <c r="D807" t="s">
-        <v>2305</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="808">
@@ -18785,13 +18830,13 @@
         <v>1594</v>
       </c>
       <c r="B808" t="s">
-        <v>2306</v>
+        <v>2310</v>
       </c>
       <c r="C808" t="s">
-        <v>2118</v>
+        <v>2311</v>
       </c>
       <c r="D808" t="s">
-        <v>2119</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="809">
@@ -18799,13 +18844,13 @@
         <v>1594</v>
       </c>
       <c r="B809" t="s">
-        <v>2307</v>
+        <v>2313</v>
       </c>
       <c r="C809" t="s">
-        <v>2308</v>
+        <v>2109</v>
       </c>
       <c r="D809" t="s">
-        <v>2309</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="810">
@@ -18813,13 +18858,13 @@
         <v>1594</v>
       </c>
       <c r="B810" t="s">
-        <v>2310</v>
+        <v>2314</v>
       </c>
       <c r="C810" t="s">
-        <v>2311</v>
+        <v>2315</v>
       </c>
       <c r="D810" t="s">
-        <v>2312</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="811">
@@ -18827,13 +18872,13 @@
         <v>1594</v>
       </c>
       <c r="B811" t="s">
-        <v>2313</v>
+        <v>2317</v>
       </c>
       <c r="C811" t="s">
-        <v>2314</v>
+        <v>2118</v>
       </c>
       <c r="D811" t="s">
-        <v>2315</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="812">
@@ -18841,13 +18886,13 @@
         <v>1594</v>
       </c>
       <c r="B812" t="s">
-        <v>2316</v>
+        <v>2318</v>
       </c>
       <c r="C812" t="s">
-        <v>2317</v>
+        <v>2319</v>
       </c>
       <c r="D812" t="s">
-        <v>2318</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="813">
@@ -18855,13 +18900,13 @@
         <v>1594</v>
       </c>
       <c r="B813" t="s">
-        <v>2319</v>
+        <v>2321</v>
       </c>
       <c r="C813" t="s">
-        <v>2320</v>
+        <v>2121</v>
       </c>
       <c r="D813" t="s">
-        <v>2321</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="814">
@@ -18886,10 +18931,10 @@
         <v>2325</v>
       </c>
       <c r="C815" t="s">
-        <v>1904</v>
+        <v>2326</v>
       </c>
       <c r="D815" t="s">
-        <v>444</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="816">
@@ -18897,13 +18942,13 @@
         <v>1594</v>
       </c>
       <c r="B816" t="s">
-        <v>2326</v>
+        <v>2328</v>
       </c>
       <c r="C816" t="s">
-        <v>2327</v>
+        <v>2329</v>
       </c>
       <c r="D816" t="s">
-        <v>2328</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="817">
@@ -18911,13 +18956,13 @@
         <v>1594</v>
       </c>
       <c r="B817" t="s">
-        <v>2329</v>
+        <v>2331</v>
       </c>
       <c r="C817" t="s">
-        <v>2330</v>
+        <v>2332</v>
       </c>
       <c r="D817" t="s">
-        <v>2331</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="818">
@@ -18925,102 +18970,102 @@
         <v>1594</v>
       </c>
       <c r="B818" t="s">
-        <v>2332</v>
+        <v>2334</v>
       </c>
       <c r="C818" t="s">
-        <v>2333</v>
+        <v>2335</v>
       </c>
       <c r="D818" t="s">
-        <v>2334</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="s">
-        <v>1609</v>
+        <v>1594</v>
       </c>
       <c r="B819" t="s">
-        <v>2335</v>
+        <v>2337</v>
       </c>
       <c r="C819" t="s">
-        <v>832</v>
+        <v>2338</v>
       </c>
       <c r="D819" t="s">
-        <v>833</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="s">
-        <v>1609</v>
+        <v>1594</v>
       </c>
       <c r="B820" t="s">
-        <v>2336</v>
+        <v>2340</v>
       </c>
       <c r="C820" t="s">
-        <v>2337</v>
+        <v>1904</v>
       </c>
       <c r="D820" t="s">
-        <v>2338</v>
+        <v>444</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="s">
-        <v>1609</v>
+        <v>1594</v>
       </c>
       <c r="B821" t="s">
-        <v>2339</v>
+        <v>2341</v>
       </c>
       <c r="C821" t="s">
-        <v>2340</v>
+        <v>2342</v>
       </c>
       <c r="D821" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="s">
-        <v>2342</v>
+        <v>1594</v>
       </c>
       <c r="B822" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="C822" t="s">
-        <v>2342</v>
+        <v>2345</v>
       </c>
       <c r="D822" t="s">
-        <v>2344</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="s">
-        <v>2342</v>
+        <v>1594</v>
       </c>
       <c r="B823" t="s">
-        <v>2345</v>
+        <v>2347</v>
       </c>
       <c r="C823" t="s">
-        <v>2346</v>
+        <v>2348</v>
       </c>
       <c r="D823" t="s">
-        <v>2347</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="s">
-        <v>2342</v>
+        <v>1609</v>
       </c>
       <c r="B824" t="s">
-        <v>2348</v>
+        <v>2350</v>
       </c>
       <c r="C824" t="s">
-        <v>2349</v>
+        <v>832</v>
       </c>
       <c r="D824" t="s">
-        <v>2350</v>
+        <v>833</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="s">
-        <v>2342</v>
+        <v>1609</v>
       </c>
       <c r="B825" t="s">
         <v>2351</v>
@@ -19034,7 +19079,7 @@
     </row>
     <row r="826">
       <c r="A826" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="B826" t="s">
         <v>2354</v>
@@ -19048,13 +19093,13 @@
     </row>
     <row r="827">
       <c r="A827" t="s">
-        <v>1612</v>
+        <v>2357</v>
       </c>
       <c r="B827" t="s">
+        <v>2358</v>
+      </c>
+      <c r="C827" t="s">
         <v>2357</v>
-      </c>
-      <c r="C827" t="s">
-        <v>2358</v>
       </c>
       <c r="D827" t="s">
         <v>2359</v>
@@ -19062,7 +19107,7 @@
     </row>
     <row r="828">
       <c r="A828" t="s">
-        <v>1612</v>
+        <v>2357</v>
       </c>
       <c r="B828" t="s">
         <v>2360</v>
@@ -19076,30 +19121,30 @@
     </row>
     <row r="829">
       <c r="A829" t="s">
-        <v>1612</v>
+        <v>2357</v>
       </c>
       <c r="B829" t="s">
         <v>2363</v>
       </c>
       <c r="C829" t="s">
-        <v>280</v>
+        <v>2364</v>
       </c>
       <c r="D829" t="s">
-        <v>281</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="s">
-        <v>1612</v>
+        <v>2357</v>
       </c>
       <c r="B830" t="s">
-        <v>2364</v>
+        <v>2366</v>
       </c>
       <c r="C830" t="s">
-        <v>2365</v>
+        <v>2367</v>
       </c>
       <c r="D830" t="s">
-        <v>1764</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="831">
@@ -19107,13 +19152,13 @@
         <v>1612</v>
       </c>
       <c r="B831" t="s">
-        <v>2366</v>
+        <v>2369</v>
       </c>
       <c r="C831" t="s">
-        <v>2367</v>
+        <v>2370</v>
       </c>
       <c r="D831" t="s">
-        <v>2368</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="832">
@@ -19121,13 +19166,13 @@
         <v>1612</v>
       </c>
       <c r="B832" t="s">
-        <v>2369</v>
+        <v>2372</v>
       </c>
       <c r="C832" t="s">
-        <v>2370</v>
+        <v>2373</v>
       </c>
       <c r="D832" t="s">
-        <v>2371</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="833">
@@ -19135,13 +19180,13 @@
         <v>1612</v>
       </c>
       <c r="B833" t="s">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="C833" t="s">
-        <v>2373</v>
+        <v>2376</v>
       </c>
       <c r="D833" t="s">
-        <v>2374</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="834">
@@ -19149,13 +19194,13 @@
         <v>1612</v>
       </c>
       <c r="B834" t="s">
-        <v>2375</v>
+        <v>2378</v>
       </c>
       <c r="C834" t="s">
-        <v>2376</v>
+        <v>280</v>
       </c>
       <c r="D834" t="s">
-        <v>2377</v>
+        <v>281</v>
       </c>
     </row>
     <row r="835">
@@ -19163,13 +19208,13 @@
         <v>1612</v>
       </c>
       <c r="B835" t="s">
-        <v>2378</v>
+        <v>2379</v>
       </c>
       <c r="C835" t="s">
-        <v>2379</v>
+        <v>2380</v>
       </c>
       <c r="D835" t="s">
-        <v>2380</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="836">
@@ -19278,10 +19323,10 @@
         <v>2402</v>
       </c>
       <c r="C843" t="s">
-        <v>2376</v>
+        <v>2403</v>
       </c>
       <c r="D843" t="s">
-        <v>2377</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="844">
@@ -19289,13 +19334,13 @@
         <v>1612</v>
       </c>
       <c r="B844" t="s">
-        <v>2403</v>
+        <v>2405</v>
       </c>
       <c r="C844" t="s">
-        <v>2404</v>
+        <v>2406</v>
       </c>
       <c r="D844" t="s">
-        <v>2405</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="845">
@@ -19303,13 +19348,13 @@
         <v>1612</v>
       </c>
       <c r="B845" t="s">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="C845" t="s">
-        <v>2407</v>
+        <v>2409</v>
       </c>
       <c r="D845" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="846">
@@ -19317,13 +19362,13 @@
         <v>1612</v>
       </c>
       <c r="B846" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
       <c r="C846" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
       <c r="D846" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="847">
@@ -19331,13 +19376,13 @@
         <v>1612</v>
       </c>
       <c r="B847" t="s">
-        <v>2412</v>
+        <v>2414</v>
       </c>
       <c r="C847" t="s">
-        <v>2413</v>
+        <v>2415</v>
       </c>
       <c r="D847" t="s">
-        <v>2414</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="848">
@@ -19345,13 +19390,13 @@
         <v>1612</v>
       </c>
       <c r="B848" t="s">
-        <v>2415</v>
+        <v>2417</v>
       </c>
       <c r="C848" t="s">
-        <v>2416</v>
+        <v>2391</v>
       </c>
       <c r="D848" t="s">
-        <v>2417</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="849">
@@ -19404,10 +19449,10 @@
         <v>2427</v>
       </c>
       <c r="C852" t="s">
-        <v>2367</v>
+        <v>2428</v>
       </c>
       <c r="D852" t="s">
-        <v>2368</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="853">
@@ -19415,13 +19460,13 @@
         <v>1612</v>
       </c>
       <c r="B853" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
       <c r="C853" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="D853" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="854">
@@ -19429,13 +19474,13 @@
         <v>1612</v>
       </c>
       <c r="B854" t="s">
-        <v>2431</v>
+        <v>2433</v>
       </c>
       <c r="C854" t="s">
-        <v>2432</v>
+        <v>2434</v>
       </c>
       <c r="D854" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="855">
@@ -19443,13 +19488,13 @@
         <v>1612</v>
       </c>
       <c r="B855" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
       <c r="C855" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="D855" t="s">
-        <v>2436</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="856">
@@ -19457,13 +19502,13 @@
         <v>1612</v>
       </c>
       <c r="B856" t="s">
-        <v>2437</v>
+        <v>2439</v>
       </c>
       <c r="C856" t="s">
-        <v>2438</v>
+        <v>2440</v>
       </c>
       <c r="D856" t="s">
-        <v>2439</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="857">
@@ -19471,13 +19516,13 @@
         <v>1612</v>
       </c>
       <c r="B857" t="s">
-        <v>2440</v>
+        <v>2442</v>
       </c>
       <c r="C857" t="s">
-        <v>2441</v>
+        <v>2382</v>
       </c>
       <c r="D857" t="s">
-        <v>2442</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="858">
@@ -19544,10 +19589,10 @@
         <v>2455</v>
       </c>
       <c r="C862" t="s">
-        <v>1240</v>
+        <v>2456</v>
       </c>
       <c r="D862" t="s">
-        <v>1241</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="863">
@@ -19555,13 +19600,13 @@
         <v>1612</v>
       </c>
       <c r="B863" t="s">
-        <v>2456</v>
+        <v>2458</v>
       </c>
       <c r="C863" t="s">
-        <v>2457</v>
+        <v>2459</v>
       </c>
       <c r="D863" t="s">
-        <v>2458</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="864">
@@ -19569,13 +19614,13 @@
         <v>1612</v>
       </c>
       <c r="B864" t="s">
-        <v>2459</v>
+        <v>2461</v>
       </c>
       <c r="C864" t="s">
-        <v>2460</v>
+        <v>2462</v>
       </c>
       <c r="D864" t="s">
-        <v>2461</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="865">
@@ -19583,13 +19628,13 @@
         <v>1612</v>
       </c>
       <c r="B865" t="s">
-        <v>2462</v>
+        <v>2464</v>
       </c>
       <c r="C865" t="s">
-        <v>2463</v>
+        <v>2465</v>
       </c>
       <c r="D865" t="s">
-        <v>2464</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="866">
@@ -19597,13 +19642,83 @@
         <v>1612</v>
       </c>
       <c r="B866" t="s">
-        <v>2465</v>
+        <v>2467</v>
       </c>
       <c r="C866" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="D866" t="s">
-        <v>2467</v>
+        <v>2469</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B867" t="s">
+        <v>2470</v>
+      </c>
+      <c r="C867" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D867" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B868" t="s">
+        <v>2471</v>
+      </c>
+      <c r="C868" t="s">
+        <v>2472</v>
+      </c>
+      <c r="D868" t="s">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B869" t="s">
+        <v>2474</v>
+      </c>
+      <c r="C869" t="s">
+        <v>2475</v>
+      </c>
+      <c r="D869" t="s">
+        <v>2476</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B870" t="s">
+        <v>2477</v>
+      </c>
+      <c r="C870" t="s">
+        <v>2478</v>
+      </c>
+      <c r="D870" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B871" t="s">
+        <v>2480</v>
+      </c>
+      <c r="C871" t="s">
+        <v>2481</v>
+      </c>
+      <c r="D871" t="s">
+        <v>2482</v>
       </c>
     </row>
   </sheetData>

--- a/docs/amharic-review.xlsx
+++ b/docs/amharic-review.xlsx
@@ -5830,6 +5830,132 @@
     <t>የውዝፍ ዕዳ ዕድሜ</t>
   </si>
   <si>
+    <t>rep.c.ageing</t>
+  </si>
+  <si>
+    <t>Where the arrears sit</t>
+  </si>
+  <si>
+    <t>ውዝፍ የት እንዳለ</t>
+  </si>
+  <si>
+    <t>rep.c.balanceOverTime</t>
+  </si>
+  <si>
+    <t>Balance over time</t>
+  </si>
+  <si>
+    <t>ቀሪ ሂሳብ በጊዜ ሂደት</t>
+  </si>
+  <si>
+    <t>rep.c.biggestDeposits</t>
+  </si>
+  <si>
+    <t>Largest deposits held</t>
+  </si>
+  <si>
+    <t>ትልቁ ተይዞ ያለ ዋስትና</t>
+  </si>
+  <si>
+    <t>rep.c.biggestRent</t>
+  </si>
+  <si>
+    <t>Rent by lease</t>
+  </si>
+  <si>
+    <t>ኪራይ በውል</t>
+  </si>
+  <si>
+    <t>rep.c.depositMix</t>
+  </si>
+  <si>
+    <t>Where the deposits stand</t>
+  </si>
+  <si>
+    <t>የዋስትና ሁኔታ</t>
+  </si>
+  <si>
+    <t>rep.c.endingByMonth</t>
+  </si>
+  <si>
+    <t>Rent of leases ending, by month</t>
+  </si>
+  <si>
+    <t>የሚያበቁ ውሎች ኪራይ በወር</t>
+  </si>
+  <si>
+    <t>rep.c.occupancy</t>
+  </si>
+  <si>
+    <t>የክፍል አጠቃቀም</t>
+  </si>
+  <si>
+    <t>rep.c.rate</t>
+  </si>
+  <si>
+    <t>Collection rate by month</t>
+  </si>
+  <si>
+    <t>የስብሰባ መጠን በወር</t>
+  </si>
+  <si>
+    <t>rep.c.rentByBuilding</t>
+  </si>
+  <si>
+    <t>Rent by building</t>
+  </si>
+  <si>
+    <t>ኪራይ በሕንፃ</t>
+  </si>
+  <si>
+    <t>rep.c.rentByCategory</t>
+  </si>
+  <si>
+    <t>Rent by category</t>
+  </si>
+  <si>
+    <t>ኪራይ በምድብ</t>
+  </si>
+  <si>
+    <t>rep.c.topDebtors</t>
+  </si>
+  <si>
+    <t>Largest balances</t>
+  </si>
+  <si>
+    <t>ትልቁ ቀሪ ሂሳብ</t>
+  </si>
+  <si>
+    <t>rep.c.trend</t>
+  </si>
+  <si>
+    <t>Billed and collected</t>
+  </si>
+  <si>
+    <t>የወጣና የተሰበሰበ</t>
+  </si>
+  <si>
+    <t>rep.c.vacantArea</t>
+  </si>
+  <si>
+    <t>Vacant area by category</t>
+  </si>
+  <si>
+    <t>ክፍት ስፋት በምድብ</t>
+  </si>
+  <si>
+    <t>rep.c.vacantByCategory</t>
+  </si>
+  <si>
+    <t>Rent waiting to be let, by category</t>
+  </si>
+  <si>
+    <t>ለመከራየት የሚጠብቅ ኪራይ በምድብ</t>
+  </si>
+  <si>
+    <t>rep.collected</t>
+  </si>
+  <si>
     <t>rep.collectedNote</t>
   </si>
   <si>
@@ -5875,6 +6001,276 @@
     <t>የውል ማብቂያ</t>
   </si>
   <si>
+    <t>rep.k.bestMonth</t>
+  </si>
+  <si>
+    <t>Best month collected</t>
+  </si>
+  <si>
+    <t>ብዙ የተሰበሰበበት ወር</t>
+  </si>
+  <si>
+    <t>rep.k.charged</t>
+  </si>
+  <si>
+    <t>Charged</t>
+  </si>
+  <si>
+    <t>የተጠየቀ</t>
+  </si>
+  <si>
+    <t>rep.k.covered</t>
+  </si>
+  <si>
+    <t>covered</t>
+  </si>
+  <si>
+    <t>የተሸፈነ</t>
+  </si>
+  <si>
+    <t>rep.k.entries</t>
+  </si>
+  <si>
+    <t>entries</t>
+  </si>
+  <si>
+    <t>መዝገቦች</t>
+  </si>
+  <si>
+    <t>rep.k.largest</t>
+  </si>
+  <si>
+    <t>Largest balance</t>
+  </si>
+  <si>
+    <t>rep.k.let</t>
+  </si>
+  <si>
+    <t>let</t>
+  </si>
+  <si>
+    <t>የተከራየ</t>
+  </si>
+  <si>
+    <t>rep.k.monthlyRent</t>
+  </si>
+  <si>
+    <t>Monthly rent</t>
+  </si>
+  <si>
+    <t>ወርሃዊ ኪራይ</t>
+  </si>
+  <si>
+    <t>rep.k.months</t>
+  </si>
+  <si>
+    <t>months</t>
+  </si>
+  <si>
+    <t>ወራት</t>
+  </si>
+  <si>
+    <t>rep.k.needsAction</t>
+  </si>
+  <si>
+    <t>Renew or close them</t>
+  </si>
+  <si>
+    <t>ያድሱ ወይም ይዝጉ</t>
+  </si>
+  <si>
+    <t>rep.k.none</t>
+  </si>
+  <si>
+    <t>ምንም</t>
+  </si>
+  <si>
+    <t>rep.k.notLet</t>
+  </si>
+  <si>
+    <t>not let</t>
+  </si>
+  <si>
+    <t>ያልተከራየ</t>
+  </si>
+  <si>
+    <t>rep.k.ofBilled</t>
+  </si>
+  <si>
+    <t>ከወጣው</t>
+  </si>
+  <si>
+    <t>rep.k.ofCharged</t>
+  </si>
+  <si>
+    <t>of charged</t>
+  </si>
+  <si>
+    <t>ከተጠየቀው</t>
+  </si>
+  <si>
+    <t>rep.k.ofOutstanding</t>
+  </si>
+  <si>
+    <t>of outstanding</t>
+  </si>
+  <si>
+    <t>ከቀሪው</t>
+  </si>
+  <si>
+    <t>rep.k.ofUnits</t>
+  </si>
+  <si>
+    <t>of all units</t>
+  </si>
+  <si>
+    <t>ከሁሉም ክፍሎች</t>
+  </si>
+  <si>
+    <t>rep.k.other</t>
+  </si>
+  <si>
+    <t>Reserved or in repair</t>
+  </si>
+  <si>
+    <t>የተያዙ ወይም በጥገና</t>
+  </si>
+  <si>
+    <t>rep.k.otherNote</t>
+  </si>
+  <si>
+    <t>not available to let</t>
+  </si>
+  <si>
+    <t>ለመከራየት የማይገኙ</t>
+  </si>
+  <si>
+    <t>rep.k.over90</t>
+  </si>
+  <si>
+    <t>Over 90 days</t>
+  </si>
+  <si>
+    <t>ከ90 ቀን በላይ</t>
+  </si>
+  <si>
+    <t>rep.k.overdue</t>
+  </si>
+  <si>
+    <t>ያለፈ</t>
+  </si>
+  <si>
+    <t>rep.k.paid</t>
+  </si>
+  <si>
+    <t>rep.k.pastEnd</t>
+  </si>
+  <si>
+    <t>Past end</t>
+  </si>
+  <si>
+    <t>rep.k.potential</t>
+  </si>
+  <si>
+    <t>Rent waiting to be let</t>
+  </si>
+  <si>
+    <t>ለመከራየት የሚጠብቅ ኪራይ</t>
+  </si>
+  <si>
+    <t>rep.k.received</t>
+  </si>
+  <si>
+    <t>received</t>
+  </si>
+  <si>
+    <t>የደረሰ</t>
+  </si>
+  <si>
+    <t>rep.k.refundsDue</t>
+  </si>
+  <si>
+    <t>refunds due</t>
+  </si>
+  <si>
+    <t>የሚመለሱ</t>
+  </si>
+  <si>
+    <t>rep.k.renters</t>
+  </si>
+  <si>
+    <t>renters owing</t>
+  </si>
+  <si>
+    <t>ተከራዮች ዕዳ ያለባቸው</t>
+  </si>
+  <si>
+    <t>rep.k.rentPerM2</t>
+  </si>
+  <si>
+    <t>Average rent per m²</t>
+  </si>
+  <si>
+    <t>አማካይ ኪራይ በካሬ ሜትር</t>
+  </si>
+  <si>
+    <t>rep.k.required</t>
+  </si>
+  <si>
+    <t>Deposits required</t>
+  </si>
+  <si>
+    <t>የሚያስፈልግ ዋስትና</t>
+  </si>
+  <si>
+    <t>rep.k.settled</t>
+  </si>
+  <si>
+    <t>Settled</t>
+  </si>
+  <si>
+    <t>rep.k.shortfallNote</t>
+  </si>
+  <si>
+    <t>held below what leases require</t>
+  </si>
+  <si>
+    <t>ከውሎች መስፈርት በታች ተይዞ ያለ</t>
+  </si>
+  <si>
+    <t>rep.k.units</t>
+  </si>
+  <si>
+    <t>units</t>
+  </si>
+  <si>
+    <t>rep.k.vacantArea</t>
+  </si>
+  <si>
+    <t>Vacant area</t>
+  </si>
+  <si>
+    <t>ክፍት ስፋት</t>
+  </si>
+  <si>
+    <t>rep.k.vacantUnits</t>
+  </si>
+  <si>
+    <t>Vacant units</t>
+  </si>
+  <si>
+    <t>ክፍት ክፍሎች</t>
+  </si>
+  <si>
+    <t>rep.k.yearly</t>
+  </si>
+  <si>
+    <t>per year</t>
+  </si>
+  <si>
+    <t>በዓመት</t>
+  </si>
+  <si>
     <t>rep.leases</t>
   </si>
   <si>
@@ -5905,6 +6301,15 @@
     <t>ከማብቂያ ቀናቸው ያለፉና ገና ያልተዘጉ</t>
   </si>
   <si>
+    <t>rep.pastEndTitle</t>
+  </si>
+  <si>
+    <t>Past their end date</t>
+  </si>
+  <si>
+    <t>ማብቂያ ቀናቸው ያለፈ</t>
+  </si>
+  <si>
     <t>rep.refundDue</t>
   </si>
   <si>
@@ -6404,9 +6809,6 @@
   </si>
   <si>
     <t>sms.kpi.delivered</t>
-  </si>
-  <si>
-    <t>የደረሰ</t>
   </si>
   <si>
     <t>sms.kpi.queued</t>
@@ -17100,7 +17502,7 @@
         <v>1954</v>
       </c>
       <c r="D684" t="s">
-        <v>1352</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="685">
@@ -17108,10 +17510,10 @@
         <v>1603</v>
       </c>
       <c r="B685" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="C685" t="s">
-        <v>1956</v>
+        <v>1685</v>
       </c>
       <c r="D685" t="s">
         <v>1957</v>
@@ -17125,10 +17527,10 @@
         <v>1958</v>
       </c>
       <c r="C686" t="s">
-        <v>1614</v>
+        <v>1959</v>
       </c>
       <c r="D686" t="s">
-        <v>1629</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="687">
@@ -17136,13 +17538,13 @@
         <v>1603</v>
       </c>
       <c r="B687" t="s">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="C687" t="s">
-        <v>42</v>
+        <v>1962</v>
       </c>
       <c r="D687" t="s">
-        <v>43</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="688">
@@ -17150,13 +17552,13 @@
         <v>1603</v>
       </c>
       <c r="B688" t="s">
-        <v>1960</v>
+        <v>1964</v>
       </c>
       <c r="C688" t="s">
-        <v>1961</v>
+        <v>1965</v>
       </c>
       <c r="D688" t="s">
-        <v>1962</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="689">
@@ -17164,13 +17566,13 @@
         <v>1603</v>
       </c>
       <c r="B689" t="s">
-        <v>1963</v>
+        <v>1967</v>
       </c>
       <c r="C689" t="s">
-        <v>1964</v>
+        <v>1968</v>
       </c>
       <c r="D689" t="s">
-        <v>1965</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="690">
@@ -17178,13 +17580,13 @@
         <v>1603</v>
       </c>
       <c r="B690" t="s">
-        <v>1966</v>
+        <v>1970</v>
       </c>
       <c r="C690" t="s">
-        <v>1967</v>
+        <v>1971</v>
       </c>
       <c r="D690" t="s">
-        <v>1968</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="691">
@@ -17192,13 +17594,13 @@
         <v>1603</v>
       </c>
       <c r="B691" t="s">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="C691" t="s">
-        <v>1970</v>
+        <v>1974</v>
       </c>
       <c r="D691" t="s">
-        <v>1971</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="692">
@@ -17206,13 +17608,13 @@
         <v>1603</v>
       </c>
       <c r="B692" t="s">
-        <v>1972</v>
+        <v>1976</v>
       </c>
       <c r="C692" t="s">
-        <v>1973</v>
+        <v>1977</v>
       </c>
       <c r="D692" t="s">
-        <v>1974</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="693">
@@ -17220,13 +17622,13 @@
         <v>1603</v>
       </c>
       <c r="B693" t="s">
-        <v>1975</v>
+        <v>1979</v>
       </c>
       <c r="C693" t="s">
-        <v>1976</v>
+        <v>346</v>
       </c>
       <c r="D693" t="s">
-        <v>1977</v>
+        <v>347</v>
       </c>
     </row>
     <row r="694">
@@ -17234,13 +17636,13 @@
         <v>1603</v>
       </c>
       <c r="B694" t="s">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="C694" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="D694" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="695">
@@ -17248,13 +17650,13 @@
         <v>1603</v>
       </c>
       <c r="B695" t="s">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="C695" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="D695" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="696">
@@ -17262,13 +17664,13 @@
         <v>1603</v>
       </c>
       <c r="B696" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="C696" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="D696" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="697">
@@ -17276,13 +17678,13 @@
         <v>1603</v>
       </c>
       <c r="B697" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="C697" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="D697" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="698">
@@ -17290,13 +17692,13 @@
         <v>1603</v>
       </c>
       <c r="B698" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="C698" t="s">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="D698" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="699">
@@ -17304,74 +17706,74 @@
         <v>1603</v>
       </c>
       <c r="B699" t="s">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="C699" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="D699" t="s">
-        <v>1995</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="s">
-        <v>1996</v>
+        <v>1603</v>
       </c>
       <c r="B700" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="C700" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="D700" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="s">
-        <v>1996</v>
+        <v>1603</v>
       </c>
       <c r="B701" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="C701" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="D701" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="s">
-        <v>1996</v>
+        <v>1603</v>
       </c>
       <c r="B702" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="C702" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="D702" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="s">
-        <v>1996</v>
+        <v>1603</v>
       </c>
       <c r="B703" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="C703" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="D703" t="s">
-        <v>2008</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="s">
-        <v>1278</v>
+        <v>1603</v>
       </c>
       <c r="B704" t="s">
         <v>2009</v>
@@ -17385,7 +17787,7 @@
     </row>
     <row r="705">
       <c r="A705" t="s">
-        <v>1278</v>
+        <v>1603</v>
       </c>
       <c r="B705" t="s">
         <v>2012</v>
@@ -17399,7 +17801,7 @@
     </row>
     <row r="706">
       <c r="A706" t="s">
-        <v>1278</v>
+        <v>1603</v>
       </c>
       <c r="B706" t="s">
         <v>2015</v>
@@ -17413,7 +17815,7 @@
     </row>
     <row r="707">
       <c r="A707" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B707" t="s">
         <v>2018</v>
@@ -17427,674 +17829,674 @@
     </row>
     <row r="708">
       <c r="A708" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B708" t="s">
         <v>2021</v>
       </c>
       <c r="C708" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D708" t="s">
         <v>2022</v>
-      </c>
-      <c r="D708" t="s">
-        <v>2023</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B709" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C709" t="s">
         <v>2024</v>
       </c>
-      <c r="C709" t="s">
+      <c r="D709" t="s">
         <v>2025</v>
-      </c>
-      <c r="D709" t="s">
-        <v>2026</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B710" t="s">
+        <v>2026</v>
+      </c>
+      <c r="C710" t="s">
+        <v>357</v>
+      </c>
+      <c r="D710" t="s">
         <v>2027</v>
-      </c>
-      <c r="C710" t="s">
-        <v>2028</v>
-      </c>
-      <c r="D710" t="s">
-        <v>2029</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B711" t="s">
+        <v>2028</v>
+      </c>
+      <c r="C711" t="s">
+        <v>2029</v>
+      </c>
+      <c r="D711" t="s">
         <v>2030</v>
-      </c>
-      <c r="C711" t="s">
-        <v>2031</v>
-      </c>
-      <c r="D711" t="s">
-        <v>2032</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B712" t="s">
+        <v>2031</v>
+      </c>
+      <c r="C712" t="s">
+        <v>2032</v>
+      </c>
+      <c r="D712" t="s">
         <v>2033</v>
-      </c>
-      <c r="C712" t="s">
-        <v>2034</v>
-      </c>
-      <c r="D712" t="s">
-        <v>2035</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B713" t="s">
+        <v>2034</v>
+      </c>
+      <c r="C713" t="s">
+        <v>2035</v>
+      </c>
+      <c r="D713" t="s">
         <v>2036</v>
-      </c>
-      <c r="C713" t="s">
-        <v>2037</v>
-      </c>
-      <c r="D713" t="s">
-        <v>2038</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B714" t="s">
+        <v>2037</v>
+      </c>
+      <c r="C714" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D714" t="s">
         <v>2039</v>
-      </c>
-      <c r="C714" t="s">
-        <v>2040</v>
-      </c>
-      <c r="D714" t="s">
-        <v>2041</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B715" t="s">
+        <v>2040</v>
+      </c>
+      <c r="C715" t="s">
+        <v>2041</v>
+      </c>
+      <c r="D715" t="s">
         <v>2042</v>
-      </c>
-      <c r="C715" t="s">
-        <v>2043</v>
-      </c>
-      <c r="D715" t="s">
-        <v>2044</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B716" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C716" t="s">
+        <v>2044</v>
+      </c>
+      <c r="D716" t="s">
         <v>2045</v>
-      </c>
-      <c r="C716" t="s">
-        <v>2046</v>
-      </c>
-      <c r="D716" t="s">
-        <v>2047</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B717" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
       <c r="C717" t="s">
-        <v>2049</v>
+        <v>352</v>
       </c>
       <c r="D717" t="s">
-        <v>2050</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B718" t="s">
-        <v>2051</v>
+        <v>2048</v>
       </c>
       <c r="C718" t="s">
-        <v>2052</v>
+        <v>369</v>
       </c>
       <c r="D718" t="s">
-        <v>2053</v>
+        <v>370</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B719" t="s">
-        <v>2054</v>
+        <v>2049</v>
       </c>
       <c r="C719" t="s">
-        <v>2055</v>
+        <v>2050</v>
       </c>
       <c r="D719" t="s">
-        <v>2056</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B720" t="s">
-        <v>2057</v>
+        <v>2051</v>
       </c>
       <c r="C720" t="s">
-        <v>2058</v>
+        <v>2052</v>
       </c>
       <c r="D720" t="s">
-        <v>2059</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B721" t="s">
-        <v>2060</v>
+        <v>2054</v>
       </c>
       <c r="C721" t="s">
-        <v>2061</v>
+        <v>2055</v>
       </c>
       <c r="D721" t="s">
-        <v>2062</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B722" t="s">
-        <v>2063</v>
+        <v>2057</v>
       </c>
       <c r="C722" t="s">
-        <v>2064</v>
+        <v>2058</v>
       </c>
       <c r="D722" t="s">
-        <v>2065</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B723" t="s">
-        <v>2066</v>
+        <v>2060</v>
       </c>
       <c r="C723" t="s">
-        <v>2067</v>
+        <v>2061</v>
       </c>
       <c r="D723" t="s">
-        <v>2068</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B724" t="s">
-        <v>2069</v>
+        <v>2063</v>
       </c>
       <c r="C724" t="s">
-        <v>2070</v>
+        <v>2064</v>
       </c>
       <c r="D724" t="s">
-        <v>2071</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B725" t="s">
-        <v>2072</v>
+        <v>2066</v>
       </c>
       <c r="C725" t="s">
-        <v>2073</v>
+        <v>2067</v>
       </c>
       <c r="D725" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B726" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="C726" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="D726" t="s">
-        <v>2077</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B727" t="s">
-        <v>2078</v>
+        <v>2071</v>
       </c>
       <c r="C727" t="s">
-        <v>2079</v>
+        <v>2072</v>
       </c>
       <c r="D727" t="s">
-        <v>2080</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B728" t="s">
-        <v>2081</v>
+        <v>2074</v>
       </c>
       <c r="C728" t="s">
-        <v>2082</v>
+        <v>2075</v>
       </c>
       <c r="D728" t="s">
-        <v>2083</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B729" t="s">
-        <v>2084</v>
+        <v>2076</v>
       </c>
       <c r="C729" t="s">
-        <v>2085</v>
+        <v>2077</v>
       </c>
       <c r="D729" t="s">
-        <v>2086</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B730" t="s">
-        <v>2087</v>
+        <v>2079</v>
       </c>
       <c r="C730" t="s">
-        <v>2088</v>
+        <v>2080</v>
       </c>
       <c r="D730" t="s">
-        <v>2089</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B731" t="s">
-        <v>2090</v>
+        <v>2082</v>
       </c>
       <c r="C731" t="s">
-        <v>2091</v>
+        <v>2083</v>
       </c>
       <c r="D731" t="s">
-        <v>2092</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B732" t="s">
-        <v>2093</v>
+        <v>2085</v>
       </c>
       <c r="C732" t="s">
-        <v>2094</v>
+        <v>2086</v>
       </c>
       <c r="D732" t="s">
-        <v>2095</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B733" t="s">
-        <v>2096</v>
+        <v>2087</v>
       </c>
       <c r="C733" t="s">
-        <v>2097</v>
+        <v>2088</v>
       </c>
       <c r="D733" t="s">
-        <v>2098</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B734" t="s">
-        <v>2099</v>
+        <v>2090</v>
       </c>
       <c r="C734" t="s">
-        <v>2100</v>
+        <v>1614</v>
       </c>
       <c r="D734" t="s">
-        <v>2101</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B735" t="s">
-        <v>2102</v>
+        <v>2091</v>
       </c>
       <c r="C735" t="s">
-        <v>2103</v>
+        <v>42</v>
       </c>
       <c r="D735" t="s">
-        <v>2104</v>
+        <v>43</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B736" t="s">
-        <v>2105</v>
+        <v>2092</v>
       </c>
       <c r="C736" t="s">
-        <v>2106</v>
+        <v>2093</v>
       </c>
       <c r="D736" t="s">
-        <v>2107</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B737" t="s">
-        <v>2108</v>
+        <v>2095</v>
       </c>
       <c r="C737" t="s">
-        <v>2109</v>
+        <v>2096</v>
       </c>
       <c r="D737" t="s">
-        <v>2110</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B738" t="s">
-        <v>2111</v>
+        <v>2098</v>
       </c>
       <c r="C738" t="s">
-        <v>2112</v>
+        <v>2099</v>
       </c>
       <c r="D738" t="s">
-        <v>2113</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B739" t="s">
-        <v>2114</v>
+        <v>2101</v>
       </c>
       <c r="C739" t="s">
-        <v>2115</v>
+        <v>2102</v>
       </c>
       <c r="D739" t="s">
-        <v>2116</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B740" t="s">
-        <v>2117</v>
+        <v>2104</v>
       </c>
       <c r="C740" t="s">
-        <v>2118</v>
+        <v>2105</v>
       </c>
       <c r="D740" t="s">
-        <v>2119</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B741" t="s">
-        <v>2120</v>
+        <v>2107</v>
       </c>
       <c r="C741" t="s">
-        <v>2121</v>
+        <v>2108</v>
       </c>
       <c r="D741" t="s">
-        <v>2122</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B742" t="s">
-        <v>2123</v>
+        <v>2110</v>
       </c>
       <c r="C742" t="s">
-        <v>2124</v>
+        <v>2111</v>
       </c>
       <c r="D742" t="s">
-        <v>2125</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B743" t="s">
-        <v>2126</v>
+        <v>2113</v>
       </c>
       <c r="C743" t="s">
-        <v>2127</v>
+        <v>2114</v>
       </c>
       <c r="D743" t="s">
-        <v>2128</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B744" t="s">
-        <v>2129</v>
+        <v>2116</v>
       </c>
       <c r="C744" t="s">
-        <v>925</v>
+        <v>2117</v>
       </c>
       <c r="D744" t="s">
-        <v>2130</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B745" t="s">
-        <v>2131</v>
+        <v>2119</v>
       </c>
       <c r="C745" t="s">
-        <v>2132</v>
+        <v>2120</v>
       </c>
       <c r="D745" t="s">
-        <v>2133</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B746" t="s">
-        <v>2134</v>
+        <v>2122</v>
       </c>
       <c r="C746" t="s">
-        <v>2135</v>
+        <v>2123</v>
       </c>
       <c r="D746" t="s">
-        <v>2136</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B747" t="s">
-        <v>2137</v>
+        <v>2125</v>
       </c>
       <c r="C747" t="s">
-        <v>2138</v>
+        <v>2126</v>
       </c>
       <c r="D747" t="s">
-        <v>2139</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="B748" t="s">
-        <v>2140</v>
+        <v>2128</v>
       </c>
       <c r="C748" t="s">
-        <v>2141</v>
+        <v>2129</v>
       </c>
       <c r="D748" t="s">
-        <v>2142</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="s">
-        <v>1594</v>
+        <v>2131</v>
       </c>
       <c r="B749" t="s">
-        <v>2143</v>
+        <v>2132</v>
       </c>
       <c r="C749" t="s">
-        <v>2144</v>
+        <v>2133</v>
       </c>
       <c r="D749" t="s">
-        <v>2145</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="s">
-        <v>1594</v>
+        <v>2131</v>
       </c>
       <c r="B750" t="s">
-        <v>2146</v>
+        <v>2135</v>
       </c>
       <c r="C750" t="s">
-        <v>2147</v>
+        <v>2136</v>
       </c>
       <c r="D750" t="s">
-        <v>2148</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="s">
-        <v>1594</v>
+        <v>2131</v>
       </c>
       <c r="B751" t="s">
-        <v>2149</v>
+        <v>2138</v>
       </c>
       <c r="C751" t="s">
-        <v>2150</v>
+        <v>2139</v>
       </c>
       <c r="D751" t="s">
-        <v>2151</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="s">
-        <v>1594</v>
+        <v>2131</v>
       </c>
       <c r="B752" t="s">
-        <v>2152</v>
+        <v>2141</v>
       </c>
       <c r="C752" t="s">
-        <v>2153</v>
+        <v>2142</v>
       </c>
       <c r="D752" t="s">
-        <v>2154</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="s">
-        <v>1594</v>
+        <v>1278</v>
       </c>
       <c r="B753" t="s">
-        <v>2155</v>
+        <v>2144</v>
       </c>
       <c r="C753" t="s">
-        <v>2156</v>
+        <v>2145</v>
       </c>
       <c r="D753" t="s">
-        <v>2157</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="s">
-        <v>1594</v>
+        <v>1278</v>
       </c>
       <c r="B754" t="s">
-        <v>2158</v>
+        <v>2147</v>
       </c>
       <c r="C754" t="s">
-        <v>2159</v>
+        <v>2148</v>
       </c>
       <c r="D754" t="s">
-        <v>2160</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="s">
-        <v>1594</v>
+        <v>1278</v>
       </c>
       <c r="B755" t="s">
-        <v>2161</v>
+        <v>2150</v>
       </c>
       <c r="C755" t="s">
-        <v>2162</v>
+        <v>2151</v>
       </c>
       <c r="D755" t="s">
-        <v>2163</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="756">
@@ -18102,13 +18504,13 @@
         <v>1594</v>
       </c>
       <c r="B756" t="s">
-        <v>2164</v>
+        <v>2153</v>
       </c>
       <c r="C756" t="s">
-        <v>2165</v>
+        <v>2154</v>
       </c>
       <c r="D756" t="s">
-        <v>2166</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="757">
@@ -18116,13 +18518,13 @@
         <v>1594</v>
       </c>
       <c r="B757" t="s">
-        <v>2167</v>
+        <v>2156</v>
       </c>
       <c r="C757" t="s">
-        <v>2168</v>
+        <v>2157</v>
       </c>
       <c r="D757" t="s">
-        <v>2169</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="758">
@@ -18130,13 +18532,13 @@
         <v>1594</v>
       </c>
       <c r="B758" t="s">
-        <v>2170</v>
+        <v>2159</v>
       </c>
       <c r="C758" t="s">
-        <v>2171</v>
+        <v>2160</v>
       </c>
       <c r="D758" t="s">
-        <v>2172</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="759">
@@ -18144,13 +18546,13 @@
         <v>1594</v>
       </c>
       <c r="B759" t="s">
-        <v>2173</v>
+        <v>2162</v>
       </c>
       <c r="C759" t="s">
-        <v>2174</v>
+        <v>2163</v>
       </c>
       <c r="D759" t="s">
-        <v>2175</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="760">
@@ -18158,13 +18560,13 @@
         <v>1594</v>
       </c>
       <c r="B760" t="s">
-        <v>2176</v>
+        <v>2165</v>
       </c>
       <c r="C760" t="s">
-        <v>2177</v>
+        <v>2166</v>
       </c>
       <c r="D760" t="s">
-        <v>2178</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="761">
@@ -18172,13 +18574,13 @@
         <v>1594</v>
       </c>
       <c r="B761" t="s">
-        <v>2179</v>
+        <v>2168</v>
       </c>
       <c r="C761" t="s">
-        <v>2180</v>
+        <v>2169</v>
       </c>
       <c r="D761" t="s">
-        <v>2181</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="762">
@@ -18186,13 +18588,13 @@
         <v>1594</v>
       </c>
       <c r="B762" t="s">
-        <v>2182</v>
+        <v>2171</v>
       </c>
       <c r="C762" t="s">
-        <v>2183</v>
+        <v>2172</v>
       </c>
       <c r="D762" t="s">
-        <v>2184</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="763">
@@ -18200,13 +18602,13 @@
         <v>1594</v>
       </c>
       <c r="B763" t="s">
-        <v>2185</v>
+        <v>2174</v>
       </c>
       <c r="C763" t="s">
-        <v>306</v>
+        <v>2175</v>
       </c>
       <c r="D763" t="s">
-        <v>307</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="764">
@@ -18214,13 +18616,13 @@
         <v>1594</v>
       </c>
       <c r="B764" t="s">
-        <v>2186</v>
+        <v>2177</v>
       </c>
       <c r="C764" t="s">
-        <v>2187</v>
+        <v>2178</v>
       </c>
       <c r="D764" t="s">
-        <v>2188</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="765">
@@ -18228,13 +18630,13 @@
         <v>1594</v>
       </c>
       <c r="B765" t="s">
-        <v>2189</v>
+        <v>2180</v>
       </c>
       <c r="C765" t="s">
-        <v>2190</v>
+        <v>2181</v>
       </c>
       <c r="D765" t="s">
-        <v>2191</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="766">
@@ -18242,13 +18644,13 @@
         <v>1594</v>
       </c>
       <c r="B766" t="s">
-        <v>2192</v>
+        <v>2183</v>
       </c>
       <c r="C766" t="s">
-        <v>2193</v>
+        <v>2184</v>
       </c>
       <c r="D766" t="s">
-        <v>2194</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="767">
@@ -18256,13 +18658,13 @@
         <v>1594</v>
       </c>
       <c r="B767" t="s">
-        <v>2195</v>
+        <v>2186</v>
       </c>
       <c r="C767" t="s">
-        <v>2196</v>
+        <v>2187</v>
       </c>
       <c r="D767" t="s">
-        <v>2197</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="768">
@@ -18270,13 +18672,13 @@
         <v>1594</v>
       </c>
       <c r="B768" t="s">
-        <v>2198</v>
+        <v>2189</v>
       </c>
       <c r="C768" t="s">
-        <v>503</v>
+        <v>2190</v>
       </c>
       <c r="D768" t="s">
-        <v>504</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="769">
@@ -18284,13 +18686,13 @@
         <v>1594</v>
       </c>
       <c r="B769" t="s">
-        <v>2199</v>
+        <v>2192</v>
       </c>
       <c r="C769" t="s">
-        <v>2200</v>
+        <v>2193</v>
       </c>
       <c r="D769" t="s">
-        <v>2201</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="770">
@@ -18298,13 +18700,13 @@
         <v>1594</v>
       </c>
       <c r="B770" t="s">
-        <v>2202</v>
+        <v>2195</v>
       </c>
       <c r="C770" t="s">
-        <v>2203</v>
+        <v>2196</v>
       </c>
       <c r="D770" t="s">
-        <v>2204</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="771">
@@ -18312,13 +18714,13 @@
         <v>1594</v>
       </c>
       <c r="B771" t="s">
-        <v>2205</v>
+        <v>2198</v>
       </c>
       <c r="C771" t="s">
-        <v>744</v>
+        <v>2199</v>
       </c>
       <c r="D771" t="s">
-        <v>745</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="772">
@@ -18326,13 +18728,13 @@
         <v>1594</v>
       </c>
       <c r="B772" t="s">
-        <v>2206</v>
+        <v>2201</v>
       </c>
       <c r="C772" t="s">
-        <v>2207</v>
+        <v>2202</v>
       </c>
       <c r="D772" t="s">
-        <v>2208</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="773">
@@ -18340,13 +18742,13 @@
         <v>1594</v>
       </c>
       <c r="B773" t="s">
-        <v>2209</v>
+        <v>2204</v>
       </c>
       <c r="C773" t="s">
-        <v>2210</v>
+        <v>2205</v>
       </c>
       <c r="D773" t="s">
-        <v>2211</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="774">
@@ -18354,13 +18756,13 @@
         <v>1594</v>
       </c>
       <c r="B774" t="s">
-        <v>2212</v>
+        <v>2207</v>
       </c>
       <c r="C774" t="s">
-        <v>2213</v>
+        <v>2208</v>
       </c>
       <c r="D774" t="s">
-        <v>2214</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="775">
@@ -18368,13 +18770,13 @@
         <v>1594</v>
       </c>
       <c r="B775" t="s">
-        <v>2215</v>
+        <v>2210</v>
       </c>
       <c r="C775" t="s">
-        <v>2216</v>
+        <v>2211</v>
       </c>
       <c r="D775" t="s">
-        <v>2217</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="776">
@@ -18382,13 +18784,13 @@
         <v>1594</v>
       </c>
       <c r="B776" t="s">
-        <v>2218</v>
+        <v>2213</v>
       </c>
       <c r="C776" t="s">
-        <v>2219</v>
+        <v>2214</v>
       </c>
       <c r="D776" t="s">
-        <v>2220</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="777">
@@ -18396,13 +18798,13 @@
         <v>1594</v>
       </c>
       <c r="B777" t="s">
-        <v>2221</v>
+        <v>2216</v>
       </c>
       <c r="C777" t="s">
-        <v>2222</v>
+        <v>2217</v>
       </c>
       <c r="D777" t="s">
-        <v>2223</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="778">
@@ -18410,13 +18812,13 @@
         <v>1594</v>
       </c>
       <c r="B778" t="s">
-        <v>2224</v>
+        <v>2219</v>
       </c>
       <c r="C778" t="s">
-        <v>2225</v>
+        <v>2220</v>
       </c>
       <c r="D778" t="s">
-        <v>2226</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="779">
@@ -18424,13 +18826,13 @@
         <v>1594</v>
       </c>
       <c r="B779" t="s">
-        <v>2227</v>
+        <v>2222</v>
       </c>
       <c r="C779" t="s">
-        <v>2228</v>
+        <v>2223</v>
       </c>
       <c r="D779" t="s">
-        <v>2229</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="780">
@@ -18438,13 +18840,13 @@
         <v>1594</v>
       </c>
       <c r="B780" t="s">
-        <v>2230</v>
+        <v>2225</v>
       </c>
       <c r="C780" t="s">
-        <v>2231</v>
+        <v>2226</v>
       </c>
       <c r="D780" t="s">
-        <v>2232</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="781">
@@ -18452,13 +18854,13 @@
         <v>1594</v>
       </c>
       <c r="B781" t="s">
-        <v>2233</v>
+        <v>2228</v>
       </c>
       <c r="C781" t="s">
-        <v>2234</v>
+        <v>2229</v>
       </c>
       <c r="D781" t="s">
-        <v>2235</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="782">
@@ -18466,13 +18868,13 @@
         <v>1594</v>
       </c>
       <c r="B782" t="s">
-        <v>2236</v>
+        <v>2231</v>
       </c>
       <c r="C782" t="s">
-        <v>2237</v>
+        <v>2232</v>
       </c>
       <c r="D782" t="s">
-        <v>733</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="783">
@@ -18480,13 +18882,13 @@
         <v>1594</v>
       </c>
       <c r="B783" t="s">
-        <v>2238</v>
+        <v>2234</v>
       </c>
       <c r="C783" t="s">
-        <v>2239</v>
+        <v>2235</v>
       </c>
       <c r="D783" t="s">
-        <v>2240</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="784">
@@ -18494,13 +18896,13 @@
         <v>1594</v>
       </c>
       <c r="B784" t="s">
-        <v>2241</v>
+        <v>2237</v>
       </c>
       <c r="C784" t="s">
-        <v>2242</v>
+        <v>2238</v>
       </c>
       <c r="D784" t="s">
-        <v>2243</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="785">
@@ -18508,13 +18910,13 @@
         <v>1594</v>
       </c>
       <c r="B785" t="s">
-        <v>2244</v>
+        <v>2240</v>
       </c>
       <c r="C785" t="s">
-        <v>2245</v>
+        <v>2241</v>
       </c>
       <c r="D785" t="s">
-        <v>2246</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="786">
@@ -18522,13 +18924,13 @@
         <v>1594</v>
       </c>
       <c r="B786" t="s">
-        <v>2247</v>
+        <v>2243</v>
       </c>
       <c r="C786" t="s">
-        <v>2248</v>
+        <v>2244</v>
       </c>
       <c r="D786" t="s">
-        <v>2249</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="787">
@@ -18536,13 +18938,13 @@
         <v>1594</v>
       </c>
       <c r="B787" t="s">
-        <v>2250</v>
+        <v>2246</v>
       </c>
       <c r="C787" t="s">
-        <v>2251</v>
+        <v>2247</v>
       </c>
       <c r="D787" t="s">
-        <v>2252</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="788">
@@ -18550,13 +18952,13 @@
         <v>1594</v>
       </c>
       <c r="B788" t="s">
-        <v>2253</v>
+        <v>2249</v>
       </c>
       <c r="C788" t="s">
-        <v>2254</v>
+        <v>2250</v>
       </c>
       <c r="D788" t="s">
-        <v>2255</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="789">
@@ -18564,13 +18966,13 @@
         <v>1594</v>
       </c>
       <c r="B789" t="s">
-        <v>2256</v>
+        <v>2252</v>
       </c>
       <c r="C789" t="s">
-        <v>2257</v>
+        <v>2253</v>
       </c>
       <c r="D789" t="s">
-        <v>2258</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="790">
@@ -18578,13 +18980,13 @@
         <v>1594</v>
       </c>
       <c r="B790" t="s">
-        <v>2259</v>
+        <v>2255</v>
       </c>
       <c r="C790" t="s">
-        <v>2260</v>
+        <v>2256</v>
       </c>
       <c r="D790" t="s">
-        <v>2261</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="791">
@@ -18592,13 +18994,13 @@
         <v>1594</v>
       </c>
       <c r="B791" t="s">
-        <v>2262</v>
+        <v>2258</v>
       </c>
       <c r="C791" t="s">
-        <v>2263</v>
+        <v>2259</v>
       </c>
       <c r="D791" t="s">
-        <v>142</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="792">
@@ -18606,13 +19008,13 @@
         <v>1594</v>
       </c>
       <c r="B792" t="s">
-        <v>2264</v>
+        <v>2261</v>
       </c>
       <c r="C792" t="s">
-        <v>2265</v>
+        <v>2262</v>
       </c>
       <c r="D792" t="s">
-        <v>1557</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="793">
@@ -18620,13 +19022,13 @@
         <v>1594</v>
       </c>
       <c r="B793" t="s">
-        <v>2266</v>
+        <v>2264</v>
       </c>
       <c r="C793" t="s">
-        <v>2267</v>
+        <v>925</v>
       </c>
       <c r="D793" t="s">
-        <v>1557</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="794">
@@ -18634,13 +19036,13 @@
         <v>1594</v>
       </c>
       <c r="B794" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="C794" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
       <c r="D794" t="s">
-        <v>2270</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="795">
@@ -18648,13 +19050,13 @@
         <v>1594</v>
       </c>
       <c r="B795" t="s">
-        <v>2271</v>
+        <v>2268</v>
       </c>
       <c r="C795" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
       <c r="D795" t="s">
-        <v>2273</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="796">
@@ -18662,13 +19064,13 @@
         <v>1594</v>
       </c>
       <c r="B796" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="C796" t="s">
-        <v>2275</v>
+        <v>2272</v>
       </c>
       <c r="D796" t="s">
-        <v>2276</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="797">
@@ -18676,13 +19078,13 @@
         <v>1594</v>
       </c>
       <c r="B797" t="s">
-        <v>2277</v>
+        <v>2274</v>
       </c>
       <c r="C797" t="s">
-        <v>2278</v>
+        <v>2275</v>
       </c>
       <c r="D797" t="s">
-        <v>2279</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="798">
@@ -18690,13 +19092,13 @@
         <v>1594</v>
       </c>
       <c r="B798" t="s">
-        <v>2280</v>
+        <v>2277</v>
       </c>
       <c r="C798" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
       <c r="D798" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="799">
@@ -18704,13 +19106,13 @@
         <v>1594</v>
       </c>
       <c r="B799" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
       <c r="C799" t="s">
-        <v>2284</v>
+        <v>2281</v>
       </c>
       <c r="D799" t="s">
-        <v>2285</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="800">
@@ -18718,13 +19120,13 @@
         <v>1594</v>
       </c>
       <c r="B800" t="s">
-        <v>2286</v>
+        <v>2283</v>
       </c>
       <c r="C800" t="s">
-        <v>2287</v>
+        <v>2284</v>
       </c>
       <c r="D800" t="s">
-        <v>2288</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="801">
@@ -18732,13 +19134,13 @@
         <v>1594</v>
       </c>
       <c r="B801" t="s">
-        <v>2289</v>
+        <v>2286</v>
       </c>
       <c r="C801" t="s">
-        <v>2290</v>
+        <v>2287</v>
       </c>
       <c r="D801" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="802">
@@ -18746,13 +19148,13 @@
         <v>1594</v>
       </c>
       <c r="B802" t="s">
-        <v>2292</v>
+        <v>2289</v>
       </c>
       <c r="C802" t="s">
-        <v>2293</v>
+        <v>2290</v>
       </c>
       <c r="D802" t="s">
-        <v>2294</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="803">
@@ -18760,13 +19162,13 @@
         <v>1594</v>
       </c>
       <c r="B803" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
       <c r="C803" t="s">
-        <v>2296</v>
+        <v>2293</v>
       </c>
       <c r="D803" t="s">
-        <v>2297</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="804">
@@ -18774,13 +19176,13 @@
         <v>1594</v>
       </c>
       <c r="B804" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
       <c r="C804" t="s">
-        <v>2299</v>
+        <v>2296</v>
       </c>
       <c r="D804" t="s">
-        <v>2300</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="805">
@@ -18788,13 +19190,13 @@
         <v>1594</v>
       </c>
       <c r="B805" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
       <c r="C805" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="D805" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="806">
@@ -18802,13 +19204,13 @@
         <v>1594</v>
       </c>
       <c r="B806" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
       <c r="C806" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="D806" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="807">
@@ -18816,13 +19218,13 @@
         <v>1594</v>
       </c>
       <c r="B807" t="s">
-        <v>2307</v>
+        <v>2304</v>
       </c>
       <c r="C807" t="s">
-        <v>2308</v>
+        <v>2305</v>
       </c>
       <c r="D807" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="808">
@@ -18830,13 +19232,13 @@
         <v>1594</v>
       </c>
       <c r="B808" t="s">
-        <v>2310</v>
+        <v>2307</v>
       </c>
       <c r="C808" t="s">
-        <v>2311</v>
+        <v>2308</v>
       </c>
       <c r="D808" t="s">
-        <v>2312</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="809">
@@ -18844,13 +19246,13 @@
         <v>1594</v>
       </c>
       <c r="B809" t="s">
-        <v>2313</v>
+        <v>2310</v>
       </c>
       <c r="C809" t="s">
-        <v>2109</v>
+        <v>2311</v>
       </c>
       <c r="D809" t="s">
-        <v>2110</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="810">
@@ -18858,13 +19260,13 @@
         <v>1594</v>
       </c>
       <c r="B810" t="s">
+        <v>2313</v>
+      </c>
+      <c r="C810" t="s">
         <v>2314</v>
       </c>
-      <c r="C810" t="s">
+      <c r="D810" t="s">
         <v>2315</v>
-      </c>
-      <c r="D810" t="s">
-        <v>2316</v>
       </c>
     </row>
     <row r="811">
@@ -18872,13 +19274,13 @@
         <v>1594</v>
       </c>
       <c r="B811" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C811" t="s">
         <v>2317</v>
       </c>
-      <c r="C811" t="s">
-        <v>2118</v>
-      </c>
       <c r="D811" t="s">
-        <v>2119</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="812">
@@ -18886,13 +19288,13 @@
         <v>1594</v>
       </c>
       <c r="B812" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="C812" t="s">
-        <v>2319</v>
+        <v>306</v>
       </c>
       <c r="D812" t="s">
-        <v>2320</v>
+        <v>307</v>
       </c>
     </row>
     <row r="813">
@@ -18900,13 +19302,13 @@
         <v>1594</v>
       </c>
       <c r="B813" t="s">
+        <v>2320</v>
+      </c>
+      <c r="C813" t="s">
         <v>2321</v>
       </c>
-      <c r="C813" t="s">
-        <v>2121</v>
-      </c>
       <c r="D813" t="s">
-        <v>2122</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="814">
@@ -18914,13 +19316,13 @@
         <v>1594</v>
       </c>
       <c r="B814" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="C814" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="D814" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="815">
@@ -18928,13 +19330,13 @@
         <v>1594</v>
       </c>
       <c r="B815" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="C815" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="D815" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="816">
@@ -18942,13 +19344,13 @@
         <v>1594</v>
       </c>
       <c r="B816" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="C816" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="D816" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="817">
@@ -18956,13 +19358,13 @@
         <v>1594</v>
       </c>
       <c r="B817" t="s">
-        <v>2331</v>
+        <v>2332</v>
       </c>
       <c r="C817" t="s">
-        <v>2332</v>
+        <v>503</v>
       </c>
       <c r="D817" t="s">
-        <v>2333</v>
+        <v>504</v>
       </c>
     </row>
     <row r="818">
@@ -18970,13 +19372,13 @@
         <v>1594</v>
       </c>
       <c r="B818" t="s">
+        <v>2333</v>
+      </c>
+      <c r="C818" t="s">
         <v>2334</v>
       </c>
-      <c r="C818" t="s">
+      <c r="D818" t="s">
         <v>2335</v>
-      </c>
-      <c r="D818" t="s">
-        <v>2336</v>
       </c>
     </row>
     <row r="819">
@@ -18984,13 +19386,13 @@
         <v>1594</v>
       </c>
       <c r="B819" t="s">
+        <v>2336</v>
+      </c>
+      <c r="C819" t="s">
         <v>2337</v>
       </c>
-      <c r="C819" t="s">
+      <c r="D819" t="s">
         <v>2338</v>
-      </c>
-      <c r="D819" t="s">
-        <v>2339</v>
       </c>
     </row>
     <row r="820">
@@ -18998,13 +19400,13 @@
         <v>1594</v>
       </c>
       <c r="B820" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="C820" t="s">
-        <v>1904</v>
+        <v>744</v>
       </c>
       <c r="D820" t="s">
-        <v>444</v>
+        <v>745</v>
       </c>
     </row>
     <row r="821">
@@ -19012,13 +19414,13 @@
         <v>1594</v>
       </c>
       <c r="B821" t="s">
+        <v>2340</v>
+      </c>
+      <c r="C821" t="s">
         <v>2341</v>
       </c>
-      <c r="C821" t="s">
+      <c r="D821" t="s">
         <v>2342</v>
-      </c>
-      <c r="D821" t="s">
-        <v>2343</v>
       </c>
     </row>
     <row r="822">
@@ -19026,13 +19428,13 @@
         <v>1594</v>
       </c>
       <c r="B822" t="s">
+        <v>2343</v>
+      </c>
+      <c r="C822" t="s">
         <v>2344</v>
       </c>
-      <c r="C822" t="s">
+      <c r="D822" t="s">
         <v>2345</v>
-      </c>
-      <c r="D822" t="s">
-        <v>2346</v>
       </c>
     </row>
     <row r="823">
@@ -19040,130 +19442,130 @@
         <v>1594</v>
       </c>
       <c r="B823" t="s">
+        <v>2346</v>
+      </c>
+      <c r="C823" t="s">
         <v>2347</v>
       </c>
-      <c r="C823" t="s">
+      <c r="D823" t="s">
         <v>2348</v>
-      </c>
-      <c r="D823" t="s">
-        <v>2349</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="s">
-        <v>1609</v>
+        <v>1594</v>
       </c>
       <c r="B824" t="s">
+        <v>2349</v>
+      </c>
+      <c r="C824" t="s">
         <v>2350</v>
       </c>
-      <c r="C824" t="s">
-        <v>832</v>
-      </c>
       <c r="D824" t="s">
-        <v>833</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="s">
-        <v>1609</v>
+        <v>1594</v>
       </c>
       <c r="B825" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
       <c r="C825" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="D825" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="s">
-        <v>1609</v>
+        <v>1594</v>
       </c>
       <c r="B826" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="C826" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="D826" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="s">
-        <v>2357</v>
+        <v>1594</v>
       </c>
       <c r="B827" t="s">
         <v>2358</v>
       </c>
       <c r="C827" t="s">
-        <v>2357</v>
+        <v>2359</v>
       </c>
       <c r="D827" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="s">
-        <v>2357</v>
+        <v>1594</v>
       </c>
       <c r="B828" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="C828" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="D828" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="s">
-        <v>2357</v>
+        <v>1594</v>
       </c>
       <c r="B829" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="C829" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="D829" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="s">
-        <v>2357</v>
+        <v>1594</v>
       </c>
       <c r="B830" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="C830" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="D830" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B831" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
       <c r="C831" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
       <c r="D831" t="s">
-        <v>2371</v>
+        <v>733</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B832" t="s">
         <v>2372</v>
@@ -19177,7 +19579,7 @@
     </row>
     <row r="833">
       <c r="A833" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B833" t="s">
         <v>2375</v>
@@ -19191,133 +19593,133 @@
     </row>
     <row r="834">
       <c r="A834" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B834" t="s">
         <v>2378</v>
       </c>
       <c r="C834" t="s">
-        <v>280</v>
+        <v>2379</v>
       </c>
       <c r="D834" t="s">
-        <v>281</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B835" t="s">
-        <v>2379</v>
+        <v>2381</v>
       </c>
       <c r="C835" t="s">
-        <v>2380</v>
+        <v>2382</v>
       </c>
       <c r="D835" t="s">
-        <v>1764</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B836" t="s">
-        <v>2381</v>
+        <v>2384</v>
       </c>
       <c r="C836" t="s">
-        <v>2382</v>
+        <v>2385</v>
       </c>
       <c r="D836" t="s">
-        <v>2383</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B837" t="s">
-        <v>2384</v>
+        <v>2387</v>
       </c>
       <c r="C837" t="s">
-        <v>2385</v>
+        <v>2388</v>
       </c>
       <c r="D837" t="s">
-        <v>2386</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B838" t="s">
-        <v>2387</v>
+        <v>2390</v>
       </c>
       <c r="C838" t="s">
-        <v>2388</v>
+        <v>2391</v>
       </c>
       <c r="D838" t="s">
-        <v>2389</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="839">
       <c r="A839" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B839" t="s">
-        <v>2390</v>
+        <v>2393</v>
       </c>
       <c r="C839" t="s">
-        <v>2391</v>
+        <v>2394</v>
       </c>
       <c r="D839" t="s">
-        <v>2392</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B840" t="s">
-        <v>2393</v>
+        <v>2396</v>
       </c>
       <c r="C840" t="s">
-        <v>2394</v>
+        <v>2397</v>
       </c>
       <c r="D840" t="s">
-        <v>2395</v>
+        <v>142</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B841" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="C841" t="s">
-        <v>2397</v>
+        <v>2399</v>
       </c>
       <c r="D841" t="s">
-        <v>2398</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B842" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="C842" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="D842" t="s">
-        <v>2401</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B843" t="s">
         <v>2402</v>
@@ -19331,7 +19733,7 @@
     </row>
     <row r="844">
       <c r="A844" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B844" t="s">
         <v>2405</v>
@@ -19345,7 +19747,7 @@
     </row>
     <row r="845">
       <c r="A845" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B845" t="s">
         <v>2408</v>
@@ -19359,7 +19761,7 @@
     </row>
     <row r="846">
       <c r="A846" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B846" t="s">
         <v>2411</v>
@@ -19373,7 +19775,7 @@
     </row>
     <row r="847">
       <c r="A847" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B847" t="s">
         <v>2414</v>
@@ -19387,189 +19789,189 @@
     </row>
     <row r="848">
       <c r="A848" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B848" t="s">
         <v>2417</v>
       </c>
       <c r="C848" t="s">
-        <v>2391</v>
+        <v>2418</v>
       </c>
       <c r="D848" t="s">
-        <v>2392</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B849" t="s">
-        <v>2418</v>
+        <v>2420</v>
       </c>
       <c r="C849" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
       <c r="D849" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B850" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="C850" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="D850" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B851" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="C851" t="s">
-        <v>2425</v>
+        <v>2427</v>
       </c>
       <c r="D851" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B852" t="s">
-        <v>2427</v>
+        <v>2429</v>
       </c>
       <c r="C852" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
       <c r="D852" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B853" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
       <c r="C853" t="s">
-        <v>2431</v>
+        <v>2433</v>
       </c>
       <c r="D853" t="s">
-        <v>2432</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B854" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
       <c r="C854" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
       <c r="D854" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B855" t="s">
-        <v>2436</v>
+        <v>2438</v>
       </c>
       <c r="C855" t="s">
-        <v>2437</v>
+        <v>2439</v>
       </c>
       <c r="D855" t="s">
-        <v>2438</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B856" t="s">
-        <v>2439</v>
+        <v>2441</v>
       </c>
       <c r="C856" t="s">
-        <v>2440</v>
+        <v>2442</v>
       </c>
       <c r="D856" t="s">
-        <v>2441</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B857" t="s">
-        <v>2442</v>
+        <v>2444</v>
       </c>
       <c r="C857" t="s">
-        <v>2382</v>
+        <v>2445</v>
       </c>
       <c r="D857" t="s">
-        <v>2383</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B858" t="s">
-        <v>2443</v>
+        <v>2447</v>
       </c>
       <c r="C858" t="s">
-        <v>2444</v>
+        <v>2244</v>
       </c>
       <c r="D858" t="s">
-        <v>2445</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B859" t="s">
-        <v>2446</v>
+        <v>2448</v>
       </c>
       <c r="C859" t="s">
-        <v>2447</v>
+        <v>2449</v>
       </c>
       <c r="D859" t="s">
-        <v>2448</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B860" t="s">
-        <v>2449</v>
+        <v>2451</v>
       </c>
       <c r="C860" t="s">
-        <v>2450</v>
+        <v>2253</v>
       </c>
       <c r="D860" t="s">
-        <v>2451</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B861" t="s">
         <v>2452</v>
@@ -19583,91 +19985,91 @@
     </row>
     <row r="862">
       <c r="A862" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B862" t="s">
         <v>2455</v>
       </c>
       <c r="C862" t="s">
-        <v>2456</v>
+        <v>2256</v>
       </c>
       <c r="D862" t="s">
-        <v>2457</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B863" t="s">
+        <v>2456</v>
+      </c>
+      <c r="C863" t="s">
+        <v>2457</v>
+      </c>
+      <c r="D863" t="s">
         <v>2458</v>
-      </c>
-      <c r="C863" t="s">
-        <v>2459</v>
-      </c>
-      <c r="D863" t="s">
-        <v>2460</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B864" t="s">
+        <v>2459</v>
+      </c>
+      <c r="C864" t="s">
+        <v>2460</v>
+      </c>
+      <c r="D864" t="s">
         <v>2461</v>
-      </c>
-      <c r="C864" t="s">
-        <v>2462</v>
-      </c>
-      <c r="D864" t="s">
-        <v>2463</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B865" t="s">
+        <v>2462</v>
+      </c>
+      <c r="C865" t="s">
+        <v>2463</v>
+      </c>
+      <c r="D865" t="s">
         <v>2464</v>
-      </c>
-      <c r="C865" t="s">
-        <v>2465</v>
-      </c>
-      <c r="D865" t="s">
-        <v>2466</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B866" t="s">
+        <v>2465</v>
+      </c>
+      <c r="C866" t="s">
+        <v>2466</v>
+      </c>
+      <c r="D866" t="s">
         <v>2467</v>
-      </c>
-      <c r="C866" t="s">
-        <v>2468</v>
-      </c>
-      <c r="D866" t="s">
-        <v>2469</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B867" t="s">
+        <v>2468</v>
+      </c>
+      <c r="C867" t="s">
+        <v>2469</v>
+      </c>
+      <c r="D867" t="s">
         <v>2470</v>
-      </c>
-      <c r="C867" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D867" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B868" t="s">
         <v>2471</v>
@@ -19681,44 +20083,730 @@
     </row>
     <row r="869">
       <c r="A869" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B869" t="s">
         <v>2474</v>
       </c>
       <c r="C869" t="s">
-        <v>2475</v>
+        <v>1904</v>
       </c>
       <c r="D869" t="s">
-        <v>2476</v>
+        <v>444</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
       <c r="B870" t="s">
+        <v>2475</v>
+      </c>
+      <c r="C870" t="s">
+        <v>2476</v>
+      </c>
+      <c r="D870" t="s">
         <v>2477</v>
-      </c>
-      <c r="C870" t="s">
-        <v>2478</v>
-      </c>
-      <c r="D870" t="s">
-        <v>2479</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B871" t="s">
+        <v>2478</v>
+      </c>
+      <c r="C871" t="s">
+        <v>2479</v>
+      </c>
+      <c r="D871" t="s">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B872" t="s">
+        <v>2481</v>
+      </c>
+      <c r="C872" t="s">
+        <v>2482</v>
+      </c>
+      <c r="D872" t="s">
+        <v>2483</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B873" t="s">
+        <v>2484</v>
+      </c>
+      <c r="C873" t="s">
+        <v>832</v>
+      </c>
+      <c r="D873" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B874" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C874" t="s">
+        <v>2486</v>
+      </c>
+      <c r="D874" t="s">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B875" t="s">
+        <v>2488</v>
+      </c>
+      <c r="C875" t="s">
+        <v>2489</v>
+      </c>
+      <c r="D875" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="s">
+        <v>2491</v>
+      </c>
+      <c r="B876" t="s">
+        <v>2492</v>
+      </c>
+      <c r="C876" t="s">
+        <v>2491</v>
+      </c>
+      <c r="D876" t="s">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="s">
+        <v>2491</v>
+      </c>
+      <c r="B877" t="s">
+        <v>2494</v>
+      </c>
+      <c r="C877" t="s">
+        <v>2495</v>
+      </c>
+      <c r="D877" t="s">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="s">
+        <v>2491</v>
+      </c>
+      <c r="B878" t="s">
+        <v>2497</v>
+      </c>
+      <c r="C878" t="s">
+        <v>2498</v>
+      </c>
+      <c r="D878" t="s">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="s">
+        <v>2491</v>
+      </c>
+      <c r="B879" t="s">
+        <v>2500</v>
+      </c>
+      <c r="C879" t="s">
+        <v>2501</v>
+      </c>
+      <c r="D879" t="s">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="s">
         <v>1612</v>
       </c>
-      <c r="B871" t="s">
-        <v>2480</v>
-      </c>
-      <c r="C871" t="s">
-        <v>2481</v>
-      </c>
-      <c r="D871" t="s">
-        <v>2482</v>
+      <c r="B880" t="s">
+        <v>2503</v>
+      </c>
+      <c r="C880" t="s">
+        <v>2504</v>
+      </c>
+      <c r="D880" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B881" t="s">
+        <v>2506</v>
+      </c>
+      <c r="C881" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D881" t="s">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B882" t="s">
+        <v>2509</v>
+      </c>
+      <c r="C882" t="s">
+        <v>2510</v>
+      </c>
+      <c r="D882" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B883" t="s">
+        <v>2512</v>
+      </c>
+      <c r="C883" t="s">
+        <v>280</v>
+      </c>
+      <c r="D883" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B884" t="s">
+        <v>2513</v>
+      </c>
+      <c r="C884" t="s">
+        <v>2514</v>
+      </c>
+      <c r="D884" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B885" t="s">
+        <v>2515</v>
+      </c>
+      <c r="C885" t="s">
+        <v>2516</v>
+      </c>
+      <c r="D885" t="s">
+        <v>2517</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B886" t="s">
+        <v>2518</v>
+      </c>
+      <c r="C886" t="s">
+        <v>2519</v>
+      </c>
+      <c r="D886" t="s">
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B887" t="s">
+        <v>2521</v>
+      </c>
+      <c r="C887" t="s">
+        <v>2522</v>
+      </c>
+      <c r="D887" t="s">
+        <v>2523</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B888" t="s">
+        <v>2524</v>
+      </c>
+      <c r="C888" t="s">
+        <v>2525</v>
+      </c>
+      <c r="D888" t="s">
+        <v>2526</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B889" t="s">
+        <v>2527</v>
+      </c>
+      <c r="C889" t="s">
+        <v>2528</v>
+      </c>
+      <c r="D889" t="s">
+        <v>2529</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B890" t="s">
+        <v>2530</v>
+      </c>
+      <c r="C890" t="s">
+        <v>2531</v>
+      </c>
+      <c r="D890" t="s">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B891" t="s">
+        <v>2533</v>
+      </c>
+      <c r="C891" t="s">
+        <v>2534</v>
+      </c>
+      <c r="D891" t="s">
+        <v>2535</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B892" t="s">
+        <v>2536</v>
+      </c>
+      <c r="C892" t="s">
+        <v>2537</v>
+      </c>
+      <c r="D892" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B893" t="s">
+        <v>2539</v>
+      </c>
+      <c r="C893" t="s">
+        <v>2540</v>
+      </c>
+      <c r="D893" t="s">
+        <v>2541</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B894" t="s">
+        <v>2542</v>
+      </c>
+      <c r="C894" t="s">
+        <v>2543</v>
+      </c>
+      <c r="D894" t="s">
+        <v>2544</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B895" t="s">
+        <v>2545</v>
+      </c>
+      <c r="C895" t="s">
+        <v>2546</v>
+      </c>
+      <c r="D895" t="s">
+        <v>2547</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B896" t="s">
+        <v>2548</v>
+      </c>
+      <c r="C896" t="s">
+        <v>2549</v>
+      </c>
+      <c r="D896" t="s">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B897" t="s">
+        <v>2551</v>
+      </c>
+      <c r="C897" t="s">
+        <v>2525</v>
+      </c>
+      <c r="D897" t="s">
+        <v>2526</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B898" t="s">
+        <v>2552</v>
+      </c>
+      <c r="C898" t="s">
+        <v>2553</v>
+      </c>
+      <c r="D898" t="s">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B899" t="s">
+        <v>2555</v>
+      </c>
+      <c r="C899" t="s">
+        <v>2556</v>
+      </c>
+      <c r="D899" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B900" t="s">
+        <v>2558</v>
+      </c>
+      <c r="C900" t="s">
+        <v>2559</v>
+      </c>
+      <c r="D900" t="s">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B901" t="s">
+        <v>2561</v>
+      </c>
+      <c r="C901" t="s">
+        <v>2562</v>
+      </c>
+      <c r="D901" t="s">
+        <v>2563</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B902" t="s">
+        <v>2564</v>
+      </c>
+      <c r="C902" t="s">
+        <v>2565</v>
+      </c>
+      <c r="D902" t="s">
+        <v>2566</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B903" t="s">
+        <v>2567</v>
+      </c>
+      <c r="C903" t="s">
+        <v>2568</v>
+      </c>
+      <c r="D903" t="s">
+        <v>2569</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B904" t="s">
+        <v>2570</v>
+      </c>
+      <c r="C904" t="s">
+        <v>2571</v>
+      </c>
+      <c r="D904" t="s">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B905" t="s">
+        <v>2573</v>
+      </c>
+      <c r="C905" t="s">
+        <v>2574</v>
+      </c>
+      <c r="D905" t="s">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B906" t="s">
+        <v>2576</v>
+      </c>
+      <c r="C906" t="s">
+        <v>2516</v>
+      </c>
+      <c r="D906" t="s">
+        <v>2517</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B907" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C907" t="s">
+        <v>2578</v>
+      </c>
+      <c r="D907" t="s">
+        <v>2579</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B908" t="s">
+        <v>2580</v>
+      </c>
+      <c r="C908" t="s">
+        <v>2581</v>
+      </c>
+      <c r="D908" t="s">
+        <v>2582</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B909" t="s">
+        <v>2583</v>
+      </c>
+      <c r="C909" t="s">
+        <v>2584</v>
+      </c>
+      <c r="D909" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B910" t="s">
+        <v>2586</v>
+      </c>
+      <c r="C910" t="s">
+        <v>2587</v>
+      </c>
+      <c r="D910" t="s">
+        <v>2588</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B911" t="s">
+        <v>2589</v>
+      </c>
+      <c r="C911" t="s">
+        <v>2590</v>
+      </c>
+      <c r="D911" t="s">
+        <v>2591</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B912" t="s">
+        <v>2592</v>
+      </c>
+      <c r="C912" t="s">
+        <v>2593</v>
+      </c>
+      <c r="D912" t="s">
+        <v>2594</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B913" t="s">
+        <v>2595</v>
+      </c>
+      <c r="C913" t="s">
+        <v>2596</v>
+      </c>
+      <c r="D913" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B914" t="s">
+        <v>2598</v>
+      </c>
+      <c r="C914" t="s">
+        <v>2599</v>
+      </c>
+      <c r="D914" t="s">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B915" t="s">
+        <v>2601</v>
+      </c>
+      <c r="C915" t="s">
+        <v>2602</v>
+      </c>
+      <c r="D915" t="s">
+        <v>2603</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B916" t="s">
+        <v>2604</v>
+      </c>
+      <c r="C916" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D916" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B917" t="s">
+        <v>2605</v>
+      </c>
+      <c r="C917" t="s">
+        <v>2606</v>
+      </c>
+      <c r="D917" t="s">
+        <v>2607</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B918" t="s">
+        <v>2608</v>
+      </c>
+      <c r="C918" t="s">
+        <v>2609</v>
+      </c>
+      <c r="D918" t="s">
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B919" t="s">
+        <v>2611</v>
+      </c>
+      <c r="C919" t="s">
+        <v>2612</v>
+      </c>
+      <c r="D919" t="s">
+        <v>2613</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B920" t="s">
+        <v>2614</v>
+      </c>
+      <c r="C920" t="s">
+        <v>2615</v>
+      </c>
+      <c r="D920" t="s">
+        <v>2616</v>
       </c>
     </row>
   </sheetData>

--- a/docs/amharic-review.xlsx
+++ b/docs/amharic-review.xlsx
@@ -4255,6 +4255,24 @@
     <t>ውሎች</t>
   </si>
   <si>
+    <t>imp.another</t>
+  </si>
+  <si>
+    <t>Import another file</t>
+  </si>
+  <si>
+    <t>ሌላ ፋይል አስገባ</t>
+  </si>
+  <si>
+    <t>imp.backupFirst</t>
+  </si>
+  <si>
+    <t>Do the load once, on go-live day. Take a backup first (see the backup guide), and prove the numbers against the old books afterwards.</t>
+  </si>
+  <si>
+    <t>መጫኑን አንድ ጊዜ፣ በሥራ መጀመሪያ ቀን ያድርጉ። መጀመሪያ ምትኬ ይውሰዱ፣ ከዚያም ቁጥሮቹን ከድሮ መዝገብ ጋር ያመሳስሉ።</t>
+  </si>
+  <si>
     <t>imp.choose</t>
   </si>
   <si>
@@ -4309,6 +4327,60 @@
     <t>ገብቷል።</t>
   </si>
   <si>
+    <t>imp.doneAgreements</t>
+  </si>
+  <si>
+    <t>{n} agreements were added: {a} active and {e} expired. Units with an active lease are now occupied.</t>
+  </si>
+  <si>
+    <t>{n} ስምምነቶች ተጨመሩ፦ {a} ንቁ እና {e} ያበቁ። ንቁ ውል ያላቸው ክፍሎች አሁን ተይዘዋል።</t>
+  </si>
+  <si>
+    <t>imp.doneOpening</t>
+  </si>
+  <si>
+    <t>{n} rows were loaded. Owed: ETB {o}. Prepaid credit: ETB {c}. Find the bills under Bills, Opening balance.</t>
+  </si>
+  <si>
+    <t>{n} ረድፎች ተጭነዋል። ዕዳ፦ ብር {o}። አስቀድሞ የተከፈለ፦ ብር {c}። ደረሰኞቹን በደረሰኞች፣ የመነሻ ቀሪ ውስጥ ያገኛሉ።</t>
+  </si>
+  <si>
+    <t>imp.doneRenters</t>
+  </si>
+  <si>
+    <t>{n} renters were added to the register.</t>
+  </si>
+  <si>
+    <t>{n} ተከራዮች ወደ መዝገቡ ተጨመሩ።</t>
+  </si>
+  <si>
+    <t>imp.doneUnits</t>
+  </si>
+  <si>
+    <t>{u} units were added, with {b} new buildings and {f} new floors.</t>
+  </si>
+  <si>
+    <t>{u} ክፍሎች ተጨመሩ፣ {b} አዲስ ሕንፃዎችና {f} አዲስ ፎቆች ጋር።</t>
+  </si>
+  <si>
+    <t>imp.downloadProblems</t>
+  </si>
+  <si>
+    <t>Download the list</t>
+  </si>
+  <si>
+    <t>ዝርዝሩን አውርድ</t>
+  </si>
+  <si>
+    <t>imp.drop</t>
+  </si>
+  <si>
+    <t>Drop your Excel or CSV file here</t>
+  </si>
+  <si>
+    <t>የExcel ወይም CSV ፋይልዎን እዚህ ይጣሉ</t>
+  </si>
+  <si>
     <t>imp.err.already_exists</t>
   </si>
   <si>
@@ -4648,6 +4720,15 @@
     <t>የመጀመሪያ ቀን</t>
   </si>
   <si>
+    <t>imp.fileNeeds</t>
+  </si>
+  <si>
+    <t>Your file needs these columns</t>
+  </si>
+  <si>
+    <t>ፋይልዎ እነዚህ ዓምዶች ያስፈልጉታል</t>
+  </si>
+  <si>
     <t>imp.fixFirst</t>
   </si>
   <si>
@@ -4711,6 +4792,15 @@
     <t>ሥራ የሚጀመርበት ቀን (ረድፍ የመክፈያ ቀን ሲጎድለው)</t>
   </si>
   <si>
+    <t>imp.op.asOfHint</t>
+  </si>
+  <si>
+    <t>Bills without a due date of their own are dated this day.</t>
+  </si>
+  <si>
+    <t>የራሱ የመክፈያ ቀን የሌላቸው ደረሰኞች በዚህ ቀን ይመዘገባሉ።</t>
+  </si>
+  <si>
     <t>imp.op.confirmBody</t>
   </si>
   <si>
@@ -4738,6 +4828,9 @@
     <t>የመነሻ ሂሳቦች</t>
   </si>
   <si>
+    <t>imp.optionalCol</t>
+  </si>
+  <si>
     <t>imp.owed</t>
   </si>
   <si>
@@ -4810,6 +4903,24 @@
     <t>ተከራዮች</t>
   </si>
   <si>
+    <t>imp.replaceFile</t>
+  </si>
+  <si>
+    <t>Click or drop to replace the file</t>
+  </si>
+  <si>
+    <t>ፋይሉን ለመቀየር ይጫኑ ወይም ይጣሉ</t>
+  </si>
+  <si>
+    <t>imp.required</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>አስፈላጊ</t>
+  </si>
+  <si>
     <t>imp.row</t>
   </si>
   <si>
@@ -4834,6 +4945,42 @@
     <t>አስገባ</t>
   </si>
   <si>
+    <t>imp.step.bills</t>
+  </si>
+  <si>
+    <t>opening bills</t>
+  </si>
+  <si>
+    <t>የመነሻ ደረሰኞች</t>
+  </si>
+  <si>
+    <t>imp.step.empty</t>
+  </si>
+  <si>
+    <t>Nothing loaded yet</t>
+  </si>
+  <si>
+    <t>እስካሁን ምንም አልተጫነም</t>
+  </si>
+  <si>
+    <t>imp.step.locked</t>
+  </si>
+  <si>
+    <t>Not for your role</t>
+  </si>
+  <si>
+    <t>ለእርስዎ ሚና አይደለም</t>
+  </si>
+  <si>
+    <t>imp.stepsLabel</t>
+  </si>
+  <si>
+    <t>Steps in order</t>
+  </si>
+  <si>
+    <t>ደረጃዎች በቅደም ተከተል</t>
+  </si>
+  <si>
     <t>imp.sub</t>
   </si>
   <si>
@@ -4871,6 +5018,42 @@
   </si>
   <si>
     <t>imp.valid</t>
+  </si>
+  <si>
+    <t>imp.what.agreements</t>
+  </si>
+  <si>
+    <t>Step 3. Current and past leases with rent, dates and deposits. Each lease needs its unit and renter from steps 1 and 2. Approvers only.</t>
+  </si>
+  <si>
+    <t>ደረጃ 3። አሁን ያሉና ያለፉ ውሎች ከኪራይ፣ ቀናትና ዋስትና ጋር። እያንዳንዱ ውል ከደረጃ 1 እና 2 ክፍልና ተከራይ ያስፈልገዋል። አጽዳቂዎች ብቻ።</t>
+  </si>
+  <si>
+    <t>imp.what.opening</t>
+  </si>
+  <si>
+    <t>Step 4. What each renter owes today, as bills with their original due dates, and any rent paid in advance. Approvers and finance only.</t>
+  </si>
+  <si>
+    <t>ደረጃ 4። እያንዳንዱ ተከራይ ዛሬ ያለበት ዕዳ በመጀመሪያ የመክፈያ ቀኑ እንደ ደረሰኝ፣ እና አስቀድሞ የተከፈለ ኪራይ። አጽዳቂዎችና ፋይናንስ ብቻ።</t>
+  </si>
+  <si>
+    <t>imp.what.renters</t>
+  </si>
+  <si>
+    <t>Step 2. The renter register: company or individual, TIN or ID number, phone and contacts.</t>
+  </si>
+  <si>
+    <t>ደረጃ 2። የተከራዮች መዝገብ፦ ድርጅት ወይም ግለሰብ፣ TIN ወይም መታወቂያ ቁጥር፣ ስልክና አድራሻዎች።</t>
+  </si>
+  <si>
+    <t>imp.what.units</t>
+  </si>
+  <si>
+    <t>Step 1. Your buildings, floors and units, with area, category and rate per m². Everything else attaches to these.</t>
+  </si>
+  <si>
+    <t>ደረጃ 1። ሕንፃዎች፣ ፎቆችና ክፍሎች ከስፋት፣ ምድብና በካሬ ሜትር ዋጋ ጋር። ሌላው ሁሉ ከእነዚህ ጋር ይያያዛል።</t>
   </si>
   <si>
     <t>Lease contract</t>
@@ -15090,10 +15273,10 @@
         <v>1455</v>
       </c>
       <c r="C498" t="s">
-        <v>826</v>
+        <v>1456</v>
       </c>
       <c r="D498" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="499">
@@ -15101,13 +15284,13 @@
         <v>1403</v>
       </c>
       <c r="B499" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C499" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="D499" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="500">
@@ -15115,13 +15298,13 @@
         <v>1403</v>
       </c>
       <c r="B500" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="C500" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="D500" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="501">
@@ -15129,13 +15312,13 @@
         <v>1403</v>
       </c>
       <c r="B501" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="C501" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="D501" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="502">
@@ -15143,13 +15326,13 @@
         <v>1403</v>
       </c>
       <c r="B502" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="C502" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="D502" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="503">
@@ -15157,13 +15340,13 @@
         <v>1403</v>
       </c>
       <c r="B503" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="C503" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="D503" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="504">
@@ -15171,13 +15354,13 @@
         <v>1403</v>
       </c>
       <c r="B504" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="C504" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="D504" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="505">
@@ -15185,13 +15368,13 @@
         <v>1403</v>
       </c>
       <c r="B505" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="C505" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="D505" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="506">
@@ -15199,10 +15382,10 @@
         <v>1403</v>
       </c>
       <c r="B506" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="C506" t="s">
-        <v>1479</v>
+        <v>826</v>
       </c>
       <c r="D506" t="s">
         <v>1480</v>
@@ -15384,10 +15567,10 @@
         <v>1517</v>
       </c>
       <c r="C519" t="s">
-        <v>886</v>
+        <v>1518</v>
       </c>
       <c r="D519" t="s">
-        <v>887</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="520">
@@ -15395,13 +15578,13 @@
         <v>1403</v>
       </c>
       <c r="B520" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="C520" t="s">
-        <v>126</v>
+        <v>1521</v>
       </c>
       <c r="D520" t="s">
-        <v>127</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="521">
@@ -15409,13 +15592,13 @@
         <v>1403</v>
       </c>
       <c r="B521" t="s">
-        <v>1519</v>
+        <v>1523</v>
       </c>
       <c r="C521" t="s">
-        <v>584</v>
+        <v>1524</v>
       </c>
       <c r="D521" t="s">
-        <v>1520</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="522">
@@ -15423,13 +15606,13 @@
         <v>1403</v>
       </c>
       <c r="B522" t="s">
-        <v>1521</v>
+        <v>1526</v>
       </c>
       <c r="C522" t="s">
-        <v>1522</v>
+        <v>1527</v>
       </c>
       <c r="D522" t="s">
-        <v>1523</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="523">
@@ -15437,13 +15620,13 @@
         <v>1403</v>
       </c>
       <c r="B523" t="s">
-        <v>1524</v>
+        <v>1529</v>
       </c>
       <c r="C523" t="s">
-        <v>330</v>
+        <v>1530</v>
       </c>
       <c r="D523" t="s">
-        <v>331</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="524">
@@ -15451,13 +15634,13 @@
         <v>1403</v>
       </c>
       <c r="B524" t="s">
-        <v>1525</v>
+        <v>1532</v>
       </c>
       <c r="C524" t="s">
-        <v>1526</v>
+        <v>1533</v>
       </c>
       <c r="D524" t="s">
-        <v>331</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="525">
@@ -15465,13 +15648,13 @@
         <v>1403</v>
       </c>
       <c r="B525" t="s">
-        <v>1527</v>
+        <v>1535</v>
       </c>
       <c r="C525" t="s">
-        <v>1528</v>
+        <v>1536</v>
       </c>
       <c r="D525" t="s">
-        <v>1529</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="526">
@@ -15479,13 +15662,13 @@
         <v>1403</v>
       </c>
       <c r="B526" t="s">
-        <v>1530</v>
+        <v>1538</v>
       </c>
       <c r="C526" t="s">
-        <v>1531</v>
+        <v>1539</v>
       </c>
       <c r="D526" t="s">
-        <v>1532</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="527">
@@ -15493,13 +15676,13 @@
         <v>1403</v>
       </c>
       <c r="B527" t="s">
-        <v>1533</v>
+        <v>1541</v>
       </c>
       <c r="C527" t="s">
-        <v>1534</v>
+        <v>886</v>
       </c>
       <c r="D527" t="s">
-        <v>1535</v>
+        <v>887</v>
       </c>
     </row>
     <row r="528">
@@ -15507,13 +15690,13 @@
         <v>1403</v>
       </c>
       <c r="B528" t="s">
-        <v>1536</v>
+        <v>1542</v>
       </c>
       <c r="C528" t="s">
-        <v>1537</v>
+        <v>126</v>
       </c>
       <c r="D528" t="s">
-        <v>528</v>
+        <v>127</v>
       </c>
     </row>
     <row r="529">
@@ -15521,13 +15704,13 @@
         <v>1403</v>
       </c>
       <c r="B529" t="s">
-        <v>1538</v>
+        <v>1543</v>
       </c>
       <c r="C529" t="s">
-        <v>1539</v>
+        <v>584</v>
       </c>
       <c r="D529" t="s">
-        <v>1540</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="530">
@@ -15535,13 +15718,13 @@
         <v>1403</v>
       </c>
       <c r="B530" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="C530" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="D530" t="s">
-        <v>1543</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="531">
@@ -15549,13 +15732,13 @@
         <v>1403</v>
       </c>
       <c r="B531" t="s">
-        <v>1544</v>
+        <v>1548</v>
       </c>
       <c r="C531" t="s">
-        <v>1545</v>
+        <v>330</v>
       </c>
       <c r="D531" t="s">
-        <v>1546</v>
+        <v>331</v>
       </c>
     </row>
     <row r="532">
@@ -15563,13 +15746,13 @@
         <v>1403</v>
       </c>
       <c r="B532" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="C532" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="D532" t="s">
-        <v>1549</v>
+        <v>331</v>
       </c>
     </row>
     <row r="533">
@@ -15577,13 +15760,13 @@
         <v>1403</v>
       </c>
       <c r="B533" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="C533" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="D533" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="534">
@@ -15591,13 +15774,13 @@
         <v>1403</v>
       </c>
       <c r="B534" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="C534" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="D534" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="535">
@@ -15605,13 +15788,13 @@
         <v>1403</v>
       </c>
       <c r="B535" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="C535" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="D535" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="536">
@@ -15619,13 +15802,13 @@
         <v>1403</v>
       </c>
       <c r="B536" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="C536" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="D536" t="s">
-        <v>1561</v>
+        <v>528</v>
       </c>
     </row>
     <row r="537">
@@ -15832,10 +16015,10 @@
         <v>1604</v>
       </c>
       <c r="C551" t="s">
-        <v>1403</v>
+        <v>1216</v>
       </c>
       <c r="D551" t="s">
-        <v>1605</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="552">
@@ -15843,13 +16026,13 @@
         <v>1403</v>
       </c>
       <c r="B552" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C552" t="s">
         <v>1606</v>
       </c>
-      <c r="C552" t="s">
+      <c r="D552" t="s">
         <v>1607</v>
-      </c>
-      <c r="D552" t="s">
-        <v>1608</v>
       </c>
     </row>
     <row r="553">
@@ -15857,13 +16040,13 @@
         <v>1403</v>
       </c>
       <c r="B553" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C553" t="s">
         <v>1609</v>
       </c>
-      <c r="C553" t="s">
+      <c r="D553" t="s">
         <v>1610</v>
-      </c>
-      <c r="D553" t="s">
-        <v>1611</v>
       </c>
     </row>
     <row r="554">
@@ -15871,13 +16054,13 @@
         <v>1403</v>
       </c>
       <c r="B554" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C554" t="s">
         <v>1612</v>
       </c>
-      <c r="C554" t="s">
+      <c r="D554" t="s">
         <v>1613</v>
-      </c>
-      <c r="D554" t="s">
-        <v>1614</v>
       </c>
     </row>
     <row r="555">
@@ -15885,13 +16068,13 @@
         <v>1403</v>
       </c>
       <c r="B555" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C555" t="s">
         <v>1615</v>
       </c>
-      <c r="C555" t="s">
+      <c r="D555" t="s">
         <v>1616</v>
-      </c>
-      <c r="D555" t="s">
-        <v>1617</v>
       </c>
     </row>
     <row r="556">
@@ -15899,18 +16082,18 @@
         <v>1403</v>
       </c>
       <c r="B556" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C556" t="s">
         <v>1618</v>
       </c>
-      <c r="C556" t="s">
-        <v>1288</v>
-      </c>
       <c r="D556" t="s">
-        <v>1289</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="s">
-        <v>1619</v>
+        <v>1403</v>
       </c>
       <c r="B557" t="s">
         <v>1620</v>
@@ -15924,1099 +16107,1099 @@
     </row>
     <row r="558">
       <c r="A558" t="s">
-        <v>1619</v>
+        <v>1403</v>
       </c>
       <c r="B558" t="s">
         <v>1623</v>
       </c>
       <c r="C558" t="s">
-        <v>1619</v>
+        <v>1624</v>
       </c>
       <c r="D558" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="s">
-        <v>1625</v>
+        <v>1403</v>
       </c>
       <c r="B559" t="s">
         <v>1626</v>
       </c>
       <c r="C559" t="s">
-        <v>7</v>
+        <v>1627</v>
       </c>
       <c r="D559" t="s">
-        <v>1412</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="s">
-        <v>1625</v>
+        <v>1403</v>
       </c>
       <c r="B560" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="C560" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="D560" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="s">
-        <v>1625</v>
+        <v>1403</v>
       </c>
       <c r="B561" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="C561" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="D561" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="s">
-        <v>1625</v>
+        <v>1403</v>
       </c>
       <c r="B562" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="C562" t="s">
-        <v>293</v>
+        <v>1636</v>
       </c>
       <c r="D562" t="s">
-        <v>1634</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="s">
-        <v>1625</v>
+        <v>1403</v>
       </c>
       <c r="B563" t="s">
-        <v>1635</v>
+        <v>1638</v>
       </c>
       <c r="C563" t="s">
-        <v>1636</v>
+        <v>1639</v>
       </c>
       <c r="D563" t="s">
-        <v>1637</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="s">
-        <v>1625</v>
+        <v>1403</v>
       </c>
       <c r="B564" t="s">
-        <v>1638</v>
+        <v>1641</v>
       </c>
       <c r="C564" t="s">
-        <v>1639</v>
+        <v>1403</v>
       </c>
       <c r="D564" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="s">
-        <v>1625</v>
+        <v>1403</v>
       </c>
       <c r="B565" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
       <c r="C565" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="D565" t="s">
-        <v>1643</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="s">
-        <v>1625</v>
+        <v>1403</v>
       </c>
       <c r="B566" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
       <c r="C566" t="s">
-        <v>1645</v>
+        <v>1647</v>
       </c>
       <c r="D566" t="s">
-        <v>1646</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="s">
-        <v>1625</v>
+        <v>1403</v>
       </c>
       <c r="B567" t="s">
-        <v>1647</v>
+        <v>1649</v>
       </c>
       <c r="C567" t="s">
-        <v>1648</v>
+        <v>1650</v>
       </c>
       <c r="D567" t="s">
-        <v>1649</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="s">
-        <v>1625</v>
+        <v>1403</v>
       </c>
       <c r="B568" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="C568" t="s">
-        <v>1651</v>
+        <v>1653</v>
       </c>
       <c r="D568" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="s">
-        <v>1625</v>
+        <v>1403</v>
       </c>
       <c r="B569" t="s">
-        <v>1653</v>
+        <v>1655</v>
       </c>
       <c r="C569" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="D569" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="s">
-        <v>1625</v>
+        <v>1403</v>
       </c>
       <c r="B570" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="C570" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="D570" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="s">
-        <v>1625</v>
+        <v>1403</v>
       </c>
       <c r="B571" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
       <c r="C571" t="s">
-        <v>447</v>
+        <v>1662</v>
       </c>
       <c r="D571" t="s">
-        <v>1660</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="s">
-        <v>1625</v>
+        <v>1403</v>
       </c>
       <c r="B572" t="s">
-        <v>1661</v>
+        <v>1664</v>
       </c>
       <c r="C572" t="s">
-        <v>1596</v>
+        <v>1665</v>
       </c>
       <c r="D572" t="s">
-        <v>1597</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="s">
-        <v>1625</v>
+        <v>1403</v>
       </c>
       <c r="B573" t="s">
-        <v>1662</v>
+        <v>1667</v>
       </c>
       <c r="C573" t="s">
-        <v>1663</v>
+        <v>1288</v>
       </c>
       <c r="D573" t="s">
-        <v>1664</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="s">
-        <v>1625</v>
+        <v>1403</v>
       </c>
       <c r="B574" t="s">
-        <v>1665</v>
+        <v>1668</v>
       </c>
       <c r="C574" t="s">
-        <v>1666</v>
+        <v>1669</v>
       </c>
       <c r="D574" t="s">
-        <v>1667</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="s">
-        <v>1625</v>
+        <v>1403</v>
       </c>
       <c r="B575" t="s">
-        <v>1668</v>
+        <v>1671</v>
       </c>
       <c r="C575" t="s">
-        <v>1669</v>
+        <v>1672</v>
       </c>
       <c r="D575" t="s">
-        <v>1670</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="s">
-        <v>1625</v>
+        <v>1403</v>
       </c>
       <c r="B576" t="s">
-        <v>1671</v>
+        <v>1674</v>
       </c>
       <c r="C576" t="s">
-        <v>1672</v>
+        <v>1675</v>
       </c>
       <c r="D576" t="s">
-        <v>1673</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="s">
-        <v>1674</v>
+        <v>1403</v>
       </c>
       <c r="B577" t="s">
-        <v>1675</v>
+        <v>1677</v>
       </c>
       <c r="C577" t="s">
-        <v>1676</v>
+        <v>1678</v>
       </c>
       <c r="D577" t="s">
-        <v>1677</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="s">
-        <v>1674</v>
+        <v>1680</v>
       </c>
       <c r="B578" t="s">
-        <v>1678</v>
+        <v>1681</v>
       </c>
       <c r="C578" t="s">
-        <v>1679</v>
+        <v>1682</v>
       </c>
       <c r="D578" t="s">
-        <v>1680</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="s">
-        <v>1674</v>
+        <v>1680</v>
       </c>
       <c r="B579" t="s">
-        <v>1681</v>
+        <v>1684</v>
       </c>
       <c r="C579" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="D579" t="s">
-        <v>1683</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="s">
-        <v>1674</v>
+        <v>1686</v>
       </c>
       <c r="B580" t="s">
-        <v>1684</v>
+        <v>1687</v>
       </c>
       <c r="C580" t="s">
-        <v>1685</v>
+        <v>7</v>
       </c>
       <c r="D580" t="s">
-        <v>1686</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="s">
-        <v>1674</v>
+        <v>1686</v>
       </c>
       <c r="B581" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="C581" t="s">
-        <v>445</v>
+        <v>1689</v>
       </c>
       <c r="D581" t="s">
-        <v>446</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="s">
-        <v>1674</v>
+        <v>1686</v>
       </c>
       <c r="B582" t="s">
-        <v>1688</v>
+        <v>1691</v>
       </c>
       <c r="C582" t="s">
-        <v>1674</v>
+        <v>1692</v>
       </c>
       <c r="D582" t="s">
-        <v>1689</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="s">
-        <v>1636</v>
+        <v>1686</v>
       </c>
       <c r="B583" t="s">
-        <v>1690</v>
+        <v>1694</v>
       </c>
       <c r="C583" t="s">
-        <v>1691</v>
+        <v>293</v>
       </c>
       <c r="D583" t="s">
-        <v>1692</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="s">
-        <v>1636</v>
+        <v>1686</v>
       </c>
       <c r="B584" t="s">
-        <v>1693</v>
+        <v>1696</v>
       </c>
       <c r="C584" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D584" t="s">
-        <v>1695</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="s">
-        <v>1636</v>
+        <v>1686</v>
       </c>
       <c r="B585" t="s">
-        <v>1696</v>
+        <v>1699</v>
       </c>
       <c r="C585" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
       <c r="D585" t="s">
-        <v>1698</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="s">
-        <v>1636</v>
+        <v>1686</v>
       </c>
       <c r="B586" t="s">
-        <v>1699</v>
+        <v>1702</v>
       </c>
       <c r="C586" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
       <c r="D586" t="s">
-        <v>1701</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="s">
-        <v>1636</v>
+        <v>1686</v>
       </c>
       <c r="B587" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
       <c r="C587" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
       <c r="D587" t="s">
-        <v>1704</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="s">
-        <v>1636</v>
+        <v>1686</v>
       </c>
       <c r="B588" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
       <c r="C588" t="s">
-        <v>1706</v>
+        <v>1709</v>
       </c>
       <c r="D588" t="s">
-        <v>1707</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="s">
-        <v>1636</v>
+        <v>1686</v>
       </c>
       <c r="B589" t="s">
-        <v>1708</v>
+        <v>1711</v>
       </c>
       <c r="C589" t="s">
-        <v>1709</v>
+        <v>1712</v>
       </c>
       <c r="D589" t="s">
-        <v>890</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="s">
-        <v>1636</v>
+        <v>1686</v>
       </c>
       <c r="B590" t="s">
-        <v>1710</v>
+        <v>1714</v>
       </c>
       <c r="C590" t="s">
-        <v>1711</v>
+        <v>1715</v>
       </c>
       <c r="D590" t="s">
-        <v>1712</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="s">
-        <v>1636</v>
+        <v>1686</v>
       </c>
       <c r="B591" t="s">
-        <v>1713</v>
+        <v>1717</v>
       </c>
       <c r="C591" t="s">
-        <v>1714</v>
+        <v>1718</v>
       </c>
       <c r="D591" t="s">
-        <v>1715</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="s">
-        <v>1636</v>
+        <v>1686</v>
       </c>
       <c r="B592" t="s">
-        <v>1716</v>
+        <v>1720</v>
       </c>
       <c r="C592" t="s">
-        <v>1717</v>
+        <v>447</v>
       </c>
       <c r="D592" t="s">
-        <v>1718</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="s">
-        <v>1636</v>
+        <v>1686</v>
       </c>
       <c r="B593" t="s">
-        <v>1719</v>
+        <v>1722</v>
       </c>
       <c r="C593" t="s">
-        <v>1720</v>
+        <v>1627</v>
       </c>
       <c r="D593" t="s">
-        <v>1721</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="s">
-        <v>1636</v>
+        <v>1686</v>
       </c>
       <c r="B594" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="C594" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="D594" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="s">
-        <v>1636</v>
+        <v>1686</v>
       </c>
       <c r="B595" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="C595" t="s">
-        <v>370</v>
+        <v>1727</v>
       </c>
       <c r="D595" t="s">
-        <v>371</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="s">
-        <v>1636</v>
+        <v>1686</v>
       </c>
       <c r="B596" t="s">
-        <v>1726</v>
+        <v>1729</v>
       </c>
       <c r="C596" t="s">
-        <v>1727</v>
+        <v>1730</v>
       </c>
       <c r="D596" t="s">
-        <v>1728</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="s">
-        <v>1636</v>
+        <v>1686</v>
       </c>
       <c r="B597" t="s">
-        <v>1729</v>
+        <v>1732</v>
       </c>
       <c r="C597" t="s">
-        <v>1730</v>
+        <v>1733</v>
       </c>
       <c r="D597" t="s">
-        <v>1731</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="s">
-        <v>1636</v>
+        <v>1735</v>
       </c>
       <c r="B598" t="s">
-        <v>1732</v>
+        <v>1736</v>
       </c>
       <c r="C598" t="s">
-        <v>1733</v>
+        <v>1737</v>
       </c>
       <c r="D598" t="s">
-        <v>1734</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="s">
-        <v>1636</v>
+        <v>1735</v>
       </c>
       <c r="B599" t="s">
-        <v>1735</v>
+        <v>1739</v>
       </c>
       <c r="C599" t="s">
-        <v>1736</v>
+        <v>1740</v>
       </c>
       <c r="D599" t="s">
-        <v>1737</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="s">
-        <v>1636</v>
+        <v>1735</v>
       </c>
       <c r="B600" t="s">
-        <v>1738</v>
+        <v>1742</v>
       </c>
       <c r="C600" t="s">
-        <v>1739</v>
+        <v>1743</v>
       </c>
       <c r="D600" t="s">
-        <v>1740</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="s">
-        <v>1636</v>
+        <v>1735</v>
       </c>
       <c r="B601" t="s">
-        <v>1741</v>
+        <v>1745</v>
       </c>
       <c r="C601" t="s">
-        <v>1742</v>
+        <v>1746</v>
       </c>
       <c r="D601" t="s">
-        <v>1743</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="s">
-        <v>1636</v>
+        <v>1735</v>
       </c>
       <c r="B602" t="s">
-        <v>1744</v>
+        <v>1748</v>
       </c>
       <c r="C602" t="s">
-        <v>1745</v>
+        <v>445</v>
       </c>
       <c r="D602" t="s">
-        <v>1746</v>
+        <v>446</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="s">
-        <v>1636</v>
+        <v>1735</v>
       </c>
       <c r="B603" t="s">
-        <v>1747</v>
+        <v>1749</v>
       </c>
       <c r="C603" t="s">
-        <v>1748</v>
+        <v>1735</v>
       </c>
       <c r="D603" t="s">
-        <v>1746</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="s">
-        <v>1636</v>
+        <v>1697</v>
       </c>
       <c r="B604" t="s">
-        <v>1749</v>
+        <v>1751</v>
       </c>
       <c r="C604" t="s">
-        <v>1750</v>
+        <v>1752</v>
       </c>
       <c r="D604" t="s">
-        <v>1751</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="s">
-        <v>1636</v>
+        <v>1697</v>
       </c>
       <c r="B605" t="s">
-        <v>1752</v>
+        <v>1754</v>
       </c>
       <c r="C605" t="s">
-        <v>373</v>
+        <v>1755</v>
       </c>
       <c r="D605" t="s">
-        <v>374</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="s">
-        <v>1636</v>
+        <v>1697</v>
       </c>
       <c r="B606" t="s">
-        <v>1753</v>
+        <v>1757</v>
       </c>
       <c r="C606" t="s">
-        <v>1754</v>
+        <v>1758</v>
       </c>
       <c r="D606" t="s">
-        <v>377</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="s">
-        <v>1636</v>
+        <v>1697</v>
       </c>
       <c r="B607" t="s">
-        <v>1755</v>
+        <v>1760</v>
       </c>
       <c r="C607" t="s">
-        <v>1756</v>
+        <v>1761</v>
       </c>
       <c r="D607" t="s">
-        <v>1757</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="s">
-        <v>1636</v>
+        <v>1697</v>
       </c>
       <c r="B608" t="s">
-        <v>1758</v>
+        <v>1763</v>
       </c>
       <c r="C608" t="s">
-        <v>1759</v>
+        <v>1764</v>
       </c>
       <c r="D608" t="s">
-        <v>328</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="s">
-        <v>1636</v>
+        <v>1697</v>
       </c>
       <c r="B609" t="s">
-        <v>1760</v>
+        <v>1766</v>
       </c>
       <c r="C609" t="s">
-        <v>1636</v>
+        <v>1767</v>
       </c>
       <c r="D609" t="s">
-        <v>1637</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="s">
-        <v>1636</v>
+        <v>1697</v>
       </c>
       <c r="B610" t="s">
-        <v>1761</v>
+        <v>1769</v>
       </c>
       <c r="C610" t="s">
-        <v>1762</v>
+        <v>1770</v>
       </c>
       <c r="D610" t="s">
-        <v>1763</v>
+        <v>890</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="s">
-        <v>1636</v>
+        <v>1697</v>
       </c>
       <c r="B611" t="s">
-        <v>1764</v>
+        <v>1771</v>
       </c>
       <c r="C611" t="s">
-        <v>1765</v>
+        <v>1772</v>
       </c>
       <c r="D611" t="s">
-        <v>1766</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="s">
-        <v>1636</v>
+        <v>1697</v>
       </c>
       <c r="B612" t="s">
-        <v>1767</v>
+        <v>1774</v>
       </c>
       <c r="C612" t="s">
-        <v>1616</v>
+        <v>1775</v>
       </c>
       <c r="D612" t="s">
-        <v>1617</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="s">
-        <v>1636</v>
+        <v>1697</v>
       </c>
       <c r="B613" t="s">
-        <v>1768</v>
+        <v>1777</v>
       </c>
       <c r="C613" t="s">
-        <v>1385</v>
+        <v>1778</v>
       </c>
       <c r="D613" t="s">
-        <v>1386</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="s">
-        <v>1636</v>
+        <v>1697</v>
       </c>
       <c r="B614" t="s">
-        <v>1769</v>
+        <v>1780</v>
       </c>
       <c r="C614" t="s">
-        <v>1770</v>
+        <v>1781</v>
       </c>
       <c r="D614" t="s">
-        <v>1771</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="s">
-        <v>1772</v>
+        <v>1697</v>
       </c>
       <c r="B615" t="s">
-        <v>1773</v>
+        <v>1783</v>
       </c>
       <c r="C615" t="s">
-        <v>1774</v>
+        <v>1784</v>
       </c>
       <c r="D615" t="s">
-        <v>1775</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="s">
-        <v>1772</v>
+        <v>1697</v>
       </c>
       <c r="B616" t="s">
-        <v>1776</v>
+        <v>1786</v>
       </c>
       <c r="C616" t="s">
-        <v>1777</v>
+        <v>370</v>
       </c>
       <c r="D616" t="s">
-        <v>1778</v>
+        <v>371</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="s">
-        <v>1772</v>
+        <v>1697</v>
       </c>
       <c r="B617" t="s">
-        <v>1779</v>
+        <v>1787</v>
       </c>
       <c r="C617" t="s">
-        <v>1772</v>
+        <v>1788</v>
       </c>
       <c r="D617" t="s">
-        <v>1780</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="s">
-        <v>1657</v>
+        <v>1697</v>
       </c>
       <c r="B618" t="s">
-        <v>1781</v>
+        <v>1790</v>
       </c>
       <c r="C618" t="s">
-        <v>1782</v>
+        <v>1791</v>
       </c>
       <c r="D618" t="s">
-        <v>1783</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="s">
-        <v>1657</v>
+        <v>1697</v>
       </c>
       <c r="B619" t="s">
-        <v>1784</v>
+        <v>1793</v>
       </c>
       <c r="C619" t="s">
-        <v>1785</v>
+        <v>1794</v>
       </c>
       <c r="D619" t="s">
-        <v>1786</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="s">
-        <v>1657</v>
+        <v>1697</v>
       </c>
       <c r="B620" t="s">
-        <v>1787</v>
+        <v>1796</v>
       </c>
       <c r="C620" t="s">
-        <v>1709</v>
+        <v>1797</v>
       </c>
       <c r="D620" t="s">
-        <v>1788</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="s">
-        <v>1657</v>
+        <v>1697</v>
       </c>
       <c r="B621" t="s">
-        <v>1789</v>
+        <v>1799</v>
       </c>
       <c r="C621" t="s">
-        <v>1790</v>
+        <v>1800</v>
       </c>
       <c r="D621" t="s">
-        <v>1791</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="s">
-        <v>1657</v>
+        <v>1697</v>
       </c>
       <c r="B622" t="s">
-        <v>1792</v>
+        <v>1802</v>
       </c>
       <c r="C622" t="s">
-        <v>1793</v>
+        <v>1803</v>
       </c>
       <c r="D622" t="s">
-        <v>1794</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="s">
-        <v>1657</v>
+        <v>1697</v>
       </c>
       <c r="B623" t="s">
-        <v>1795</v>
+        <v>1805</v>
       </c>
       <c r="C623" t="s">
-        <v>1796</v>
+        <v>1806</v>
       </c>
       <c r="D623" t="s">
-        <v>1797</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="s">
-        <v>1657</v>
+        <v>1697</v>
       </c>
       <c r="B624" t="s">
-        <v>1798</v>
+        <v>1808</v>
       </c>
       <c r="C624" t="s">
-        <v>1799</v>
+        <v>1809</v>
       </c>
       <c r="D624" t="s">
-        <v>1800</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="s">
-        <v>1657</v>
+        <v>1697</v>
       </c>
       <c r="B625" t="s">
-        <v>1801</v>
+        <v>1810</v>
       </c>
       <c r="C625" t="s">
-        <v>1802</v>
+        <v>1811</v>
       </c>
       <c r="D625" t="s">
-        <v>1803</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="s">
-        <v>1657</v>
+        <v>1697</v>
       </c>
       <c r="B626" t="s">
-        <v>1804</v>
+        <v>1813</v>
       </c>
       <c r="C626" t="s">
-        <v>1805</v>
+        <v>373</v>
       </c>
       <c r="D626" t="s">
-        <v>1806</v>
+        <v>374</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="s">
-        <v>1657</v>
+        <v>1697</v>
       </c>
       <c r="B627" t="s">
-        <v>1807</v>
+        <v>1814</v>
       </c>
       <c r="C627" t="s">
-        <v>1808</v>
+        <v>1815</v>
       </c>
       <c r="D627" t="s">
-        <v>1809</v>
+        <v>377</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="s">
-        <v>1657</v>
+        <v>1697</v>
       </c>
       <c r="B628" t="s">
-        <v>1810</v>
+        <v>1816</v>
       </c>
       <c r="C628" t="s">
-        <v>1811</v>
+        <v>1817</v>
       </c>
       <c r="D628" t="s">
-        <v>1812</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="s">
-        <v>1657</v>
+        <v>1697</v>
       </c>
       <c r="B629" t="s">
-        <v>1813</v>
+        <v>1819</v>
       </c>
       <c r="C629" t="s">
-        <v>1814</v>
+        <v>1820</v>
       </c>
       <c r="D629" t="s">
-        <v>1815</v>
+        <v>328</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="s">
-        <v>1657</v>
+        <v>1697</v>
       </c>
       <c r="B630" t="s">
-        <v>1816</v>
+        <v>1821</v>
       </c>
       <c r="C630" t="s">
-        <v>1817</v>
+        <v>1697</v>
       </c>
       <c r="D630" t="s">
-        <v>1818</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="s">
-        <v>1657</v>
+        <v>1697</v>
       </c>
       <c r="B631" t="s">
-        <v>1819</v>
+        <v>1822</v>
       </c>
       <c r="C631" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="D631" t="s">
-        <v>1821</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="s">
-        <v>1657</v>
+        <v>1697</v>
       </c>
       <c r="B632" t="s">
-        <v>1822</v>
+        <v>1825</v>
       </c>
       <c r="C632" t="s">
-        <v>1823</v>
+        <v>1826</v>
       </c>
       <c r="D632" t="s">
-        <v>1824</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="s">
-        <v>1657</v>
+        <v>1697</v>
       </c>
       <c r="B633" t="s">
-        <v>1825</v>
+        <v>1828</v>
       </c>
       <c r="C633" t="s">
-        <v>1826</v>
+        <v>1665</v>
       </c>
       <c r="D633" t="s">
-        <v>1827</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="s">
-        <v>1657</v>
+        <v>1697</v>
       </c>
       <c r="B634" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="C634" t="s">
-        <v>1829</v>
+        <v>1385</v>
       </c>
       <c r="D634" t="s">
-        <v>1830</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="s">
-        <v>1657</v>
+        <v>1697</v>
       </c>
       <c r="B635" t="s">
+        <v>1830</v>
+      </c>
+      <c r="C635" t="s">
         <v>1831</v>
       </c>
-      <c r="C635" t="s">
+      <c r="D635" t="s">
         <v>1832</v>
-      </c>
-      <c r="D635" t="s">
-        <v>1833</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="s">
-        <v>1657</v>
+        <v>1833</v>
       </c>
       <c r="B636" t="s">
         <v>1834</v>
@@ -17030,7 +17213,7 @@
     </row>
     <row r="637">
       <c r="A637" t="s">
-        <v>1657</v>
+        <v>1833</v>
       </c>
       <c r="B637" t="s">
         <v>1837</v>
@@ -17044,41 +17227,41 @@
     </row>
     <row r="638">
       <c r="A638" t="s">
-        <v>1657</v>
+        <v>1833</v>
       </c>
       <c r="B638" t="s">
         <v>1840</v>
       </c>
       <c r="C638" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D638" t="s">
         <v>1841</v>
-      </c>
-      <c r="D638" t="s">
-        <v>1842</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B639" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C639" t="s">
         <v>1843</v>
       </c>
-      <c r="C639" t="s">
+      <c r="D639" t="s">
         <v>1844</v>
-      </c>
-      <c r="D639" t="s">
-        <v>1845</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B640" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C640" t="s">
         <v>1846</v>
-      </c>
-      <c r="C640" t="s">
-        <v>1709</v>
       </c>
       <c r="D640" t="s">
         <v>1847</v>
@@ -17086,2457 +17269,2457 @@
     </row>
     <row r="641">
       <c r="A641" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B641" t="s">
         <v>1848</v>
       </c>
       <c r="C641" t="s">
+        <v>1770</v>
+      </c>
+      <c r="D641" t="s">
         <v>1849</v>
-      </c>
-      <c r="D641" t="s">
-        <v>1850</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B642" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C642" t="s">
         <v>1851</v>
       </c>
-      <c r="C642" t="s">
+      <c r="D642" t="s">
         <v>1852</v>
-      </c>
-      <c r="D642" t="s">
-        <v>1853</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B643" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C643" t="s">
         <v>1854</v>
       </c>
-      <c r="C643" t="s">
+      <c r="D643" t="s">
         <v>1855</v>
-      </c>
-      <c r="D643" t="s">
-        <v>1856</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B644" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C644" t="s">
         <v>1857</v>
       </c>
-      <c r="C644" t="s">
+      <c r="D644" t="s">
         <v>1858</v>
-      </c>
-      <c r="D644" t="s">
-        <v>1859</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B645" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C645" t="s">
         <v>1860</v>
       </c>
-      <c r="C645" t="s">
+      <c r="D645" t="s">
         <v>1861</v>
-      </c>
-      <c r="D645" t="s">
-        <v>1862</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B646" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C646" t="s">
         <v>1863</v>
       </c>
-      <c r="C646" t="s">
-        <v>6</v>
-      </c>
       <c r="D646" t="s">
-        <v>528</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B647" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="C647" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="D647" t="s">
-        <v>385</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B648" t="s">
-        <v>1866</v>
+        <v>1868</v>
       </c>
       <c r="C648" t="s">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="D648" t="s">
-        <v>1868</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B649" t="s">
-        <v>1869</v>
+        <v>1871</v>
       </c>
       <c r="C649" t="s">
-        <v>1870</v>
+        <v>1872</v>
       </c>
       <c r="D649" t="s">
-        <v>1868</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B650" t="s">
-        <v>1871</v>
+        <v>1874</v>
       </c>
       <c r="C650" t="s">
-        <v>1872</v>
+        <v>1875</v>
       </c>
       <c r="D650" t="s">
-        <v>1873</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B651" t="s">
-        <v>1874</v>
+        <v>1877</v>
       </c>
       <c r="C651" t="s">
-        <v>1875</v>
+        <v>1878</v>
       </c>
       <c r="D651" t="s">
-        <v>1658</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B652" t="s">
-        <v>1876</v>
+        <v>1880</v>
       </c>
       <c r="C652" t="s">
-        <v>1877</v>
+        <v>1881</v>
       </c>
       <c r="D652" t="s">
-        <v>343</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B653" t="s">
-        <v>1878</v>
+        <v>1883</v>
       </c>
       <c r="C653" t="s">
-        <v>1879</v>
+        <v>1884</v>
       </c>
       <c r="D653" t="s">
-        <v>1880</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B654" t="s">
-        <v>1881</v>
+        <v>1886</v>
       </c>
       <c r="C654" t="s">
-        <v>279</v>
+        <v>1887</v>
       </c>
       <c r="D654" t="s">
-        <v>280</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B655" t="s">
-        <v>1882</v>
+        <v>1889</v>
       </c>
       <c r="C655" t="s">
-        <v>1883</v>
+        <v>1890</v>
       </c>
       <c r="D655" t="s">
-        <v>1884</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B656" t="s">
-        <v>1885</v>
+        <v>1892</v>
       </c>
       <c r="C656" t="s">
-        <v>1886</v>
+        <v>1893</v>
       </c>
       <c r="D656" t="s">
-        <v>1887</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B657" t="s">
-        <v>1888</v>
+        <v>1895</v>
       </c>
       <c r="C657" t="s">
-        <v>1889</v>
+        <v>1896</v>
       </c>
       <c r="D657" t="s">
-        <v>1890</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B658" t="s">
-        <v>1891</v>
+        <v>1898</v>
       </c>
       <c r="C658" t="s">
-        <v>1892</v>
+        <v>1899</v>
       </c>
       <c r="D658" t="s">
-        <v>1893</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B659" t="s">
-        <v>1894</v>
+        <v>1901</v>
       </c>
       <c r="C659" t="s">
-        <v>1895</v>
+        <v>1902</v>
       </c>
       <c r="D659" t="s">
-        <v>1896</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B660" t="s">
-        <v>1897</v>
+        <v>1904</v>
       </c>
       <c r="C660" t="s">
-        <v>1628</v>
+        <v>1905</v>
       </c>
       <c r="D660" t="s">
-        <v>1629</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B661" t="s">
-        <v>1898</v>
+        <v>1907</v>
       </c>
       <c r="C661" t="s">
-        <v>1899</v>
+        <v>1770</v>
       </c>
       <c r="D661" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B662" t="s">
-        <v>1901</v>
+        <v>1909</v>
       </c>
       <c r="C662" t="s">
-        <v>1902</v>
+        <v>1910</v>
       </c>
       <c r="D662" t="s">
-        <v>1903</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B663" t="s">
-        <v>1904</v>
+        <v>1912</v>
       </c>
       <c r="C663" t="s">
-        <v>1905</v>
+        <v>1913</v>
       </c>
       <c r="D663" t="s">
-        <v>1906</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="s">
-        <v>1657</v>
+        <v>1718</v>
       </c>
       <c r="B664" t="s">
-        <v>1907</v>
+        <v>1915</v>
       </c>
       <c r="C664" t="s">
-        <v>1908</v>
+        <v>1916</v>
       </c>
       <c r="D664" t="s">
-        <v>920</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="s">
-        <v>1877</v>
+        <v>1718</v>
       </c>
       <c r="B665" t="s">
-        <v>1909</v>
+        <v>1918</v>
       </c>
       <c r="C665" t="s">
-        <v>1910</v>
+        <v>1919</v>
       </c>
       <c r="D665" t="s">
-        <v>1911</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="s">
-        <v>1877</v>
+        <v>1718</v>
       </c>
       <c r="B666" t="s">
-        <v>1912</v>
+        <v>1921</v>
       </c>
       <c r="C666" t="s">
-        <v>1913</v>
+        <v>1922</v>
       </c>
       <c r="D666" t="s">
-        <v>1914</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="s">
-        <v>1877</v>
+        <v>1718</v>
       </c>
       <c r="B667" t="s">
-        <v>1915</v>
+        <v>1924</v>
       </c>
       <c r="C667" t="s">
-        <v>1916</v>
+        <v>6</v>
       </c>
       <c r="D667" t="s">
-        <v>1917</v>
+        <v>528</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="s">
-        <v>1877</v>
+        <v>1718</v>
       </c>
       <c r="B668" t="s">
-        <v>1918</v>
+        <v>1925</v>
       </c>
       <c r="C668" t="s">
-        <v>405</v>
+        <v>1926</v>
       </c>
       <c r="D668" t="s">
-        <v>406</v>
+        <v>385</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="s">
-        <v>1877</v>
+        <v>1718</v>
       </c>
       <c r="B669" t="s">
-        <v>1919</v>
+        <v>1927</v>
       </c>
       <c r="C669" t="s">
-        <v>1920</v>
+        <v>1928</v>
       </c>
       <c r="D669" t="s">
-        <v>1751</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="s">
-        <v>1877</v>
+        <v>1718</v>
       </c>
       <c r="B670" t="s">
-        <v>1921</v>
+        <v>1930</v>
       </c>
       <c r="C670" t="s">
-        <v>1922</v>
+        <v>1931</v>
       </c>
       <c r="D670" t="s">
-        <v>1923</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="s">
-        <v>1596</v>
+        <v>1718</v>
       </c>
       <c r="B671" t="s">
-        <v>1924</v>
+        <v>1932</v>
       </c>
       <c r="C671" t="s">
-        <v>1925</v>
+        <v>1933</v>
       </c>
       <c r="D671" t="s">
-        <v>1926</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="s">
-        <v>1596</v>
+        <v>1718</v>
       </c>
       <c r="B672" t="s">
-        <v>1927</v>
+        <v>1935</v>
       </c>
       <c r="C672" t="s">
-        <v>455</v>
+        <v>1936</v>
       </c>
       <c r="D672" t="s">
-        <v>456</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="s">
-        <v>1596</v>
+        <v>1718</v>
       </c>
       <c r="B673" t="s">
-        <v>1928</v>
+        <v>1937</v>
       </c>
       <c r="C673" t="s">
-        <v>1929</v>
+        <v>1938</v>
       </c>
       <c r="D673" t="s">
-        <v>1930</v>
+        <v>343</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="s">
-        <v>1596</v>
+        <v>1718</v>
       </c>
       <c r="B674" t="s">
-        <v>1931</v>
+        <v>1939</v>
       </c>
       <c r="C674" t="s">
-        <v>1932</v>
+        <v>1940</v>
       </c>
       <c r="D674" t="s">
-        <v>1933</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="s">
-        <v>1596</v>
+        <v>1718</v>
       </c>
       <c r="B675" t="s">
-        <v>1934</v>
+        <v>1942</v>
       </c>
       <c r="C675" t="s">
-        <v>1935</v>
+        <v>279</v>
       </c>
       <c r="D675" t="s">
-        <v>1936</v>
+        <v>280</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="s">
-        <v>1596</v>
+        <v>1718</v>
       </c>
       <c r="B676" t="s">
-        <v>1937</v>
+        <v>1943</v>
       </c>
       <c r="C676" t="s">
-        <v>482</v>
+        <v>1944</v>
       </c>
       <c r="D676" t="s">
-        <v>483</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="s">
-        <v>1596</v>
+        <v>1718</v>
       </c>
       <c r="B677" t="s">
-        <v>1938</v>
+        <v>1946</v>
       </c>
       <c r="C677" t="s">
-        <v>322</v>
+        <v>1947</v>
       </c>
       <c r="D677" t="s">
-        <v>179</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="s">
-        <v>1596</v>
+        <v>1718</v>
       </c>
       <c r="B678" t="s">
-        <v>1939</v>
+        <v>1949</v>
       </c>
       <c r="C678" t="s">
-        <v>1940</v>
+        <v>1950</v>
       </c>
       <c r="D678" t="s">
-        <v>1941</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="s">
-        <v>1596</v>
+        <v>1718</v>
       </c>
       <c r="B679" t="s">
-        <v>1942</v>
+        <v>1952</v>
       </c>
       <c r="C679" t="s">
-        <v>1943</v>
+        <v>1953</v>
       </c>
       <c r="D679" t="s">
-        <v>1944</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="s">
-        <v>1596</v>
+        <v>1718</v>
       </c>
       <c r="B680" t="s">
-        <v>1945</v>
+        <v>1955</v>
       </c>
       <c r="C680" t="s">
-        <v>1946</v>
+        <v>1956</v>
       </c>
       <c r="D680" t="s">
-        <v>1947</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="s">
-        <v>1596</v>
+        <v>1718</v>
       </c>
       <c r="B681" t="s">
-        <v>1948</v>
+        <v>1958</v>
       </c>
       <c r="C681" t="s">
-        <v>1949</v>
+        <v>1689</v>
       </c>
       <c r="D681" t="s">
-        <v>1950</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="s">
-        <v>1596</v>
+        <v>1718</v>
       </c>
       <c r="B682" t="s">
-        <v>1951</v>
+        <v>1959</v>
       </c>
       <c r="C682" t="s">
-        <v>1952</v>
+        <v>1960</v>
       </c>
       <c r="D682" t="s">
-        <v>1953</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="s">
-        <v>1596</v>
+        <v>1718</v>
       </c>
       <c r="B683" t="s">
-        <v>1954</v>
+        <v>1962</v>
       </c>
       <c r="C683" t="s">
-        <v>1955</v>
+        <v>1963</v>
       </c>
       <c r="D683" t="s">
-        <v>1956</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="s">
-        <v>1596</v>
+        <v>1718</v>
       </c>
       <c r="B684" t="s">
-        <v>1957</v>
+        <v>1965</v>
       </c>
       <c r="C684" t="s">
-        <v>1958</v>
+        <v>1966</v>
       </c>
       <c r="D684" t="s">
-        <v>1959</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="s">
-        <v>1596</v>
+        <v>1718</v>
       </c>
       <c r="B685" t="s">
-        <v>1960</v>
+        <v>1968</v>
       </c>
       <c r="C685" t="s">
-        <v>1961</v>
+        <v>1969</v>
       </c>
       <c r="D685" t="s">
-        <v>1962</v>
+        <v>920</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="s">
-        <v>1596</v>
+        <v>1938</v>
       </c>
       <c r="B686" t="s">
-        <v>1963</v>
+        <v>1970</v>
       </c>
       <c r="C686" t="s">
-        <v>1964</v>
+        <v>1971</v>
       </c>
       <c r="D686" t="s">
-        <v>474</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="s">
-        <v>1596</v>
+        <v>1938</v>
       </c>
       <c r="B687" t="s">
-        <v>1965</v>
+        <v>1973</v>
       </c>
       <c r="C687" t="s">
-        <v>285</v>
+        <v>1974</v>
       </c>
       <c r="D687" t="s">
-        <v>1966</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="s">
-        <v>1596</v>
+        <v>1938</v>
       </c>
       <c r="B688" t="s">
-        <v>1967</v>
+        <v>1976</v>
       </c>
       <c r="C688" t="s">
-        <v>1968</v>
+        <v>1977</v>
       </c>
       <c r="D688" t="s">
-        <v>1969</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="s">
-        <v>1596</v>
+        <v>1938</v>
       </c>
       <c r="B689" t="s">
-        <v>1970</v>
+        <v>1979</v>
       </c>
       <c r="C689" t="s">
-        <v>1971</v>
+        <v>405</v>
       </c>
       <c r="D689" t="s">
-        <v>1972</v>
+        <v>406</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="s">
-        <v>1596</v>
+        <v>1938</v>
       </c>
       <c r="B690" t="s">
-        <v>1973</v>
+        <v>1980</v>
       </c>
       <c r="C690" t="s">
-        <v>1974</v>
+        <v>1981</v>
       </c>
       <c r="D690" t="s">
-        <v>1975</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="s">
-        <v>1596</v>
+        <v>1938</v>
       </c>
       <c r="B691" t="s">
-        <v>1976</v>
+        <v>1982</v>
       </c>
       <c r="C691" t="s">
-        <v>1977</v>
+        <v>1983</v>
       </c>
       <c r="D691" t="s">
-        <v>1978</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="s">
-        <v>1596</v>
+        <v>1627</v>
       </c>
       <c r="B692" t="s">
-        <v>1979</v>
+        <v>1985</v>
       </c>
       <c r="C692" t="s">
-        <v>6</v>
+        <v>1986</v>
       </c>
       <c r="D692" t="s">
-        <v>528</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="s">
-        <v>1596</v>
+        <v>1627</v>
       </c>
       <c r="B693" t="s">
-        <v>1980</v>
+        <v>1988</v>
       </c>
       <c r="C693" t="s">
-        <v>1981</v>
+        <v>455</v>
       </c>
       <c r="D693" t="s">
-        <v>1982</v>
+        <v>456</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="s">
-        <v>1596</v>
+        <v>1627</v>
       </c>
       <c r="B694" t="s">
-        <v>1983</v>
+        <v>1989</v>
       </c>
       <c r="C694" t="s">
-        <v>1984</v>
+        <v>1990</v>
       </c>
       <c r="D694" t="s">
-        <v>1985</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="s">
-        <v>1596</v>
+        <v>1627</v>
       </c>
       <c r="B695" t="s">
-        <v>1986</v>
+        <v>1992</v>
       </c>
       <c r="C695" t="s">
-        <v>1987</v>
+        <v>1993</v>
       </c>
       <c r="D695" t="s">
-        <v>1988</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="s">
-        <v>1596</v>
+        <v>1627</v>
       </c>
       <c r="B696" t="s">
-        <v>1989</v>
+        <v>1995</v>
       </c>
       <c r="C696" t="s">
-        <v>1990</v>
+        <v>1996</v>
       </c>
       <c r="D696" t="s">
-        <v>1991</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="s">
-        <v>1596</v>
+        <v>1627</v>
       </c>
       <c r="B697" t="s">
-        <v>1992</v>
+        <v>1998</v>
       </c>
       <c r="C697" t="s">
-        <v>1993</v>
+        <v>482</v>
       </c>
       <c r="D697" t="s">
-        <v>1994</v>
+        <v>483</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="s">
-        <v>1663</v>
+        <v>1627</v>
       </c>
       <c r="B698" t="s">
-        <v>1995</v>
+        <v>1999</v>
       </c>
       <c r="C698" t="s">
-        <v>1996</v>
+        <v>322</v>
       </c>
       <c r="D698" t="s">
-        <v>1997</v>
+        <v>179</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="s">
-        <v>1663</v>
+        <v>1627</v>
       </c>
       <c r="B699" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="C699" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="D699" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="s">
-        <v>1663</v>
+        <v>1627</v>
       </c>
       <c r="B700" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="C700" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="D700" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="s">
-        <v>1663</v>
+        <v>1627</v>
       </c>
       <c r="B701" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="C701" t="s">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="D701" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="s">
-        <v>1663</v>
+        <v>1627</v>
       </c>
       <c r="B702" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="C702" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="D702" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="s">
-        <v>1663</v>
+        <v>1627</v>
       </c>
       <c r="B703" t="s">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="C703" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="D703" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="s">
-        <v>1663</v>
+        <v>1627</v>
       </c>
       <c r="B704" t="s">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="C704" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="D704" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="s">
-        <v>1663</v>
+        <v>1627</v>
       </c>
       <c r="B705" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C705" t="s">
-        <v>1745</v>
+        <v>2019</v>
       </c>
       <c r="D705" t="s">
-        <v>2017</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="s">
-        <v>1663</v>
+        <v>1627</v>
       </c>
       <c r="B706" t="s">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C706" t="s">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="D706" t="s">
-        <v>2020</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="s">
-        <v>1663</v>
+        <v>1627</v>
       </c>
       <c r="B707" t="s">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="C707" t="s">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D707" t="s">
-        <v>2023</v>
+        <v>474</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="s">
-        <v>1663</v>
+        <v>1627</v>
       </c>
       <c r="B708" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C708" t="s">
-        <v>2025</v>
+        <v>285</v>
       </c>
       <c r="D708" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="s">
-        <v>1663</v>
+        <v>1627</v>
       </c>
       <c r="B709" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C709" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="D709" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="s">
-        <v>1663</v>
+        <v>1627</v>
       </c>
       <c r="B710" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C710" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="D710" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="s">
-        <v>1663</v>
+        <v>1627</v>
       </c>
       <c r="B711" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="C711" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="D711" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="s">
-        <v>1663</v>
+        <v>1627</v>
       </c>
       <c r="B712" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="C712" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="D712" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="s">
-        <v>1663</v>
+        <v>1627</v>
       </c>
       <c r="B713" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="C713" t="s">
-        <v>370</v>
+        <v>6</v>
       </c>
       <c r="D713" t="s">
-        <v>371</v>
+        <v>528</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="s">
-        <v>1663</v>
+        <v>1627</v>
       </c>
       <c r="B714" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="C714" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="D714" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="s">
-        <v>1663</v>
+        <v>1627</v>
       </c>
       <c r="B715" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="C715" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="D715" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="s">
-        <v>1663</v>
+        <v>1627</v>
       </c>
       <c r="B716" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="C716" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="D716" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="s">
-        <v>1663</v>
+        <v>1627</v>
       </c>
       <c r="B717" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="C717" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="D717" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="s">
-        <v>1663</v>
+        <v>1627</v>
       </c>
       <c r="B718" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="C718" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="D718" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B719" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="C719" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="D719" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B720" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="C720" t="s">
-        <v>21</v>
+        <v>2060</v>
       </c>
       <c r="D720" t="s">
-        <v>2059</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B721" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="C721" t="s">
-        <v>2061</v>
+        <v>2063</v>
       </c>
       <c r="D721" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B722" t="s">
-        <v>2063</v>
+        <v>2065</v>
       </c>
       <c r="C722" t="s">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="D722" t="s">
-        <v>2065</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B723" t="s">
-        <v>2066</v>
+        <v>2068</v>
       </c>
       <c r="C723" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="D723" t="s">
-        <v>2068</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B724" t="s">
-        <v>2069</v>
+        <v>2071</v>
       </c>
       <c r="C724" t="s">
-        <v>2070</v>
+        <v>2072</v>
       </c>
       <c r="D724" t="s">
-        <v>2029</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B725" t="s">
-        <v>2071</v>
+        <v>2074</v>
       </c>
       <c r="C725" t="s">
-        <v>2072</v>
+        <v>2075</v>
       </c>
       <c r="D725" t="s">
-        <v>2073</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B726" t="s">
-        <v>2074</v>
+        <v>2077</v>
       </c>
       <c r="C726" t="s">
-        <v>2075</v>
+        <v>1806</v>
       </c>
       <c r="D726" t="s">
-        <v>2076</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B727" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="C727" t="s">
-        <v>2078</v>
+        <v>2080</v>
       </c>
       <c r="D727" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B728" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="C728" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="D728" t="s">
-        <v>2082</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B729" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="C729" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="D729" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B730" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="C730" t="s">
-        <v>1208</v>
+        <v>2089</v>
       </c>
       <c r="D730" t="s">
-        <v>2087</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B731" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="C731" t="s">
-        <v>2089</v>
+        <v>2092</v>
       </c>
       <c r="D731" t="s">
-        <v>2090</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B732" t="s">
-        <v>2091</v>
+        <v>2094</v>
       </c>
       <c r="C732" t="s">
-        <v>381</v>
+        <v>2095</v>
       </c>
       <c r="D732" t="s">
-        <v>2092</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B733" t="s">
-        <v>2093</v>
+        <v>2097</v>
       </c>
       <c r="C733" t="s">
-        <v>2094</v>
+        <v>2098</v>
       </c>
       <c r="D733" t="s">
-        <v>2095</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B734" t="s">
-        <v>2096</v>
+        <v>2100</v>
       </c>
       <c r="C734" t="s">
-        <v>2097</v>
+        <v>370</v>
       </c>
       <c r="D734" t="s">
-        <v>2098</v>
+        <v>371</v>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B735" t="s">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="C735" t="s">
-        <v>2100</v>
+        <v>2102</v>
       </c>
       <c r="D735" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B736" t="s">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="C736" t="s">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="D736" t="s">
-        <v>2104</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B737" t="s">
-        <v>2105</v>
+        <v>2107</v>
       </c>
       <c r="C737" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="D737" t="s">
-        <v>2107</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B738" t="s">
-        <v>2108</v>
+        <v>2110</v>
       </c>
       <c r="C738" t="s">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="D738" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B739" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="C739" t="s">
-        <v>376</v>
+        <v>2114</v>
       </c>
       <c r="D739" t="s">
-        <v>2112</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B740" t="s">
-        <v>2113</v>
+        <v>2116</v>
       </c>
       <c r="C740" t="s">
-        <v>393</v>
+        <v>2117</v>
       </c>
       <c r="D740" t="s">
-        <v>394</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B741" t="s">
-        <v>2114</v>
+        <v>2119</v>
       </c>
       <c r="C741" t="s">
-        <v>2115</v>
+        <v>21</v>
       </c>
       <c r="D741" t="s">
-        <v>2112</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B742" t="s">
-        <v>2116</v>
+        <v>2121</v>
       </c>
       <c r="C742" t="s">
-        <v>2117</v>
+        <v>2122</v>
       </c>
       <c r="D742" t="s">
-        <v>2118</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B743" t="s">
-        <v>2119</v>
+        <v>2124</v>
       </c>
       <c r="C743" t="s">
-        <v>2120</v>
+        <v>2125</v>
       </c>
       <c r="D743" t="s">
-        <v>2121</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B744" t="s">
-        <v>2122</v>
+        <v>2127</v>
       </c>
       <c r="C744" t="s">
-        <v>2123</v>
+        <v>2128</v>
       </c>
       <c r="D744" t="s">
-        <v>2124</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B745" t="s">
-        <v>2125</v>
+        <v>2130</v>
       </c>
       <c r="C745" t="s">
-        <v>2126</v>
+        <v>2131</v>
       </c>
       <c r="D745" t="s">
-        <v>2127</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B746" t="s">
-        <v>2128</v>
+        <v>2132</v>
       </c>
       <c r="C746" t="s">
-        <v>2129</v>
+        <v>2133</v>
       </c>
       <c r="D746" t="s">
-        <v>2130</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B747" t="s">
-        <v>2131</v>
+        <v>2135</v>
       </c>
       <c r="C747" t="s">
-        <v>2132</v>
+        <v>2136</v>
       </c>
       <c r="D747" t="s">
-        <v>2133</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B748" t="s">
-        <v>2134</v>
+        <v>2138</v>
       </c>
       <c r="C748" t="s">
-        <v>2135</v>
+        <v>2139</v>
       </c>
       <c r="D748" t="s">
-        <v>2065</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B749" t="s">
-        <v>2136</v>
+        <v>2141</v>
       </c>
       <c r="C749" t="s">
-        <v>2137</v>
+        <v>2142</v>
       </c>
       <c r="D749" t="s">
-        <v>2138</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B750" t="s">
-        <v>2139</v>
+        <v>2144</v>
       </c>
       <c r="C750" t="s">
-        <v>2140</v>
+        <v>2145</v>
       </c>
       <c r="D750" t="s">
-        <v>1617</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B751" t="s">
-        <v>2141</v>
+        <v>2147</v>
       </c>
       <c r="C751" t="s">
-        <v>2142</v>
+        <v>1208</v>
       </c>
       <c r="D751" t="s">
-        <v>2143</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B752" t="s">
-        <v>2144</v>
+        <v>2149</v>
       </c>
       <c r="C752" t="s">
-        <v>2145</v>
+        <v>2150</v>
       </c>
       <c r="D752" t="s">
-        <v>2146</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B753" t="s">
-        <v>2147</v>
+        <v>2152</v>
       </c>
       <c r="C753" t="s">
-        <v>2148</v>
+        <v>381</v>
       </c>
       <c r="D753" t="s">
-        <v>2149</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B754" t="s">
-        <v>2150</v>
+        <v>2154</v>
       </c>
       <c r="C754" t="s">
-        <v>2151</v>
+        <v>2155</v>
       </c>
       <c r="D754" t="s">
-        <v>1412</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B755" t="s">
-        <v>2152</v>
+        <v>2157</v>
       </c>
       <c r="C755" t="s">
-        <v>2153</v>
+        <v>2158</v>
       </c>
       <c r="D755" t="s">
-        <v>2154</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B756" t="s">
-        <v>2155</v>
+        <v>2160</v>
       </c>
       <c r="C756" t="s">
-        <v>1674</v>
+        <v>2161</v>
       </c>
       <c r="D756" t="s">
-        <v>1689</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B757" t="s">
-        <v>2156</v>
+        <v>2163</v>
       </c>
       <c r="C757" t="s">
-        <v>48</v>
+        <v>2164</v>
       </c>
       <c r="D757" t="s">
-        <v>49</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B758" t="s">
-        <v>2157</v>
+        <v>2166</v>
       </c>
       <c r="C758" t="s">
-        <v>2158</v>
+        <v>2167</v>
       </c>
       <c r="D758" t="s">
-        <v>2159</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B759" t="s">
-        <v>2160</v>
+        <v>2169</v>
       </c>
       <c r="C759" t="s">
-        <v>2161</v>
+        <v>2170</v>
       </c>
       <c r="D759" t="s">
-        <v>2162</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B760" t="s">
-        <v>2163</v>
+        <v>2172</v>
       </c>
       <c r="C760" t="s">
-        <v>2164</v>
+        <v>376</v>
       </c>
       <c r="D760" t="s">
-        <v>2165</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B761" t="s">
-        <v>2166</v>
+        <v>2174</v>
       </c>
       <c r="C761" t="s">
-        <v>2167</v>
+        <v>393</v>
       </c>
       <c r="D761" t="s">
-        <v>2168</v>
+        <v>394</v>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B762" t="s">
-        <v>2169</v>
+        <v>2175</v>
       </c>
       <c r="C762" t="s">
-        <v>2170</v>
+        <v>2176</v>
       </c>
       <c r="D762" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B763" t="s">
-        <v>2172</v>
+        <v>2177</v>
       </c>
       <c r="C763" t="s">
-        <v>2173</v>
+        <v>2178</v>
       </c>
       <c r="D763" t="s">
-        <v>2174</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B764" t="s">
-        <v>2175</v>
+        <v>2180</v>
       </c>
       <c r="C764" t="s">
-        <v>2176</v>
+        <v>2181</v>
       </c>
       <c r="D764" t="s">
-        <v>2177</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B765" t="s">
-        <v>2178</v>
+        <v>2183</v>
       </c>
       <c r="C765" t="s">
-        <v>2179</v>
+        <v>2184</v>
       </c>
       <c r="D765" t="s">
-        <v>2180</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B766" t="s">
-        <v>2181</v>
+        <v>2186</v>
       </c>
       <c r="C766" t="s">
-        <v>2182</v>
+        <v>2187</v>
       </c>
       <c r="D766" t="s">
-        <v>2183</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B767" t="s">
-        <v>2184</v>
+        <v>2189</v>
       </c>
       <c r="C767" t="s">
-        <v>2185</v>
+        <v>2190</v>
       </c>
       <c r="D767" t="s">
-        <v>2186</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B768" t="s">
-        <v>2187</v>
+        <v>2192</v>
       </c>
       <c r="C768" t="s">
-        <v>2188</v>
+        <v>2193</v>
       </c>
       <c r="D768" t="s">
-        <v>2189</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B769" t="s">
-        <v>2190</v>
+        <v>2195</v>
       </c>
       <c r="C769" t="s">
-        <v>2191</v>
+        <v>2196</v>
       </c>
       <c r="D769" t="s">
-        <v>2192</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="s">
-        <v>1663</v>
+        <v>1724</v>
       </c>
       <c r="B770" t="s">
-        <v>2193</v>
+        <v>2197</v>
       </c>
       <c r="C770" t="s">
-        <v>2194</v>
+        <v>2198</v>
       </c>
       <c r="D770" t="s">
-        <v>2195</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="s">
-        <v>2196</v>
+        <v>1724</v>
       </c>
       <c r="B771" t="s">
-        <v>2197</v>
+        <v>2200</v>
       </c>
       <c r="C771" t="s">
-        <v>2198</v>
+        <v>2201</v>
       </c>
       <c r="D771" t="s">
-        <v>2199</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="s">
-        <v>2196</v>
+        <v>1724</v>
       </c>
       <c r="B772" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="C772" t="s">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="D772" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="s">
-        <v>2196</v>
+        <v>1724</v>
       </c>
       <c r="B773" t="s">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="C773" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="D773" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="s">
-        <v>2196</v>
+        <v>1724</v>
       </c>
       <c r="B774" t="s">
-        <v>2206</v>
+        <v>2208</v>
       </c>
       <c r="C774" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="D774" t="s">
-        <v>2208</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="s">
-        <v>1338</v>
+        <v>1724</v>
       </c>
       <c r="B775" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="C775" t="s">
-        <v>2210</v>
+        <v>2212</v>
       </c>
       <c r="D775" t="s">
-        <v>2211</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="s">
-        <v>1338</v>
+        <v>1724</v>
       </c>
       <c r="B776" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="C776" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="D776" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="s">
-        <v>1338</v>
+        <v>1724</v>
       </c>
       <c r="B777" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="C777" t="s">
-        <v>2216</v>
+        <v>1735</v>
       </c>
       <c r="D777" t="s">
-        <v>2217</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="s">
-        <v>1654</v>
+        <v>1724</v>
       </c>
       <c r="B778" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="C778" t="s">
-        <v>2219</v>
+        <v>48</v>
       </c>
       <c r="D778" t="s">
-        <v>2220</v>
+        <v>49</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="s">
-        <v>1654</v>
+        <v>1724</v>
       </c>
       <c r="B779" t="s">
-        <v>2221</v>
+        <v>2218</v>
       </c>
       <c r="C779" t="s">
-        <v>2222</v>
+        <v>2219</v>
       </c>
       <c r="D779" t="s">
-        <v>2223</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="s">
-        <v>1654</v>
+        <v>1724</v>
       </c>
       <c r="B780" t="s">
-        <v>2224</v>
+        <v>2221</v>
       </c>
       <c r="C780" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
       <c r="D780" t="s">
-        <v>2226</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="s">
-        <v>1654</v>
+        <v>1724</v>
       </c>
       <c r="B781" t="s">
-        <v>2227</v>
+        <v>2224</v>
       </c>
       <c r="C781" t="s">
-        <v>2228</v>
+        <v>2225</v>
       </c>
       <c r="D781" t="s">
-        <v>2229</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="s">
-        <v>1654</v>
+        <v>1724</v>
       </c>
       <c r="B782" t="s">
-        <v>2230</v>
+        <v>2227</v>
       </c>
       <c r="C782" t="s">
-        <v>2231</v>
+        <v>2228</v>
       </c>
       <c r="D782" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="s">
-        <v>1654</v>
+        <v>1724</v>
       </c>
       <c r="B783" t="s">
-        <v>2233</v>
+        <v>2230</v>
       </c>
       <c r="C783" t="s">
-        <v>2234</v>
+        <v>2231</v>
       </c>
       <c r="D783" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="s">
-        <v>1654</v>
+        <v>1724</v>
       </c>
       <c r="B784" t="s">
-        <v>2236</v>
+        <v>2233</v>
       </c>
       <c r="C784" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
       <c r="D784" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="s">
-        <v>1654</v>
+        <v>1724</v>
       </c>
       <c r="B785" t="s">
-        <v>2239</v>
+        <v>2236</v>
       </c>
       <c r="C785" t="s">
-        <v>2240</v>
+        <v>2237</v>
       </c>
       <c r="D785" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="s">
-        <v>1654</v>
+        <v>1724</v>
       </c>
       <c r="B786" t="s">
-        <v>2242</v>
+        <v>2239</v>
       </c>
       <c r="C786" t="s">
-        <v>2243</v>
+        <v>2240</v>
       </c>
       <c r="D786" t="s">
-        <v>2244</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="s">
-        <v>1654</v>
+        <v>1724</v>
       </c>
       <c r="B787" t="s">
-        <v>2245</v>
+        <v>2242</v>
       </c>
       <c r="C787" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
       <c r="D787" t="s">
-        <v>2247</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="s">
-        <v>1654</v>
+        <v>1724</v>
       </c>
       <c r="B788" t="s">
-        <v>2248</v>
+        <v>2245</v>
       </c>
       <c r="C788" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
       <c r="D788" t="s">
-        <v>2250</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="s">
-        <v>1654</v>
+        <v>1724</v>
       </c>
       <c r="B789" t="s">
-        <v>2251</v>
+        <v>2248</v>
       </c>
       <c r="C789" t="s">
-        <v>2252</v>
+        <v>2249</v>
       </c>
       <c r="D789" t="s">
-        <v>2253</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="s">
-        <v>1654</v>
+        <v>1724</v>
       </c>
       <c r="B790" t="s">
-        <v>2254</v>
+        <v>2251</v>
       </c>
       <c r="C790" t="s">
-        <v>2255</v>
+        <v>2252</v>
       </c>
       <c r="D790" t="s">
-        <v>2256</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="s">
-        <v>1654</v>
+        <v>1724</v>
       </c>
       <c r="B791" t="s">
-        <v>2257</v>
+        <v>2254</v>
       </c>
       <c r="C791" t="s">
-        <v>2258</v>
+        <v>2255</v>
       </c>
       <c r="D791" t="s">
-        <v>2259</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="s">
-        <v>1654</v>
+        <v>2257</v>
       </c>
       <c r="B792" t="s">
+        <v>2258</v>
+      </c>
+      <c r="C792" t="s">
+        <v>2259</v>
+      </c>
+      <c r="D792" t="s">
         <v>2260</v>
-      </c>
-      <c r="C792" t="s">
-        <v>2261</v>
-      </c>
-      <c r="D792" t="s">
-        <v>2262</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="s">
-        <v>1654</v>
+        <v>2257</v>
       </c>
       <c r="B793" t="s">
+        <v>2261</v>
+      </c>
+      <c r="C793" t="s">
+        <v>2262</v>
+      </c>
+      <c r="D793" t="s">
         <v>2263</v>
-      </c>
-      <c r="C793" t="s">
-        <v>2264</v>
-      </c>
-      <c r="D793" t="s">
-        <v>2265</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="s">
-        <v>1654</v>
+        <v>2257</v>
       </c>
       <c r="B794" t="s">
+        <v>2264</v>
+      </c>
+      <c r="C794" t="s">
+        <v>2265</v>
+      </c>
+      <c r="D794" t="s">
         <v>2266</v>
-      </c>
-      <c r="C794" t="s">
-        <v>2267</v>
-      </c>
-      <c r="D794" t="s">
-        <v>2268</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="s">
-        <v>1654</v>
+        <v>2257</v>
       </c>
       <c r="B795" t="s">
+        <v>2267</v>
+      </c>
+      <c r="C795" t="s">
+        <v>2268</v>
+      </c>
+      <c r="D795" t="s">
         <v>2269</v>
-      </c>
-      <c r="C795" t="s">
-        <v>2270</v>
-      </c>
-      <c r="D795" t="s">
-        <v>2271</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="s">
-        <v>1654</v>
+        <v>1338</v>
       </c>
       <c r="B796" t="s">
+        <v>2270</v>
+      </c>
+      <c r="C796" t="s">
+        <v>2271</v>
+      </c>
+      <c r="D796" t="s">
         <v>2272</v>
-      </c>
-      <c r="C796" t="s">
-        <v>2273</v>
-      </c>
-      <c r="D796" t="s">
-        <v>2274</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="s">
-        <v>1654</v>
+        <v>1338</v>
       </c>
       <c r="B797" t="s">
+        <v>2273</v>
+      </c>
+      <c r="C797" t="s">
+        <v>2274</v>
+      </c>
+      <c r="D797" t="s">
         <v>2275</v>
-      </c>
-      <c r="C797" t="s">
-        <v>2276</v>
-      </c>
-      <c r="D797" t="s">
-        <v>2277</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="s">
-        <v>1654</v>
+        <v>1338</v>
       </c>
       <c r="B798" t="s">
+        <v>2276</v>
+      </c>
+      <c r="C798" t="s">
+        <v>2277</v>
+      </c>
+      <c r="D798" t="s">
         <v>2278</v>
-      </c>
-      <c r="C798" t="s">
-        <v>2279</v>
-      </c>
-      <c r="D798" t="s">
-        <v>2280</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B799" t="s">
+        <v>2279</v>
+      </c>
+      <c r="C799" t="s">
+        <v>2280</v>
+      </c>
+      <c r="D799" t="s">
         <v>2281</v>
-      </c>
-      <c r="C799" t="s">
-        <v>2282</v>
-      </c>
-      <c r="D799" t="s">
-        <v>2283</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B800" t="s">
+        <v>2282</v>
+      </c>
+      <c r="C800" t="s">
+        <v>2283</v>
+      </c>
+      <c r="D800" t="s">
         <v>2284</v>
-      </c>
-      <c r="C800" t="s">
-        <v>2285</v>
-      </c>
-      <c r="D800" t="s">
-        <v>2286</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B801" t="s">
+        <v>2285</v>
+      </c>
+      <c r="C801" t="s">
+        <v>2286</v>
+      </c>
+      <c r="D801" t="s">
         <v>2287</v>
-      </c>
-      <c r="C801" t="s">
-        <v>2288</v>
-      </c>
-      <c r="D801" t="s">
-        <v>2289</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B802" t="s">
+        <v>2288</v>
+      </c>
+      <c r="C802" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D802" t="s">
         <v>2290</v>
-      </c>
-      <c r="C802" t="s">
-        <v>2291</v>
-      </c>
-      <c r="D802" t="s">
-        <v>2292</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B803" t="s">
+        <v>2291</v>
+      </c>
+      <c r="C803" t="s">
+        <v>2292</v>
+      </c>
+      <c r="D803" t="s">
         <v>2293</v>
-      </c>
-      <c r="C803" t="s">
-        <v>2294</v>
-      </c>
-      <c r="D803" t="s">
-        <v>2295</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B804" t="s">
+        <v>2294</v>
+      </c>
+      <c r="C804" t="s">
+        <v>2295</v>
+      </c>
+      <c r="D804" t="s">
         <v>2296</v>
-      </c>
-      <c r="C804" t="s">
-        <v>2297</v>
-      </c>
-      <c r="D804" t="s">
-        <v>2298</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B805" t="s">
+        <v>2297</v>
+      </c>
+      <c r="C805" t="s">
+        <v>2298</v>
+      </c>
+      <c r="D805" t="s">
         <v>2299</v>
-      </c>
-      <c r="C805" t="s">
-        <v>2300</v>
-      </c>
-      <c r="D805" t="s">
-        <v>2301</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B806" t="s">
+        <v>2300</v>
+      </c>
+      <c r="C806" t="s">
+        <v>2301</v>
+      </c>
+      <c r="D806" t="s">
         <v>2302</v>
-      </c>
-      <c r="C806" t="s">
-        <v>2303</v>
-      </c>
-      <c r="D806" t="s">
-        <v>2304</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B807" t="s">
+        <v>2303</v>
+      </c>
+      <c r="C807" t="s">
+        <v>2304</v>
+      </c>
+      <c r="D807" t="s">
         <v>2305</v>
-      </c>
-      <c r="C807" t="s">
-        <v>2306</v>
-      </c>
-      <c r="D807" t="s">
-        <v>2307</v>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B808" t="s">
+        <v>2306</v>
+      </c>
+      <c r="C808" t="s">
+        <v>2307</v>
+      </c>
+      <c r="D808" t="s">
         <v>2308</v>
-      </c>
-      <c r="C808" t="s">
-        <v>2309</v>
-      </c>
-      <c r="D808" t="s">
-        <v>2310</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B809" t="s">
+        <v>2309</v>
+      </c>
+      <c r="C809" t="s">
+        <v>2310</v>
+      </c>
+      <c r="D809" t="s">
         <v>2311</v>
-      </c>
-      <c r="C809" t="s">
-        <v>2312</v>
-      </c>
-      <c r="D809" t="s">
-        <v>2313</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B810" t="s">
+        <v>2312</v>
+      </c>
+      <c r="C810" t="s">
+        <v>2313</v>
+      </c>
+      <c r="D810" t="s">
         <v>2314</v>
-      </c>
-      <c r="C810" t="s">
-        <v>2315</v>
-      </c>
-      <c r="D810" t="s">
-        <v>2316</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B811" t="s">
+        <v>2315</v>
+      </c>
+      <c r="C811" t="s">
+        <v>2316</v>
+      </c>
+      <c r="D811" t="s">
         <v>2317</v>
-      </c>
-      <c r="C811" t="s">
-        <v>2318</v>
-      </c>
-      <c r="D811" t="s">
-        <v>2319</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B812" t="s">
+        <v>2318</v>
+      </c>
+      <c r="C812" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D812" t="s">
         <v>2320</v>
-      </c>
-      <c r="C812" t="s">
-        <v>2321</v>
-      </c>
-      <c r="D812" t="s">
-        <v>2322</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B813" t="s">
+        <v>2321</v>
+      </c>
+      <c r="C813" t="s">
+        <v>2322</v>
+      </c>
+      <c r="D813" t="s">
         <v>2323</v>
-      </c>
-      <c r="C813" t="s">
-        <v>2324</v>
-      </c>
-      <c r="D813" t="s">
-        <v>2325</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B814" t="s">
+        <v>2324</v>
+      </c>
+      <c r="C814" t="s">
+        <v>2325</v>
+      </c>
+      <c r="D814" t="s">
         <v>2326</v>
-      </c>
-      <c r="C814" t="s">
-        <v>2327</v>
-      </c>
-      <c r="D814" t="s">
-        <v>2328</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B815" t="s">
+        <v>2327</v>
+      </c>
+      <c r="C815" t="s">
+        <v>2328</v>
+      </c>
+      <c r="D815" t="s">
         <v>2329</v>
-      </c>
-      <c r="C815" t="s">
-        <v>967</v>
-      </c>
-      <c r="D815" t="s">
-        <v>2121</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B816" t="s">
         <v>2330</v>
@@ -19550,7 +19733,7 @@
     </row>
     <row r="817">
       <c r="A817" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B817" t="s">
         <v>2333</v>
@@ -19564,7 +19747,7 @@
     </row>
     <row r="818">
       <c r="A818" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B818" t="s">
         <v>2336</v>
@@ -19578,7 +19761,7 @@
     </row>
     <row r="819">
       <c r="A819" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B819" t="s">
         <v>2339</v>
@@ -19592,7 +19775,7 @@
     </row>
     <row r="820">
       <c r="A820" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B820" t="s">
         <v>2342</v>
@@ -19606,7 +19789,7 @@
     </row>
     <row r="821">
       <c r="A821" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B821" t="s">
         <v>2345</v>
@@ -19620,7 +19803,7 @@
     </row>
     <row r="822">
       <c r="A822" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B822" t="s">
         <v>2348</v>
@@ -19634,7 +19817,7 @@
     </row>
     <row r="823">
       <c r="A823" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B823" t="s">
         <v>2351</v>
@@ -19648,7 +19831,7 @@
     </row>
     <row r="824">
       <c r="A824" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B824" t="s">
         <v>2354</v>
@@ -19662,7 +19845,7 @@
     </row>
     <row r="825">
       <c r="A825" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B825" t="s">
         <v>2357</v>
@@ -19676,7 +19859,7 @@
     </row>
     <row r="826">
       <c r="A826" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B826" t="s">
         <v>2360</v>
@@ -19690,7 +19873,7 @@
     </row>
     <row r="827">
       <c r="A827" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B827" t="s">
         <v>2363</v>
@@ -19704,7 +19887,7 @@
     </row>
     <row r="828">
       <c r="A828" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B828" t="s">
         <v>2366</v>
@@ -19718,7 +19901,7 @@
     </row>
     <row r="829">
       <c r="A829" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B829" t="s">
         <v>2369</v>
@@ -19732,7 +19915,7 @@
     </row>
     <row r="830">
       <c r="A830" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B830" t="s">
         <v>2372</v>
@@ -19746,7 +19929,7 @@
     </row>
     <row r="831">
       <c r="A831" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B831" t="s">
         <v>2375</v>
@@ -19760,7 +19943,7 @@
     </row>
     <row r="832">
       <c r="A832" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B832" t="s">
         <v>2378</v>
@@ -19774,7 +19957,7 @@
     </row>
     <row r="833">
       <c r="A833" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B833" t="s">
         <v>2381</v>
@@ -19788,49 +19971,49 @@
     </row>
     <row r="834">
       <c r="A834" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B834" t="s">
         <v>2384</v>
       </c>
       <c r="C834" t="s">
-        <v>330</v>
+        <v>2385</v>
       </c>
       <c r="D834" t="s">
-        <v>331</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B835" t="s">
-        <v>2385</v>
+        <v>2387</v>
       </c>
       <c r="C835" t="s">
-        <v>2386</v>
+        <v>2388</v>
       </c>
       <c r="D835" t="s">
-        <v>2387</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B836" t="s">
-        <v>2388</v>
+        <v>2390</v>
       </c>
       <c r="C836" t="s">
-        <v>2389</v>
+        <v>967</v>
       </c>
       <c r="D836" t="s">
-        <v>2390</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B837" t="s">
         <v>2391</v>
@@ -19844,7 +20027,7 @@
     </row>
     <row r="838">
       <c r="A838" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B838" t="s">
         <v>2394</v>
@@ -19858,1458 +20041,1752 @@
     </row>
     <row r="839">
       <c r="A839" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B839" t="s">
         <v>2397</v>
       </c>
       <c r="C839" t="s">
-        <v>545</v>
+        <v>2398</v>
       </c>
       <c r="D839" t="s">
-        <v>546</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="840">
       <c r="A840" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B840" t="s">
-        <v>2398</v>
+        <v>2400</v>
       </c>
       <c r="C840" t="s">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="D840" t="s">
-        <v>2400</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B841" t="s">
-        <v>2401</v>
+        <v>2403</v>
       </c>
       <c r="C841" t="s">
-        <v>2402</v>
+        <v>2404</v>
       </c>
       <c r="D841" t="s">
-        <v>2403</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B842" t="s">
-        <v>2404</v>
+        <v>2406</v>
       </c>
       <c r="C842" t="s">
-        <v>786</v>
+        <v>2407</v>
       </c>
       <c r="D842" t="s">
-        <v>787</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B843" t="s">
-        <v>2405</v>
+        <v>2409</v>
       </c>
       <c r="C843" t="s">
-        <v>2406</v>
+        <v>2410</v>
       </c>
       <c r="D843" t="s">
-        <v>2407</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B844" t="s">
-        <v>2408</v>
+        <v>2412</v>
       </c>
       <c r="C844" t="s">
-        <v>2409</v>
+        <v>2413</v>
       </c>
       <c r="D844" t="s">
-        <v>2410</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B845" t="s">
-        <v>2411</v>
+        <v>2415</v>
       </c>
       <c r="C845" t="s">
-        <v>2412</v>
+        <v>2416</v>
       </c>
       <c r="D845" t="s">
-        <v>2413</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B846" t="s">
-        <v>2414</v>
+        <v>2418</v>
       </c>
       <c r="C846" t="s">
-        <v>2415</v>
+        <v>2419</v>
       </c>
       <c r="D846" t="s">
-        <v>2416</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B847" t="s">
-        <v>2417</v>
+        <v>2421</v>
       </c>
       <c r="C847" t="s">
-        <v>2418</v>
+        <v>2422</v>
       </c>
       <c r="D847" t="s">
-        <v>2419</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B848" t="s">
-        <v>2420</v>
+        <v>2424</v>
       </c>
       <c r="C848" t="s">
-        <v>2421</v>
+        <v>2425</v>
       </c>
       <c r="D848" t="s">
-        <v>2422</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B849" t="s">
-        <v>2423</v>
+        <v>2427</v>
       </c>
       <c r="C849" t="s">
-        <v>2424</v>
+        <v>2428</v>
       </c>
       <c r="D849" t="s">
-        <v>2425</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B850" t="s">
-        <v>2426</v>
+        <v>2430</v>
       </c>
       <c r="C850" t="s">
-        <v>2427</v>
+        <v>2431</v>
       </c>
       <c r="D850" t="s">
-        <v>2428</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B851" t="s">
-        <v>2429</v>
+        <v>2433</v>
       </c>
       <c r="C851" t="s">
-        <v>2430</v>
+        <v>2434</v>
       </c>
       <c r="D851" t="s">
-        <v>2431</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B852" t="s">
-        <v>2432</v>
+        <v>2436</v>
       </c>
       <c r="C852" t="s">
-        <v>2433</v>
+        <v>2437</v>
       </c>
       <c r="D852" t="s">
-        <v>2434</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B853" t="s">
-        <v>2435</v>
+        <v>2439</v>
       </c>
       <c r="C853" t="s">
-        <v>2436</v>
+        <v>2440</v>
       </c>
       <c r="D853" t="s">
-        <v>775</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B854" t="s">
-        <v>2437</v>
+        <v>2442</v>
       </c>
       <c r="C854" t="s">
-        <v>2438</v>
+        <v>2443</v>
       </c>
       <c r="D854" t="s">
-        <v>2439</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B855" t="s">
-        <v>2440</v>
+        <v>2445</v>
       </c>
       <c r="C855" t="s">
-        <v>2441</v>
+        <v>330</v>
       </c>
       <c r="D855" t="s">
-        <v>2442</v>
+        <v>331</v>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B856" t="s">
-        <v>2443</v>
+        <v>2446</v>
       </c>
       <c r="C856" t="s">
-        <v>2444</v>
+        <v>2447</v>
       </c>
       <c r="D856" t="s">
-        <v>2445</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B857" t="s">
-        <v>2446</v>
+        <v>2449</v>
       </c>
       <c r="C857" t="s">
-        <v>2447</v>
+        <v>2450</v>
       </c>
       <c r="D857" t="s">
-        <v>2448</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B858" t="s">
-        <v>2449</v>
+        <v>2452</v>
       </c>
       <c r="C858" t="s">
-        <v>2450</v>
+        <v>2453</v>
       </c>
       <c r="D858" t="s">
-        <v>2451</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B859" t="s">
-        <v>2452</v>
+        <v>2455</v>
       </c>
       <c r="C859" t="s">
-        <v>2453</v>
+        <v>2456</v>
       </c>
       <c r="D859" t="s">
-        <v>2454</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B860" t="s">
-        <v>2455</v>
+        <v>2458</v>
       </c>
       <c r="C860" t="s">
-        <v>2456</v>
+        <v>545</v>
       </c>
       <c r="D860" t="s">
-        <v>2457</v>
+        <v>546</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B861" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="C861" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
       <c r="D861" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B862" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="C862" t="s">
-        <v>2462</v>
+        <v>2463</v>
       </c>
       <c r="D862" t="s">
-        <v>166</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B863" t="s">
-        <v>2463</v>
+        <v>2465</v>
       </c>
       <c r="C863" t="s">
-        <v>2464</v>
+        <v>786</v>
       </c>
       <c r="D863" t="s">
-        <v>1617</v>
+        <v>787</v>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B864" t="s">
-        <v>2465</v>
+        <v>2466</v>
       </c>
       <c r="C864" t="s">
-        <v>2466</v>
+        <v>2467</v>
       </c>
       <c r="D864" t="s">
-        <v>1617</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B865" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="C865" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="D865" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B866" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="C866" t="s">
-        <v>2471</v>
+        <v>2473</v>
       </c>
       <c r="D866" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B867" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="C867" t="s">
-        <v>2474</v>
+        <v>2476</v>
       </c>
       <c r="D867" t="s">
-        <v>2475</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B868" t="s">
-        <v>2476</v>
+        <v>2478</v>
       </c>
       <c r="C868" t="s">
-        <v>2477</v>
+        <v>2479</v>
       </c>
       <c r="D868" t="s">
-        <v>2478</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B869" t="s">
-        <v>2479</v>
+        <v>2481</v>
       </c>
       <c r="C869" t="s">
-        <v>2480</v>
+        <v>2482</v>
       </c>
       <c r="D869" t="s">
-        <v>2481</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B870" t="s">
-        <v>2482</v>
+        <v>2484</v>
       </c>
       <c r="C870" t="s">
-        <v>2483</v>
+        <v>2485</v>
       </c>
       <c r="D870" t="s">
-        <v>2484</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B871" t="s">
-        <v>2485</v>
+        <v>2487</v>
       </c>
       <c r="C871" t="s">
-        <v>2486</v>
+        <v>2488</v>
       </c>
       <c r="D871" t="s">
-        <v>2487</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B872" t="s">
-        <v>2488</v>
+        <v>2490</v>
       </c>
       <c r="C872" t="s">
-        <v>2489</v>
+        <v>2491</v>
       </c>
       <c r="D872" t="s">
-        <v>2490</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B873" t="s">
-        <v>2491</v>
+        <v>2493</v>
       </c>
       <c r="C873" t="s">
-        <v>2492</v>
+        <v>2494</v>
       </c>
       <c r="D873" t="s">
-        <v>2493</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B874" t="s">
-        <v>2494</v>
+        <v>2496</v>
       </c>
       <c r="C874" t="s">
-        <v>2495</v>
+        <v>2497</v>
       </c>
       <c r="D874" t="s">
-        <v>2496</v>
+        <v>775</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B875" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="C875" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="D875" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B876" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="C876" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="D876" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B877" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="C877" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="D877" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B878" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="C878" t="s">
-        <v>2507</v>
+        <v>2508</v>
       </c>
       <c r="D878" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B879" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="C879" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="D879" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B880" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
       <c r="C880" t="s">
-        <v>2309</v>
+        <v>2514</v>
       </c>
       <c r="D880" t="s">
-        <v>2310</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B881" t="s">
-        <v>2513</v>
+        <v>2516</v>
       </c>
       <c r="C881" t="s">
-        <v>2514</v>
+        <v>2517</v>
       </c>
       <c r="D881" t="s">
-        <v>2515</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B882" t="s">
-        <v>2516</v>
+        <v>2519</v>
       </c>
       <c r="C882" t="s">
-        <v>2318</v>
+        <v>2520</v>
       </c>
       <c r="D882" t="s">
-        <v>2319</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B883" t="s">
-        <v>2517</v>
+        <v>2522</v>
       </c>
       <c r="C883" t="s">
-        <v>2518</v>
+        <v>2523</v>
       </c>
       <c r="D883" t="s">
-        <v>2519</v>
+        <v>166</v>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B884" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="C884" t="s">
-        <v>2321</v>
+        <v>2525</v>
       </c>
       <c r="D884" t="s">
-        <v>2322</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B885" t="s">
-        <v>2521</v>
+        <v>2526</v>
       </c>
       <c r="C885" t="s">
-        <v>2522</v>
+        <v>2527</v>
       </c>
       <c r="D885" t="s">
-        <v>2523</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B886" t="s">
-        <v>2524</v>
+        <v>2528</v>
       </c>
       <c r="C886" t="s">
-        <v>2525</v>
+        <v>2529</v>
       </c>
       <c r="D886" t="s">
-        <v>2526</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B887" t="s">
-        <v>2527</v>
+        <v>2531</v>
       </c>
       <c r="C887" t="s">
-        <v>2528</v>
+        <v>2532</v>
       </c>
       <c r="D887" t="s">
-        <v>2529</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B888" t="s">
-        <v>2530</v>
+        <v>2534</v>
       </c>
       <c r="C888" t="s">
-        <v>2531</v>
+        <v>2535</v>
       </c>
       <c r="D888" t="s">
-        <v>2532</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B889" t="s">
-        <v>2533</v>
+        <v>2537</v>
       </c>
       <c r="C889" t="s">
-        <v>2534</v>
+        <v>2538</v>
       </c>
       <c r="D889" t="s">
-        <v>2535</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B890" t="s">
-        <v>2536</v>
+        <v>2540</v>
       </c>
       <c r="C890" t="s">
-        <v>2537</v>
+        <v>2541</v>
       </c>
       <c r="D890" t="s">
-        <v>2538</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B891" t="s">
-        <v>2539</v>
+        <v>2543</v>
       </c>
       <c r="C891" t="s">
-        <v>1964</v>
+        <v>2544</v>
       </c>
       <c r="D891" t="s">
-        <v>474</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B892" t="s">
-        <v>2540</v>
+        <v>2546</v>
       </c>
       <c r="C892" t="s">
-        <v>2541</v>
+        <v>2547</v>
       </c>
       <c r="D892" t="s">
-        <v>2542</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B893" t="s">
-        <v>2543</v>
+        <v>2549</v>
       </c>
       <c r="C893" t="s">
-        <v>2544</v>
+        <v>2550</v>
       </c>
       <c r="D893" t="s">
-        <v>2545</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="s">
-        <v>1654</v>
+        <v>1715</v>
       </c>
       <c r="B894" t="s">
-        <v>2546</v>
+        <v>2552</v>
       </c>
       <c r="C894" t="s">
-        <v>2547</v>
+        <v>2553</v>
       </c>
       <c r="D894" t="s">
-        <v>2548</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="s">
-        <v>1669</v>
+        <v>1715</v>
       </c>
       <c r="B895" t="s">
-        <v>2549</v>
+        <v>2555</v>
       </c>
       <c r="C895" t="s">
-        <v>874</v>
+        <v>2556</v>
       </c>
       <c r="D895" t="s">
-        <v>875</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="s">
-        <v>1669</v>
+        <v>1715</v>
       </c>
       <c r="B896" t="s">
-        <v>2550</v>
+        <v>2558</v>
       </c>
       <c r="C896" t="s">
-        <v>2551</v>
+        <v>2559</v>
       </c>
       <c r="D896" t="s">
-        <v>2552</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="s">
-        <v>1669</v>
+        <v>1715</v>
       </c>
       <c r="B897" t="s">
-        <v>2553</v>
+        <v>2561</v>
       </c>
       <c r="C897" t="s">
-        <v>2554</v>
+        <v>2562</v>
       </c>
       <c r="D897" t="s">
-        <v>2555</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="s">
-        <v>2556</v>
+        <v>1715</v>
       </c>
       <c r="B898" t="s">
-        <v>2557</v>
+        <v>2564</v>
       </c>
       <c r="C898" t="s">
-        <v>2556</v>
+        <v>2565</v>
       </c>
       <c r="D898" t="s">
-        <v>2558</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="s">
-        <v>2556</v>
+        <v>1715</v>
       </c>
       <c r="B899" t="s">
-        <v>2559</v>
+        <v>2567</v>
       </c>
       <c r="C899" t="s">
-        <v>2560</v>
+        <v>2568</v>
       </c>
       <c r="D899" t="s">
-        <v>2561</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="s">
-        <v>2556</v>
+        <v>1715</v>
       </c>
       <c r="B900" t="s">
-        <v>2562</v>
+        <v>2570</v>
       </c>
       <c r="C900" t="s">
-        <v>2563</v>
+        <v>2571</v>
       </c>
       <c r="D900" t="s">
-        <v>2564</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="s">
-        <v>2556</v>
+        <v>1715</v>
       </c>
       <c r="B901" t="s">
-        <v>2565</v>
+        <v>2573</v>
       </c>
       <c r="C901" t="s">
-        <v>2566</v>
+        <v>2370</v>
       </c>
       <c r="D901" t="s">
-        <v>2567</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="s">
-        <v>1672</v>
+        <v>1715</v>
       </c>
       <c r="B902" t="s">
-        <v>2568</v>
+        <v>2574</v>
       </c>
       <c r="C902" t="s">
-        <v>2569</v>
+        <v>2575</v>
       </c>
       <c r="D902" t="s">
-        <v>2570</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="s">
-        <v>1672</v>
+        <v>1715</v>
       </c>
       <c r="B903" t="s">
-        <v>2571</v>
+        <v>2577</v>
       </c>
       <c r="C903" t="s">
-        <v>2572</v>
+        <v>2379</v>
       </c>
       <c r="D903" t="s">
-        <v>2573</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="904">
       <c r="A904" t="s">
-        <v>1672</v>
+        <v>1715</v>
       </c>
       <c r="B904" t="s">
-        <v>2574</v>
+        <v>2578</v>
       </c>
       <c r="C904" t="s">
-        <v>2575</v>
+        <v>2579</v>
       </c>
       <c r="D904" t="s">
-        <v>2576</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="s">
-        <v>1672</v>
+        <v>1715</v>
       </c>
       <c r="B905" t="s">
-        <v>2577</v>
+        <v>2581</v>
       </c>
       <c r="C905" t="s">
-        <v>304</v>
+        <v>2382</v>
       </c>
       <c r="D905" t="s">
-        <v>305</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="s">
-        <v>1672</v>
+        <v>1715</v>
       </c>
       <c r="B906" t="s">
-        <v>2578</v>
+        <v>2582</v>
       </c>
       <c r="C906" t="s">
-        <v>2579</v>
+        <v>2583</v>
       </c>
       <c r="D906" t="s">
-        <v>1824</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="s">
-        <v>1672</v>
+        <v>1715</v>
       </c>
       <c r="B907" t="s">
-        <v>2580</v>
+        <v>2585</v>
       </c>
       <c r="C907" t="s">
-        <v>2581</v>
+        <v>2586</v>
       </c>
       <c r="D907" t="s">
-        <v>2582</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="908">
       <c r="A908" t="s">
-        <v>1672</v>
+        <v>1715</v>
       </c>
       <c r="B908" t="s">
-        <v>2583</v>
+        <v>2588</v>
       </c>
       <c r="C908" t="s">
-        <v>2584</v>
+        <v>2589</v>
       </c>
       <c r="D908" t="s">
-        <v>2585</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="s">
-        <v>1672</v>
+        <v>1715</v>
       </c>
       <c r="B909" t="s">
-        <v>2586</v>
+        <v>2591</v>
       </c>
       <c r="C909" t="s">
-        <v>2587</v>
+        <v>2592</v>
       </c>
       <c r="D909" t="s">
-        <v>2588</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="s">
-        <v>1672</v>
+        <v>1715</v>
       </c>
       <c r="B910" t="s">
-        <v>2589</v>
+        <v>2594</v>
       </c>
       <c r="C910" t="s">
-        <v>2590</v>
+        <v>2595</v>
       </c>
       <c r="D910" t="s">
-        <v>2591</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="911">
       <c r="A911" t="s">
-        <v>1672</v>
+        <v>1715</v>
       </c>
       <c r="B911" t="s">
-        <v>2592</v>
+        <v>2597</v>
       </c>
       <c r="C911" t="s">
-        <v>2593</v>
+        <v>2598</v>
       </c>
       <c r="D911" t="s">
-        <v>2594</v>
+        <v>2599</v>
       </c>
     </row>
     <row r="912">
       <c r="A912" t="s">
-        <v>1672</v>
+        <v>1715</v>
       </c>
       <c r="B912" t="s">
-        <v>2595</v>
+        <v>2600</v>
       </c>
       <c r="C912" t="s">
-        <v>2596</v>
+        <v>2025</v>
       </c>
       <c r="D912" t="s">
-        <v>2597</v>
+        <v>474</v>
       </c>
     </row>
     <row r="913">
       <c r="A913" t="s">
-        <v>1672</v>
+        <v>1715</v>
       </c>
       <c r="B913" t="s">
-        <v>2598</v>
+        <v>2601</v>
       </c>
       <c r="C913" t="s">
-        <v>2599</v>
+        <v>2602</v>
       </c>
       <c r="D913" t="s">
-        <v>2600</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="914">
       <c r="A914" t="s">
-        <v>1672</v>
+        <v>1715</v>
       </c>
       <c r="B914" t="s">
-        <v>2601</v>
+        <v>2604</v>
       </c>
       <c r="C914" t="s">
-        <v>2602</v>
+        <v>2605</v>
       </c>
       <c r="D914" t="s">
-        <v>2603</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="915">
       <c r="A915" t="s">
-        <v>1672</v>
+        <v>1715</v>
       </c>
       <c r="B915" t="s">
-        <v>2604</v>
+        <v>2607</v>
       </c>
       <c r="C915" t="s">
-        <v>2605</v>
+        <v>2608</v>
       </c>
       <c r="D915" t="s">
-        <v>2606</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="916">
       <c r="A916" t="s">
-        <v>1672</v>
+        <v>1730</v>
       </c>
       <c r="B916" t="s">
-        <v>2607</v>
+        <v>2610</v>
       </c>
       <c r="C916" t="s">
-        <v>2608</v>
+        <v>874</v>
       </c>
       <c r="D916" t="s">
-        <v>2609</v>
+        <v>875</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="s">
-        <v>1672</v>
+        <v>1730</v>
       </c>
       <c r="B917" t="s">
-        <v>2610</v>
+        <v>2611</v>
       </c>
       <c r="C917" t="s">
-        <v>2611</v>
+        <v>2612</v>
       </c>
       <c r="D917" t="s">
-        <v>2612</v>
+        <v>2613</v>
       </c>
     </row>
     <row r="918">
       <c r="A918" t="s">
-        <v>1672</v>
+        <v>1730</v>
       </c>
       <c r="B918" t="s">
-        <v>2613</v>
+        <v>2614</v>
       </c>
       <c r="C918" t="s">
-        <v>2614</v>
+        <v>2615</v>
       </c>
       <c r="D918" t="s">
-        <v>2615</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="s">
-        <v>1672</v>
+        <v>2617</v>
       </c>
       <c r="B919" t="s">
-        <v>2616</v>
+        <v>2618</v>
       </c>
       <c r="C919" t="s">
-        <v>2590</v>
+        <v>2617</v>
       </c>
       <c r="D919" t="s">
-        <v>2591</v>
+        <v>2619</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="s">
-        <v>1672</v>
+        <v>2617</v>
       </c>
       <c r="B920" t="s">
-        <v>2617</v>
+        <v>2620</v>
       </c>
       <c r="C920" t="s">
-        <v>2618</v>
+        <v>2621</v>
       </c>
       <c r="D920" t="s">
-        <v>2619</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="921">
       <c r="A921" t="s">
-        <v>1672</v>
+        <v>2617</v>
       </c>
       <c r="B921" t="s">
-        <v>2620</v>
+        <v>2623</v>
       </c>
       <c r="C921" t="s">
-        <v>2621</v>
+        <v>2624</v>
       </c>
       <c r="D921" t="s">
-        <v>2622</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="922">
       <c r="A922" t="s">
-        <v>1672</v>
+        <v>2617</v>
       </c>
       <c r="B922" t="s">
-        <v>2623</v>
+        <v>2626</v>
       </c>
       <c r="C922" t="s">
-        <v>2624</v>
+        <v>2627</v>
       </c>
       <c r="D922" t="s">
-        <v>2625</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="923">
       <c r="A923" t="s">
-        <v>1672</v>
+        <v>1733</v>
       </c>
       <c r="B923" t="s">
-        <v>2626</v>
+        <v>2629</v>
       </c>
       <c r="C923" t="s">
-        <v>2627</v>
+        <v>2630</v>
       </c>
       <c r="D923" t="s">
-        <v>2628</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="924">
       <c r="A924" t="s">
-        <v>1672</v>
+        <v>1733</v>
       </c>
       <c r="B924" t="s">
-        <v>2629</v>
+        <v>2632</v>
       </c>
       <c r="C924" t="s">
-        <v>2630</v>
+        <v>2633</v>
       </c>
       <c r="D924" t="s">
-        <v>2631</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="925">
       <c r="A925" t="s">
-        <v>1672</v>
+        <v>1733</v>
       </c>
       <c r="B925" t="s">
-        <v>2632</v>
+        <v>2635</v>
       </c>
       <c r="C925" t="s">
-        <v>2633</v>
+        <v>2636</v>
       </c>
       <c r="D925" t="s">
-        <v>2634</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="926">
       <c r="A926" t="s">
-        <v>1672</v>
+        <v>1733</v>
       </c>
       <c r="B926" t="s">
-        <v>2635</v>
+        <v>2638</v>
       </c>
       <c r="C926" t="s">
-        <v>2636</v>
+        <v>304</v>
       </c>
       <c r="D926" t="s">
-        <v>2637</v>
+        <v>305</v>
       </c>
     </row>
     <row r="927">
       <c r="A927" t="s">
-        <v>1672</v>
+        <v>1733</v>
       </c>
       <c r="B927" t="s">
-        <v>2638</v>
+        <v>2639</v>
       </c>
       <c r="C927" t="s">
-        <v>2639</v>
+        <v>2640</v>
       </c>
       <c r="D927" t="s">
-        <v>2640</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="928">
       <c r="A928" t="s">
-        <v>1672</v>
+        <v>1733</v>
       </c>
       <c r="B928" t="s">
         <v>2641</v>
       </c>
       <c r="C928" t="s">
-        <v>2581</v>
+        <v>2642</v>
       </c>
       <c r="D928" t="s">
-        <v>2582</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="929">
       <c r="A929" t="s">
-        <v>1672</v>
+        <v>1733</v>
       </c>
       <c r="B929" t="s">
-        <v>2642</v>
+        <v>2644</v>
       </c>
       <c r="C929" t="s">
-        <v>2643</v>
+        <v>2645</v>
       </c>
       <c r="D929" t="s">
-        <v>2644</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="930">
       <c r="A930" t="s">
-        <v>1672</v>
+        <v>1733</v>
       </c>
       <c r="B930" t="s">
-        <v>2645</v>
+        <v>2647</v>
       </c>
       <c r="C930" t="s">
-        <v>2646</v>
+        <v>2648</v>
       </c>
       <c r="D930" t="s">
-        <v>2647</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="931">
       <c r="A931" t="s">
-        <v>1672</v>
+        <v>1733</v>
       </c>
       <c r="B931" t="s">
-        <v>2648</v>
+        <v>2650</v>
       </c>
       <c r="C931" t="s">
-        <v>2649</v>
+        <v>2651</v>
       </c>
       <c r="D931" t="s">
-        <v>2650</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="932">
       <c r="A932" t="s">
-        <v>1672</v>
+        <v>1733</v>
       </c>
       <c r="B932" t="s">
-        <v>2651</v>
+        <v>2653</v>
       </c>
       <c r="C932" t="s">
-        <v>2652</v>
+        <v>2654</v>
       </c>
       <c r="D932" t="s">
-        <v>2653</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="s">
-        <v>1672</v>
+        <v>1733</v>
       </c>
       <c r="B933" t="s">
-        <v>2654</v>
+        <v>2656</v>
       </c>
       <c r="C933" t="s">
-        <v>2655</v>
+        <v>2657</v>
       </c>
       <c r="D933" t="s">
-        <v>2656</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="s">
-        <v>1672</v>
+        <v>1733</v>
       </c>
       <c r="B934" t="s">
-        <v>2657</v>
+        <v>2659</v>
       </c>
       <c r="C934" t="s">
-        <v>2658</v>
+        <v>2660</v>
       </c>
       <c r="D934" t="s">
-        <v>2659</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="s">
-        <v>1672</v>
+        <v>1733</v>
       </c>
       <c r="B935" t="s">
-        <v>2660</v>
+        <v>2662</v>
       </c>
       <c r="C935" t="s">
-        <v>2661</v>
+        <v>2663</v>
       </c>
       <c r="D935" t="s">
-        <v>2662</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="s">
-        <v>1672</v>
+        <v>1733</v>
       </c>
       <c r="B936" t="s">
-        <v>2663</v>
+        <v>2665</v>
       </c>
       <c r="C936" t="s">
-        <v>2664</v>
+        <v>2666</v>
       </c>
       <c r="D936" t="s">
-        <v>2665</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="s">
-        <v>1672</v>
+        <v>1733</v>
       </c>
       <c r="B937" t="s">
-        <v>2666</v>
+        <v>2668</v>
       </c>
       <c r="C937" t="s">
-        <v>2667</v>
+        <v>2669</v>
       </c>
       <c r="D937" t="s">
-        <v>2668</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="s">
-        <v>1672</v>
+        <v>1733</v>
       </c>
       <c r="B938" t="s">
-        <v>2669</v>
+        <v>2671</v>
       </c>
       <c r="C938" t="s">
-        <v>1282</v>
+        <v>2672</v>
       </c>
       <c r="D938" t="s">
-        <v>1283</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="s">
-        <v>1672</v>
+        <v>1733</v>
       </c>
       <c r="B939" t="s">
-        <v>2670</v>
+        <v>2674</v>
       </c>
       <c r="C939" t="s">
-        <v>2671</v>
+        <v>2675</v>
       </c>
       <c r="D939" t="s">
-        <v>2672</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="s">
-        <v>1672</v>
+        <v>1733</v>
       </c>
       <c r="B940" t="s">
-        <v>2673</v>
+        <v>2677</v>
       </c>
       <c r="C940" t="s">
-        <v>2674</v>
+        <v>2651</v>
       </c>
       <c r="D940" t="s">
-        <v>2675</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="s">
-        <v>1672</v>
+        <v>1733</v>
       </c>
       <c r="B941" t="s">
-        <v>2676</v>
+        <v>2678</v>
       </c>
       <c r="C941" t="s">
-        <v>2677</v>
+        <v>2679</v>
       </c>
       <c r="D941" t="s">
-        <v>2678</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="s">
-        <v>1672</v>
+        <v>1733</v>
       </c>
       <c r="B942" t="s">
-        <v>2679</v>
+        <v>2681</v>
       </c>
       <c r="C942" t="s">
-        <v>2680</v>
+        <v>2682</v>
       </c>
       <c r="D942" t="s">
-        <v>2681</v>
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B943" t="s">
+        <v>2684</v>
+      </c>
+      <c r="C943" t="s">
+        <v>2685</v>
+      </c>
+      <c r="D943" t="s">
+        <v>2686</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B944" t="s">
+        <v>2687</v>
+      </c>
+      <c r="C944" t="s">
+        <v>2688</v>
+      </c>
+      <c r="D944" t="s">
+        <v>2689</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B945" t="s">
+        <v>2690</v>
+      </c>
+      <c r="C945" t="s">
+        <v>2691</v>
+      </c>
+      <c r="D945" t="s">
+        <v>2692</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B946" t="s">
+        <v>2693</v>
+      </c>
+      <c r="C946" t="s">
+        <v>2694</v>
+      </c>
+      <c r="D946" t="s">
+        <v>2695</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B947" t="s">
+        <v>2696</v>
+      </c>
+      <c r="C947" t="s">
+        <v>2697</v>
+      </c>
+      <c r="D947" t="s">
+        <v>2698</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B948" t="s">
+        <v>2699</v>
+      </c>
+      <c r="C948" t="s">
+        <v>2700</v>
+      </c>
+      <c r="D948" t="s">
+        <v>2701</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B949" t="s">
+        <v>2702</v>
+      </c>
+      <c r="C949" t="s">
+        <v>2642</v>
+      </c>
+      <c r="D949" t="s">
+        <v>2643</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B950" t="s">
+        <v>2703</v>
+      </c>
+      <c r="C950" t="s">
+        <v>2704</v>
+      </c>
+      <c r="D950" t="s">
+        <v>2705</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B951" t="s">
+        <v>2706</v>
+      </c>
+      <c r="C951" t="s">
+        <v>2707</v>
+      </c>
+      <c r="D951" t="s">
+        <v>2708</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B952" t="s">
+        <v>2709</v>
+      </c>
+      <c r="C952" t="s">
+        <v>2710</v>
+      </c>
+      <c r="D952" t="s">
+        <v>2711</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B953" t="s">
+        <v>2712</v>
+      </c>
+      <c r="C953" t="s">
+        <v>2713</v>
+      </c>
+      <c r="D953" t="s">
+        <v>2714</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B954" t="s">
+        <v>2715</v>
+      </c>
+      <c r="C954" t="s">
+        <v>2716</v>
+      </c>
+      <c r="D954" t="s">
+        <v>2717</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B955" t="s">
+        <v>2718</v>
+      </c>
+      <c r="C955" t="s">
+        <v>2719</v>
+      </c>
+      <c r="D955" t="s">
+        <v>2720</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B956" t="s">
+        <v>2721</v>
+      </c>
+      <c r="C956" t="s">
+        <v>2722</v>
+      </c>
+      <c r="D956" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B957" t="s">
+        <v>2724</v>
+      </c>
+      <c r="C957" t="s">
+        <v>2725</v>
+      </c>
+      <c r="D957" t="s">
+        <v>2726</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B958" t="s">
+        <v>2727</v>
+      </c>
+      <c r="C958" t="s">
+        <v>2728</v>
+      </c>
+      <c r="D958" t="s">
+        <v>2729</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B959" t="s">
+        <v>2730</v>
+      </c>
+      <c r="C959" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D959" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B960" t="s">
+        <v>2731</v>
+      </c>
+      <c r="C960" t="s">
+        <v>2732</v>
+      </c>
+      <c r="D960" t="s">
+        <v>2733</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B961" t="s">
+        <v>2734</v>
+      </c>
+      <c r="C961" t="s">
+        <v>2735</v>
+      </c>
+      <c r="D961" t="s">
+        <v>2736</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B962" t="s">
+        <v>2737</v>
+      </c>
+      <c r="C962" t="s">
+        <v>2738</v>
+      </c>
+      <c r="D962" t="s">
+        <v>2739</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B963" t="s">
+        <v>2740</v>
+      </c>
+      <c r="C963" t="s">
+        <v>2741</v>
+      </c>
+      <c r="D963" t="s">
+        <v>2742</v>
       </c>
     </row>
   </sheetData>

--- a/docs/amharic-review.xlsx
+++ b/docs/amharic-review.xlsx
@@ -6364,6 +6364,15 @@
     <t>የውል ማብቂያ</t>
   </si>
   <si>
+    <t>rep.fromMonth</t>
+  </si>
+  <si>
+    <t>From month</t>
+  </si>
+  <si>
+    <t>ከወር</t>
+  </si>
+  <si>
     <t>rep.k.bestMonth</t>
   </si>
   <si>
@@ -6749,6 +6758,15 @@
   </si>
   <si>
     <t>የቀረ ጊዜ</t>
+  </si>
+  <si>
+    <t>rep.toMonth</t>
+  </si>
+  <si>
+    <t>To month</t>
+  </si>
+  <si>
+    <t>እስከ ወር</t>
   </si>
   <si>
     <t>rep.toReturn</t>
@@ -18675,10 +18693,10 @@
         <v>2119</v>
       </c>
       <c r="C741" t="s">
-        <v>21</v>
+        <v>2120</v>
       </c>
       <c r="D741" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="742">
@@ -18686,10 +18704,10 @@
         <v>1724</v>
       </c>
       <c r="B742" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="C742" t="s">
-        <v>2122</v>
+        <v>21</v>
       </c>
       <c r="D742" t="s">
         <v>2123</v>
@@ -18734,7 +18752,7 @@
         <v>2131</v>
       </c>
       <c r="D745" t="s">
-        <v>2090</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="746">
@@ -18742,13 +18760,13 @@
         <v>1724</v>
       </c>
       <c r="B746" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="C746" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="D746" t="s">
-        <v>2134</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="747">
@@ -18815,10 +18833,10 @@
         <v>2147</v>
       </c>
       <c r="C751" t="s">
-        <v>1208</v>
+        <v>2148</v>
       </c>
       <c r="D751" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="752">
@@ -18826,10 +18844,10 @@
         <v>1724</v>
       </c>
       <c r="B752" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="C752" t="s">
-        <v>2150</v>
+        <v>1208</v>
       </c>
       <c r="D752" t="s">
         <v>2151</v>
@@ -18843,10 +18861,10 @@
         <v>2152</v>
       </c>
       <c r="C753" t="s">
-        <v>381</v>
+        <v>2153</v>
       </c>
       <c r="D753" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="754">
@@ -18854,10 +18872,10 @@
         <v>1724</v>
       </c>
       <c r="B754" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="C754" t="s">
-        <v>2155</v>
+        <v>381</v>
       </c>
       <c r="D754" t="s">
         <v>2156</v>
@@ -18941,10 +18959,10 @@
         <v>2172</v>
       </c>
       <c r="C760" t="s">
-        <v>376</v>
+        <v>2173</v>
       </c>
       <c r="D760" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="761">
@@ -18952,13 +18970,13 @@
         <v>1724</v>
       </c>
       <c r="B761" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="C761" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="D761" t="s">
-        <v>394</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="762">
@@ -18966,13 +18984,13 @@
         <v>1724</v>
       </c>
       <c r="B762" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="C762" t="s">
-        <v>2176</v>
+        <v>393</v>
       </c>
       <c r="D762" t="s">
-        <v>2173</v>
+        <v>394</v>
       </c>
     </row>
     <row r="763">
@@ -18980,13 +18998,13 @@
         <v>1724</v>
       </c>
       <c r="B763" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="C763" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="D763" t="s">
-        <v>2179</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="764">
@@ -19070,7 +19088,7 @@
         <v>2196</v>
       </c>
       <c r="D769" t="s">
-        <v>2126</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="770">
@@ -19078,13 +19096,13 @@
         <v>1724</v>
       </c>
       <c r="B770" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="C770" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="D770" t="s">
-        <v>2199</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="771">
@@ -19098,7 +19116,7 @@
         <v>2201</v>
       </c>
       <c r="D771" t="s">
-        <v>1666</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="772">
@@ -19106,13 +19124,13 @@
         <v>1724</v>
       </c>
       <c r="B772" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="C772" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="D772" t="s">
-        <v>2204</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="773">
@@ -19154,7 +19172,7 @@
         <v>2212</v>
       </c>
       <c r="D775" t="s">
-        <v>1412</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="776">
@@ -19162,13 +19180,13 @@
         <v>1724</v>
       </c>
       <c r="B776" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="C776" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="D776" t="s">
-        <v>2215</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="777">
@@ -19179,10 +19197,10 @@
         <v>2216</v>
       </c>
       <c r="C777" t="s">
-        <v>1735</v>
+        <v>2217</v>
       </c>
       <c r="D777" t="s">
-        <v>1750</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="778">
@@ -19190,13 +19208,13 @@
         <v>1724</v>
       </c>
       <c r="B778" t="s">
-        <v>2217</v>
+        <v>2219</v>
       </c>
       <c r="C778" t="s">
-        <v>48</v>
+        <v>1735</v>
       </c>
       <c r="D778" t="s">
-        <v>49</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="779">
@@ -19204,13 +19222,13 @@
         <v>1724</v>
       </c>
       <c r="B779" t="s">
-        <v>2218</v>
+        <v>2220</v>
       </c>
       <c r="C779" t="s">
-        <v>2219</v>
+        <v>48</v>
       </c>
       <c r="D779" t="s">
-        <v>2220</v>
+        <v>49</v>
       </c>
     </row>
     <row r="780">
@@ -19383,35 +19401,35 @@
     </row>
     <row r="792">
       <c r="A792" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B792" t="s">
         <v>2257</v>
       </c>
-      <c r="B792" t="s">
+      <c r="C792" t="s">
         <v>2258</v>
       </c>
-      <c r="C792" t="s">
+      <c r="D792" t="s">
         <v>2259</v>
-      </c>
-      <c r="D792" t="s">
-        <v>2260</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="s">
-        <v>2257</v>
+        <v>1724</v>
       </c>
       <c r="B793" t="s">
+        <v>2260</v>
+      </c>
+      <c r="C793" t="s">
         <v>2261</v>
       </c>
-      <c r="C793" t="s">
+      <c r="D793" t="s">
         <v>2262</v>
-      </c>
-      <c r="D793" t="s">
-        <v>2263</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="s">
-        <v>2257</v>
+        <v>2263</v>
       </c>
       <c r="B794" t="s">
         <v>2264</v>
@@ -19425,7 +19443,7 @@
     </row>
     <row r="795">
       <c r="A795" t="s">
-        <v>2257</v>
+        <v>2263</v>
       </c>
       <c r="B795" t="s">
         <v>2267</v>
@@ -19439,7 +19457,7 @@
     </row>
     <row r="796">
       <c r="A796" t="s">
-        <v>1338</v>
+        <v>2263</v>
       </c>
       <c r="B796" t="s">
         <v>2270</v>
@@ -19453,7 +19471,7 @@
     </row>
     <row r="797">
       <c r="A797" t="s">
-        <v>1338</v>
+        <v>2263</v>
       </c>
       <c r="B797" t="s">
         <v>2273</v>
@@ -19481,7 +19499,7 @@
     </row>
     <row r="799">
       <c r="A799" t="s">
-        <v>1715</v>
+        <v>1338</v>
       </c>
       <c r="B799" t="s">
         <v>2279</v>
@@ -19495,7 +19513,7 @@
     </row>
     <row r="800">
       <c r="A800" t="s">
-        <v>1715</v>
+        <v>1338</v>
       </c>
       <c r="B800" t="s">
         <v>2282</v>
@@ -20005,10 +20023,10 @@
         <v>2390</v>
       </c>
       <c r="C836" t="s">
-        <v>967</v>
+        <v>2391</v>
       </c>
       <c r="D836" t="s">
-        <v>2182</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="837">
@@ -20016,13 +20034,13 @@
         <v>1715</v>
       </c>
       <c r="B837" t="s">
-        <v>2391</v>
+        <v>2393</v>
       </c>
       <c r="C837" t="s">
-        <v>2392</v>
+        <v>2394</v>
       </c>
       <c r="D837" t="s">
-        <v>2393</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="838">
@@ -20030,13 +20048,13 @@
         <v>1715</v>
       </c>
       <c r="B838" t="s">
-        <v>2394</v>
+        <v>2396</v>
       </c>
       <c r="C838" t="s">
-        <v>2395</v>
+        <v>967</v>
       </c>
       <c r="D838" t="s">
-        <v>2396</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="839">
@@ -20271,10 +20289,10 @@
         <v>2445</v>
       </c>
       <c r="C855" t="s">
-        <v>330</v>
+        <v>2446</v>
       </c>
       <c r="D855" t="s">
-        <v>331</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="856">
@@ -20282,13 +20300,13 @@
         <v>1715</v>
       </c>
       <c r="B856" t="s">
-        <v>2446</v>
+        <v>2448</v>
       </c>
       <c r="C856" t="s">
-        <v>2447</v>
+        <v>2449</v>
       </c>
       <c r="D856" t="s">
-        <v>2448</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="857">
@@ -20296,13 +20314,13 @@
         <v>1715</v>
       </c>
       <c r="B857" t="s">
-        <v>2449</v>
+        <v>2451</v>
       </c>
       <c r="C857" t="s">
-        <v>2450</v>
+        <v>330</v>
       </c>
       <c r="D857" t="s">
-        <v>2451</v>
+        <v>331</v>
       </c>
     </row>
     <row r="858">
@@ -20341,10 +20359,10 @@
         <v>2458</v>
       </c>
       <c r="C860" t="s">
-        <v>545</v>
+        <v>2459</v>
       </c>
       <c r="D860" t="s">
-        <v>546</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="861">
@@ -20352,13 +20370,13 @@
         <v>1715</v>
       </c>
       <c r="B861" t="s">
-        <v>2459</v>
+        <v>2461</v>
       </c>
       <c r="C861" t="s">
-        <v>2460</v>
+        <v>2462</v>
       </c>
       <c r="D861" t="s">
-        <v>2461</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="862">
@@ -20366,13 +20384,13 @@
         <v>1715</v>
       </c>
       <c r="B862" t="s">
-        <v>2462</v>
+        <v>2464</v>
       </c>
       <c r="C862" t="s">
-        <v>2463</v>
+        <v>545</v>
       </c>
       <c r="D862" t="s">
-        <v>2464</v>
+        <v>546</v>
       </c>
     </row>
     <row r="863">
@@ -20383,10 +20401,10 @@
         <v>2465</v>
       </c>
       <c r="C863" t="s">
-        <v>786</v>
+        <v>2466</v>
       </c>
       <c r="D863" t="s">
-        <v>787</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="864">
@@ -20394,13 +20412,13 @@
         <v>1715</v>
       </c>
       <c r="B864" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="C864" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="D864" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="865">
@@ -20408,13 +20426,13 @@
         <v>1715</v>
       </c>
       <c r="B865" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="C865" t="s">
-        <v>2470</v>
+        <v>786</v>
       </c>
       <c r="D865" t="s">
-        <v>2471</v>
+        <v>787</v>
       </c>
     </row>
     <row r="866">
@@ -20540,7 +20558,7 @@
         <v>2497</v>
       </c>
       <c r="D874" t="s">
-        <v>775</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="875">
@@ -20548,13 +20566,13 @@
         <v>1715</v>
       </c>
       <c r="B875" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="C875" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="D875" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="876">
@@ -20562,13 +20580,13 @@
         <v>1715</v>
       </c>
       <c r="B876" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="C876" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="D876" t="s">
-        <v>2503</v>
+        <v>775</v>
       </c>
     </row>
     <row r="877">
@@ -20666,7 +20684,7 @@
         <v>2523</v>
       </c>
       <c r="D883" t="s">
-        <v>166</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="884">
@@ -20674,13 +20692,13 @@
         <v>1715</v>
       </c>
       <c r="B884" t="s">
-        <v>2524</v>
+        <v>2525</v>
       </c>
       <c r="C884" t="s">
-        <v>2525</v>
+        <v>2526</v>
       </c>
       <c r="D884" t="s">
-        <v>1666</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="885">
@@ -20688,13 +20706,13 @@
         <v>1715</v>
       </c>
       <c r="B885" t="s">
-        <v>2526</v>
+        <v>2528</v>
       </c>
       <c r="C885" t="s">
-        <v>2527</v>
+        <v>2529</v>
       </c>
       <c r="D885" t="s">
-        <v>1666</v>
+        <v>166</v>
       </c>
     </row>
     <row r="886">
@@ -20702,13 +20720,13 @@
         <v>1715</v>
       </c>
       <c r="B886" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="C886" t="s">
-        <v>2529</v>
+        <v>2531</v>
       </c>
       <c r="D886" t="s">
-        <v>2530</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="887">
@@ -20716,13 +20734,13 @@
         <v>1715</v>
       </c>
       <c r="B887" t="s">
-        <v>2531</v>
+        <v>2532</v>
       </c>
       <c r="C887" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
       <c r="D887" t="s">
-        <v>2533</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="888">
@@ -20915,10 +20933,10 @@
         <v>2573</v>
       </c>
       <c r="C901" t="s">
-        <v>2370</v>
+        <v>2574</v>
       </c>
       <c r="D901" t="s">
-        <v>2371</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="902">
@@ -20926,13 +20944,13 @@
         <v>1715</v>
       </c>
       <c r="B902" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="C902" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="D902" t="s">
-        <v>2576</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="903">
@@ -20940,13 +20958,13 @@
         <v>1715</v>
       </c>
       <c r="B903" t="s">
-        <v>2577</v>
+        <v>2579</v>
       </c>
       <c r="C903" t="s">
-        <v>2379</v>
+        <v>2376</v>
       </c>
       <c r="D903" t="s">
-        <v>2380</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="904">
@@ -20954,13 +20972,13 @@
         <v>1715</v>
       </c>
       <c r="B904" t="s">
-        <v>2578</v>
+        <v>2580</v>
       </c>
       <c r="C904" t="s">
-        <v>2579</v>
+        <v>2581</v>
       </c>
       <c r="D904" t="s">
-        <v>2580</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="905">
@@ -20968,13 +20986,13 @@
         <v>1715</v>
       </c>
       <c r="B905" t="s">
-        <v>2581</v>
+        <v>2583</v>
       </c>
       <c r="C905" t="s">
-        <v>2382</v>
+        <v>2385</v>
       </c>
       <c r="D905" t="s">
-        <v>2383</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="906">
@@ -20982,13 +21000,13 @@
         <v>1715</v>
       </c>
       <c r="B906" t="s">
-        <v>2582</v>
+        <v>2584</v>
       </c>
       <c r="C906" t="s">
-        <v>2583</v>
+        <v>2585</v>
       </c>
       <c r="D906" t="s">
-        <v>2584</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="907">
@@ -20996,13 +21014,13 @@
         <v>1715</v>
       </c>
       <c r="B907" t="s">
-        <v>2585</v>
+        <v>2587</v>
       </c>
       <c r="C907" t="s">
-        <v>2586</v>
+        <v>2388</v>
       </c>
       <c r="D907" t="s">
-        <v>2587</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="908">
@@ -21069,10 +21087,10 @@
         <v>2600</v>
       </c>
       <c r="C912" t="s">
-        <v>2025</v>
+        <v>2601</v>
       </c>
       <c r="D912" t="s">
-        <v>474</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="913">
@@ -21080,13 +21098,13 @@
         <v>1715</v>
       </c>
       <c r="B913" t="s">
-        <v>2601</v>
+        <v>2603</v>
       </c>
       <c r="C913" t="s">
-        <v>2602</v>
+        <v>2604</v>
       </c>
       <c r="D913" t="s">
-        <v>2603</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="914">
@@ -21094,13 +21112,13 @@
         <v>1715</v>
       </c>
       <c r="B914" t="s">
-        <v>2604</v>
+        <v>2606</v>
       </c>
       <c r="C914" t="s">
-        <v>2605</v>
+        <v>2025</v>
       </c>
       <c r="D914" t="s">
-        <v>2606</v>
+        <v>474</v>
       </c>
     </row>
     <row r="915">
@@ -21119,30 +21137,30 @@
     </row>
     <row r="916">
       <c r="A916" t="s">
-        <v>1730</v>
+        <v>1715</v>
       </c>
       <c r="B916" t="s">
         <v>2610</v>
       </c>
       <c r="C916" t="s">
-        <v>874</v>
+        <v>2611</v>
       </c>
       <c r="D916" t="s">
-        <v>875</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="917">
       <c r="A917" t="s">
-        <v>1730</v>
+        <v>1715</v>
       </c>
       <c r="B917" t="s">
-        <v>2611</v>
+        <v>2613</v>
       </c>
       <c r="C917" t="s">
-        <v>2612</v>
+        <v>2614</v>
       </c>
       <c r="D917" t="s">
-        <v>2613</v>
+        <v>2615</v>
       </c>
     </row>
     <row r="918">
@@ -21150,24 +21168,24 @@
         <v>1730</v>
       </c>
       <c r="B918" t="s">
-        <v>2614</v>
+        <v>2616</v>
       </c>
       <c r="C918" t="s">
-        <v>2615</v>
+        <v>874</v>
       </c>
       <c r="D918" t="s">
-        <v>2616</v>
+        <v>875</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="s">
+        <v>1730</v>
+      </c>
+      <c r="B919" t="s">
         <v>2617</v>
       </c>
-      <c r="B919" t="s">
+      <c r="C919" t="s">
         <v>2618</v>
-      </c>
-      <c r="C919" t="s">
-        <v>2617</v>
       </c>
       <c r="D919" t="s">
         <v>2619</v>
@@ -21175,7 +21193,7 @@
     </row>
     <row r="920">
       <c r="A920" t="s">
-        <v>2617</v>
+        <v>1730</v>
       </c>
       <c r="B920" t="s">
         <v>2620</v>
@@ -21189,13 +21207,13 @@
     </row>
     <row r="921">
       <c r="A921" t="s">
-        <v>2617</v>
+        <v>2623</v>
       </c>
       <c r="B921" t="s">
+        <v>2624</v>
+      </c>
+      <c r="C921" t="s">
         <v>2623</v>
-      </c>
-      <c r="C921" t="s">
-        <v>2624</v>
       </c>
       <c r="D921" t="s">
         <v>2625</v>
@@ -21203,7 +21221,7 @@
     </row>
     <row r="922">
       <c r="A922" t="s">
-        <v>2617</v>
+        <v>2623</v>
       </c>
       <c r="B922" t="s">
         <v>2626</v>
@@ -21217,7 +21235,7 @@
     </row>
     <row r="923">
       <c r="A923" t="s">
-        <v>1733</v>
+        <v>2623</v>
       </c>
       <c r="B923" t="s">
         <v>2629</v>
@@ -21231,7 +21249,7 @@
     </row>
     <row r="924">
       <c r="A924" t="s">
-        <v>1733</v>
+        <v>2623</v>
       </c>
       <c r="B924" t="s">
         <v>2632</v>
@@ -21265,10 +21283,10 @@
         <v>2638</v>
       </c>
       <c r="C926" t="s">
-        <v>304</v>
+        <v>2639</v>
       </c>
       <c r="D926" t="s">
-        <v>305</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="927">
@@ -21276,13 +21294,13 @@
         <v>1733</v>
       </c>
       <c r="B927" t="s">
-        <v>2639</v>
+        <v>2641</v>
       </c>
       <c r="C927" t="s">
-        <v>2640</v>
+        <v>2642</v>
       </c>
       <c r="D927" t="s">
-        <v>1885</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="928">
@@ -21290,13 +21308,13 @@
         <v>1733</v>
       </c>
       <c r="B928" t="s">
-        <v>2641</v>
+        <v>2644</v>
       </c>
       <c r="C928" t="s">
-        <v>2642</v>
+        <v>304</v>
       </c>
       <c r="D928" t="s">
-        <v>2643</v>
+        <v>305</v>
       </c>
     </row>
     <row r="929">
@@ -21304,13 +21322,13 @@
         <v>1733</v>
       </c>
       <c r="B929" t="s">
-        <v>2644</v>
+        <v>2645</v>
       </c>
       <c r="C929" t="s">
-        <v>2645</v>
+        <v>2646</v>
       </c>
       <c r="D929" t="s">
-        <v>2646</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="930">
@@ -21461,10 +21479,10 @@
         <v>2677</v>
       </c>
       <c r="C940" t="s">
-        <v>2651</v>
+        <v>2678</v>
       </c>
       <c r="D940" t="s">
-        <v>2652</v>
+        <v>2679</v>
       </c>
     </row>
     <row r="941">
@@ -21472,13 +21490,13 @@
         <v>1733</v>
       </c>
       <c r="B941" t="s">
-        <v>2678</v>
+        <v>2680</v>
       </c>
       <c r="C941" t="s">
-        <v>2679</v>
+        <v>2681</v>
       </c>
       <c r="D941" t="s">
-        <v>2680</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="942">
@@ -21486,13 +21504,13 @@
         <v>1733</v>
       </c>
       <c r="B942" t="s">
-        <v>2681</v>
+        <v>2683</v>
       </c>
       <c r="C942" t="s">
-        <v>2682</v>
+        <v>2657</v>
       </c>
       <c r="D942" t="s">
-        <v>2683</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="943">
@@ -21587,10 +21605,10 @@
         <v>2702</v>
       </c>
       <c r="C949" t="s">
-        <v>2642</v>
+        <v>2703</v>
       </c>
       <c r="D949" t="s">
-        <v>2643</v>
+        <v>2704</v>
       </c>
     </row>
     <row r="950">
@@ -21598,13 +21616,13 @@
         <v>1733</v>
       </c>
       <c r="B950" t="s">
-        <v>2703</v>
+        <v>2705</v>
       </c>
       <c r="C950" t="s">
-        <v>2704</v>
+        <v>2706</v>
       </c>
       <c r="D950" t="s">
-        <v>2705</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="951">
@@ -21612,13 +21630,13 @@
         <v>1733</v>
       </c>
       <c r="B951" t="s">
-        <v>2706</v>
+        <v>2708</v>
       </c>
       <c r="C951" t="s">
-        <v>2707</v>
+        <v>2648</v>
       </c>
       <c r="D951" t="s">
-        <v>2708</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="952">
@@ -21727,10 +21745,10 @@
         <v>2730</v>
       </c>
       <c r="C959" t="s">
-        <v>1282</v>
+        <v>2731</v>
       </c>
       <c r="D959" t="s">
-        <v>1283</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="960">
@@ -21738,13 +21756,13 @@
         <v>1733</v>
       </c>
       <c r="B960" t="s">
-        <v>2731</v>
+        <v>2733</v>
       </c>
       <c r="C960" t="s">
-        <v>2732</v>
+        <v>2734</v>
       </c>
       <c r="D960" t="s">
-        <v>2733</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="961">
@@ -21752,13 +21770,13 @@
         <v>1733</v>
       </c>
       <c r="B961" t="s">
-        <v>2734</v>
+        <v>2736</v>
       </c>
       <c r="C961" t="s">
-        <v>2735</v>
+        <v>1282</v>
       </c>
       <c r="D961" t="s">
-        <v>2736</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="962">
@@ -21789,6 +21807,34 @@
         <v>2742</v>
       </c>
     </row>
+    <row r="964">
+      <c r="A964" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B964" t="s">
+        <v>2743</v>
+      </c>
+      <c r="C964" t="s">
+        <v>2744</v>
+      </c>
+      <c r="D964" t="s">
+        <v>2745</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B965" t="s">
+        <v>2746</v>
+      </c>
+      <c r="C965" t="s">
+        <v>2747</v>
+      </c>
+      <c r="D965" t="s">
+        <v>2748</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/docs/amharic-review.xlsx
+++ b/docs/amharic-review.xlsx
@@ -1723,10 +1723,19 @@
     <t>prop.unitStatus</t>
   </si>
   <si>
-    <t>Starting status</t>
+    <t>Availability</t>
   </si>
   <si>
     <t>መነሻ ሁኔታ</t>
+  </si>
+  <si>
+    <t>prop.unitStatusHint</t>
+  </si>
+  <si>
+    <t>Occupied is set automatically when a lease starts. You never set it by hand.</t>
+  </si>
+  <si>
+    <t>ተይዟል የሚለው ውል ሲጀምር በራስ-ሰር ይሆናል። በእጅ አያስቀምጡትም።</t>
   </si>
   <si>
     <t>prop.viewPlan</t>
@@ -11685,21 +11694,21 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
+        <v>453</v>
+      </c>
+      <c r="B195" t="s">
         <v>574</v>
       </c>
-      <c r="B195" t="s">
+      <c r="C195" t="s">
         <v>575</v>
       </c>
-      <c r="C195" t="s">
+      <c r="D195" t="s">
         <v>576</v>
-      </c>
-      <c r="D195" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B196" t="s">
         <v>578</v>
@@ -11713,7 +11722,7 @@
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B197" t="s">
         <v>581</v>
@@ -11727,7 +11736,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B198" t="s">
         <v>584</v>
@@ -11741,7 +11750,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B199" t="s">
         <v>587</v>
@@ -11755,7 +11764,7 @@
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B200" t="s">
         <v>590</v>
@@ -11769,7 +11778,7 @@
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B201" t="s">
         <v>593</v>
@@ -11783,7 +11792,7 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B202" t="s">
         <v>596</v>
@@ -11797,7 +11806,7 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B203" t="s">
         <v>599</v>
@@ -11811,7 +11820,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B204" t="s">
         <v>602</v>
@@ -11825,21 +11834,21 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
+        <v>577</v>
+      </c>
+      <c r="B205" t="s">
         <v>605</v>
       </c>
-      <c r="B205" t="s">
+      <c r="C205" t="s">
         <v>606</v>
       </c>
-      <c r="C205" t="s">
+      <c r="D205" t="s">
         <v>607</v>
-      </c>
-      <c r="D205" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B206" t="s">
         <v>609</v>
@@ -11853,7 +11862,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B207" t="s">
         <v>612</v>
@@ -11867,7 +11876,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B208" t="s">
         <v>615</v>
@@ -11881,7 +11890,7 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B209" t="s">
         <v>618</v>
@@ -11895,7 +11904,7 @@
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B210" t="s">
         <v>621</v>
@@ -11909,7 +11918,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B211" t="s">
         <v>624</v>
@@ -11923,7 +11932,7 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B212" t="s">
         <v>627</v>
@@ -11937,21 +11946,21 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
+        <v>608</v>
+      </c>
+      <c r="B213" t="s">
         <v>630</v>
       </c>
-      <c r="B213" t="s">
+      <c r="C213" t="s">
         <v>631</v>
       </c>
-      <c r="C213" t="s">
+      <c r="D213" t="s">
         <v>632</v>
-      </c>
-      <c r="D213" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B214" t="s">
         <v>634</v>
@@ -11965,7 +11974,7 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B215" t="s">
         <v>637</v>
@@ -11979,7 +11988,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B216" t="s">
         <v>640</v>
@@ -11993,7 +12002,7 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B217" t="s">
         <v>643</v>
@@ -12007,7 +12016,7 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B218" t="s">
         <v>646</v>
@@ -12021,7 +12030,7 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B219" t="s">
         <v>649</v>
@@ -12035,7 +12044,7 @@
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B220" t="s">
         <v>652</v>
@@ -12049,7 +12058,7 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B221" t="s">
         <v>655</v>
@@ -12063,7 +12072,7 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B222" t="s">
         <v>658</v>
@@ -12077,7 +12086,7 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B223" t="s">
         <v>661</v>
@@ -12091,7 +12100,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B224" t="s">
         <v>664</v>
@@ -12105,7 +12114,7 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B225" t="s">
         <v>667</v>
@@ -12119,7 +12128,7 @@
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B226" t="s">
         <v>670</v>
@@ -12133,21 +12142,21 @@
     </row>
     <row r="227">
       <c r="A227" t="s">
+        <v>633</v>
+      </c>
+      <c r="B227" t="s">
         <v>673</v>
       </c>
-      <c r="B227" t="s">
+      <c r="C227" t="s">
         <v>674</v>
       </c>
-      <c r="C227" t="s">
+      <c r="D227" t="s">
         <v>675</v>
-      </c>
-      <c r="D227" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B228" t="s">
         <v>677</v>
@@ -12161,7 +12170,7 @@
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B229" t="s">
         <v>680</v>
@@ -12175,7 +12184,7 @@
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B230" t="s">
         <v>683</v>
@@ -12189,7 +12198,7 @@
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B231" t="s">
         <v>686</v>
@@ -12203,7 +12212,7 @@
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B232" t="s">
         <v>689</v>
@@ -12217,7 +12226,7 @@
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B233" t="s">
         <v>692</v>
@@ -12231,7 +12240,7 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B234" t="s">
         <v>695</v>
@@ -12245,7 +12254,7 @@
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B235" t="s">
         <v>698</v>
@@ -12259,7 +12268,7 @@
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B236" t="s">
         <v>701</v>
@@ -12273,7 +12282,7 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B237" t="s">
         <v>704</v>
@@ -12287,7 +12296,7 @@
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B238" t="s">
         <v>707</v>
@@ -12301,7 +12310,7 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B239" t="s">
         <v>710</v>
@@ -12315,7 +12324,7 @@
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B240" t="s">
         <v>713</v>
@@ -12329,7 +12338,7 @@
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B241" t="s">
         <v>716</v>
@@ -12343,7 +12352,7 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B242" t="s">
         <v>719</v>
@@ -12357,7 +12366,7 @@
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B243" t="s">
         <v>722</v>
@@ -12371,7 +12380,7 @@
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B244" t="s">
         <v>725</v>
@@ -12385,7 +12394,7 @@
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B245" t="s">
         <v>728</v>
@@ -12399,7 +12408,7 @@
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B246" t="s">
         <v>731</v>
@@ -12413,7 +12422,7 @@
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B247" t="s">
         <v>734</v>
@@ -12427,7 +12436,7 @@
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B248" t="s">
         <v>737</v>
@@ -12441,7 +12450,7 @@
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B249" t="s">
         <v>740</v>
@@ -12455,7 +12464,7 @@
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B250" t="s">
         <v>743</v>
@@ -12469,7 +12478,7 @@
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B251" t="s">
         <v>746</v>
@@ -12483,7 +12492,7 @@
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B252" t="s">
         <v>749</v>
@@ -12497,7 +12506,7 @@
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B253" t="s">
         <v>752</v>
@@ -12511,7 +12520,7 @@
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B254" t="s">
         <v>755</v>
@@ -12525,7 +12534,7 @@
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B255" t="s">
         <v>758</v>
@@ -12539,7 +12548,7 @@
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B256" t="s">
         <v>761</v>
@@ -12553,7 +12562,7 @@
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B257" t="s">
         <v>764</v>
@@ -12567,7 +12576,7 @@
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B258" t="s">
         <v>767</v>
@@ -12581,7 +12590,7 @@
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B259" t="s">
         <v>770</v>
@@ -12595,7 +12604,7 @@
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B260" t="s">
         <v>773</v>
@@ -12609,7 +12618,7 @@
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B261" t="s">
         <v>776</v>
@@ -12623,7 +12632,7 @@
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B262" t="s">
         <v>779</v>
@@ -12637,7 +12646,7 @@
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B263" t="s">
         <v>782</v>
@@ -12651,7 +12660,7 @@
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B264" t="s">
         <v>785</v>
@@ -12665,7 +12674,7 @@
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B265" t="s">
         <v>788</v>
@@ -12679,7 +12688,7 @@
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B266" t="s">
         <v>791</v>
@@ -12693,7 +12702,7 @@
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B267" t="s">
         <v>794</v>
@@ -12707,7 +12716,7 @@
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B268" t="s">
         <v>797</v>
@@ -12721,7 +12730,7 @@
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B269" t="s">
         <v>800</v>
@@ -12735,7 +12744,7 @@
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B270" t="s">
         <v>803</v>
@@ -12749,7 +12758,7 @@
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B271" t="s">
         <v>806</v>
@@ -12763,7 +12772,7 @@
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B272" t="s">
         <v>809</v>
@@ -12777,7 +12786,7 @@
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B273" t="s">
         <v>812</v>
@@ -12791,7 +12800,7 @@
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B274" t="s">
         <v>815</v>
@@ -12805,7 +12814,7 @@
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B275" t="s">
         <v>818</v>
@@ -12819,7 +12828,7 @@
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B276" t="s">
         <v>821</v>
@@ -12833,7 +12842,7 @@
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B277" t="s">
         <v>824</v>
@@ -12847,7 +12856,7 @@
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B278" t="s">
         <v>827</v>
@@ -12861,7 +12870,7 @@
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B279" t="s">
         <v>830</v>
@@ -12875,7 +12884,7 @@
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B280" t="s">
         <v>833</v>
@@ -12889,7 +12898,7 @@
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B281" t="s">
         <v>836</v>
@@ -12903,7 +12912,7 @@
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B282" t="s">
         <v>839</v>
@@ -12917,7 +12926,7 @@
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B283" t="s">
         <v>842</v>
@@ -12931,7 +12940,7 @@
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B284" t="s">
         <v>845</v>
@@ -12945,7 +12954,7 @@
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B285" t="s">
         <v>848</v>
@@ -12959,7 +12968,7 @@
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B286" t="s">
         <v>851</v>
@@ -12973,7 +12982,7 @@
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B287" t="s">
         <v>854</v>
@@ -12987,7 +12996,7 @@
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B288" t="s">
         <v>857</v>
@@ -13001,7 +13010,7 @@
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B289" t="s">
         <v>860</v>
@@ -13015,7 +13024,7 @@
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B290" t="s">
         <v>863</v>
@@ -13029,7 +13038,7 @@
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B291" t="s">
         <v>866</v>
@@ -13043,21 +13052,21 @@
     </row>
     <row r="292">
       <c r="A292" t="s">
+        <v>676</v>
+      </c>
+      <c r="B292" t="s">
         <v>869</v>
       </c>
-      <c r="B292" t="s">
+      <c r="C292" t="s">
         <v>870</v>
       </c>
-      <c r="C292" t="s">
+      <c r="D292" t="s">
         <v>871</v>
-      </c>
-      <c r="D292" t="s">
-        <v>872</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B293" t="s">
         <v>873</v>
@@ -13071,7 +13080,7 @@
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B294" t="s">
         <v>876</v>
@@ -13085,49 +13094,49 @@
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B295" t="s">
         <v>879</v>
       </c>
       <c r="C295" t="s">
-        <v>756</v>
+        <v>880</v>
       </c>
       <c r="D295" t="s">
-        <v>757</v>
+        <v>881</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B296" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="C296" t="s">
-        <v>711</v>
+        <v>759</v>
       </c>
       <c r="D296" t="s">
-        <v>712</v>
+        <v>760</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B297" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C297" t="s">
-        <v>882</v>
+        <v>714</v>
       </c>
       <c r="D297" t="s">
-        <v>883</v>
+        <v>715</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B298" t="s">
         <v>884</v>
@@ -13141,7 +13150,7 @@
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B299" t="s">
         <v>887</v>
@@ -13155,7 +13164,7 @@
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B300" t="s">
         <v>890</v>
@@ -13169,7 +13178,7 @@
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B301" t="s">
         <v>893</v>
@@ -13183,7 +13192,7 @@
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B302" t="s">
         <v>896</v>
@@ -13197,7 +13206,7 @@
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B303" t="s">
         <v>899</v>
@@ -13211,7 +13220,7 @@
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B304" t="s">
         <v>902</v>
@@ -13225,7 +13234,7 @@
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B305" t="s">
         <v>905</v>
@@ -13239,49 +13248,49 @@
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B306" t="s">
         <v>908</v>
       </c>
       <c r="C306" t="s">
-        <v>768</v>
+        <v>909</v>
       </c>
       <c r="D306" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B307" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C307" t="s">
         <v>771</v>
       </c>
       <c r="D307" t="s">
-        <v>772</v>
+        <v>912</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>911</v>
+        <v>872</v>
       </c>
       <c r="B308" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C308" t="s">
-        <v>913</v>
+        <v>774</v>
       </c>
       <c r="D308" t="s">
-        <v>914</v>
+        <v>775</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B309" t="s">
         <v>915</v>
@@ -13295,7 +13304,7 @@
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B310" t="s">
         <v>918</v>
@@ -13309,7 +13318,7 @@
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B311" t="s">
         <v>921</v>
@@ -13323,7 +13332,7 @@
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B312" t="s">
         <v>924</v>
@@ -13337,7 +13346,7 @@
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B313" t="s">
         <v>927</v>
@@ -13351,7 +13360,7 @@
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B314" t="s">
         <v>930</v>
@@ -13365,7 +13374,7 @@
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B315" t="s">
         <v>933</v>
@@ -13379,7 +13388,7 @@
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B316" t="s">
         <v>936</v>
@@ -13393,7 +13402,7 @@
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B317" t="s">
         <v>939</v>
@@ -13407,7 +13416,7 @@
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B318" t="s">
         <v>942</v>
@@ -13421,7 +13430,7 @@
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B319" t="s">
         <v>945</v>
@@ -13435,7 +13444,7 @@
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B320" t="s">
         <v>948</v>
@@ -13449,7 +13458,7 @@
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B321" t="s">
         <v>951</v>
@@ -13463,7 +13472,7 @@
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B322" t="s">
         <v>954</v>
@@ -13477,7 +13486,7 @@
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B323" t="s">
         <v>957</v>
@@ -13491,7 +13500,7 @@
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B324" t="s">
         <v>960</v>
@@ -13505,7 +13514,7 @@
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B325" t="s">
         <v>963</v>
@@ -13519,7 +13528,7 @@
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B326" t="s">
         <v>966</v>
@@ -13533,7 +13542,7 @@
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B327" t="s">
         <v>969</v>
@@ -13547,7 +13556,7 @@
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B328" t="s">
         <v>972</v>
@@ -13561,7 +13570,7 @@
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B329" t="s">
         <v>975</v>
@@ -13575,7 +13584,7 @@
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B330" t="s">
         <v>978</v>
@@ -13589,7 +13598,7 @@
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B331" t="s">
         <v>981</v>
@@ -13603,7 +13612,7 @@
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B332" t="s">
         <v>984</v>
@@ -13617,7 +13626,7 @@
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B333" t="s">
         <v>987</v>
@@ -13631,7 +13640,7 @@
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B334" t="s">
         <v>990</v>
@@ -13645,7 +13654,7 @@
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B335" t="s">
         <v>993</v>
@@ -13659,7 +13668,7 @@
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B336" t="s">
         <v>996</v>
@@ -13673,7 +13682,7 @@
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B337" t="s">
         <v>999</v>
@@ -13687,7 +13696,7 @@
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B338" t="s">
         <v>1002</v>
@@ -13701,7 +13710,7 @@
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B339" t="s">
         <v>1005</v>
@@ -13715,7 +13724,7 @@
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B340" t="s">
         <v>1008</v>
@@ -13729,7 +13738,7 @@
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B341" t="s">
         <v>1011</v>
@@ -13743,7 +13752,7 @@
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B342" t="s">
         <v>1014</v>
@@ -13752,26 +13761,26 @@
         <v>1015</v>
       </c>
       <c r="D342" t="s">
-        <v>968</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B343" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C343" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="D343" t="s">
-        <v>1018</v>
+        <v>971</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B344" t="s">
         <v>1019</v>
@@ -13785,7 +13794,7 @@
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B345" t="s">
         <v>1022</v>
@@ -13799,7 +13808,7 @@
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B346" t="s">
         <v>1025</v>
@@ -13813,7 +13822,7 @@
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B347" t="s">
         <v>1028</v>
@@ -13827,7 +13836,7 @@
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B348" t="s">
         <v>1031</v>
@@ -13841,7 +13850,7 @@
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B349" t="s">
         <v>1034</v>
@@ -13855,7 +13864,7 @@
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B350" t="s">
         <v>1037</v>
@@ -13869,7 +13878,7 @@
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B351" t="s">
         <v>1040</v>
@@ -13883,7 +13892,7 @@
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B352" t="s">
         <v>1043</v>
@@ -13897,7 +13906,7 @@
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B353" t="s">
         <v>1046</v>
@@ -13911,7 +13920,7 @@
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B354" t="s">
         <v>1049</v>
@@ -13925,7 +13934,7 @@
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B355" t="s">
         <v>1052</v>
@@ -13939,7 +13948,7 @@
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B356" t="s">
         <v>1055</v>
@@ -13953,7 +13962,7 @@
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B357" t="s">
         <v>1058</v>
@@ -13967,7 +13976,7 @@
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B358" t="s">
         <v>1061</v>
@@ -13981,7 +13990,7 @@
     </row>
     <row r="359">
       <c r="A359" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B359" t="s">
         <v>1064</v>
@@ -13990,26 +13999,26 @@
         <v>1065</v>
       </c>
       <c r="D359" t="s">
-        <v>1051</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B360" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C360" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D360" t="s">
-        <v>1068</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B361" t="s">
         <v>1069</v>
@@ -14023,7 +14032,7 @@
     </row>
     <row r="362">
       <c r="A362" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B362" t="s">
         <v>1072</v>
@@ -14037,7 +14046,7 @@
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B363" t="s">
         <v>1075</v>
@@ -14051,7 +14060,7 @@
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B364" t="s">
         <v>1078</v>
@@ -14065,7 +14074,7 @@
     </row>
     <row r="365">
       <c r="A365" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B365" t="s">
         <v>1081</v>
@@ -14079,7 +14088,7 @@
     </row>
     <row r="366">
       <c r="A366" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B366" t="s">
         <v>1084</v>
@@ -14093,7 +14102,7 @@
     </row>
     <row r="367">
       <c r="A367" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B367" t="s">
         <v>1087</v>
@@ -14107,7 +14116,7 @@
     </row>
     <row r="368">
       <c r="A368" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B368" t="s">
         <v>1090</v>
@@ -14121,7 +14130,7 @@
     </row>
     <row r="369">
       <c r="A369" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B369" t="s">
         <v>1093</v>
@@ -14135,7 +14144,7 @@
     </row>
     <row r="370">
       <c r="A370" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B370" t="s">
         <v>1096</v>
@@ -14149,35 +14158,35 @@
     </row>
     <row r="371">
       <c r="A371" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B371" t="s">
         <v>1099</v>
       </c>
       <c r="C371" t="s">
-        <v>1079</v>
+        <v>1100</v>
       </c>
       <c r="D371" t="s">
-        <v>1080</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B372" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="C372" t="s">
-        <v>1101</v>
+        <v>1082</v>
       </c>
       <c r="D372" t="s">
-        <v>1102</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B373" t="s">
         <v>1103</v>
@@ -14191,7 +14200,7 @@
     </row>
     <row r="374">
       <c r="A374" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B374" t="s">
         <v>1106</v>
@@ -14205,7 +14214,7 @@
     </row>
     <row r="375">
       <c r="A375" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B375" t="s">
         <v>1109</v>
@@ -14219,7 +14228,7 @@
     </row>
     <row r="376">
       <c r="A376" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B376" t="s">
         <v>1112</v>
@@ -14233,7 +14242,7 @@
     </row>
     <row r="377">
       <c r="A377" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B377" t="s">
         <v>1115</v>
@@ -14247,7 +14256,7 @@
     </row>
     <row r="378">
       <c r="A378" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B378" t="s">
         <v>1118</v>
@@ -14261,27 +14270,27 @@
     </row>
     <row r="379">
       <c r="A379" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B379" t="s">
         <v>1121</v>
       </c>
       <c r="C379" t="s">
-        <v>246</v>
+        <v>1122</v>
       </c>
       <c r="D379" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B380" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C380" t="s">
-        <v>1124</v>
+        <v>246</v>
       </c>
       <c r="D380" t="s">
         <v>1125</v>
@@ -14289,7 +14298,7 @@
     </row>
     <row r="381">
       <c r="A381" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B381" t="s">
         <v>1126</v>
@@ -14303,7 +14312,7 @@
     </row>
     <row r="382">
       <c r="A382" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B382" t="s">
         <v>1129</v>
@@ -14317,7 +14326,7 @@
     </row>
     <row r="383">
       <c r="A383" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B383" t="s">
         <v>1132</v>
@@ -14331,7 +14340,7 @@
     </row>
     <row r="384">
       <c r="A384" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B384" t="s">
         <v>1135</v>
@@ -14345,7 +14354,7 @@
     </row>
     <row r="385">
       <c r="A385" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B385" t="s">
         <v>1138</v>
@@ -14359,7 +14368,7 @@
     </row>
     <row r="386">
       <c r="A386" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B386" t="s">
         <v>1141</v>
@@ -14373,7 +14382,7 @@
     </row>
     <row r="387">
       <c r="A387" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B387" t="s">
         <v>1144</v>
@@ -14387,7 +14396,7 @@
     </row>
     <row r="388">
       <c r="A388" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B388" t="s">
         <v>1147</v>
@@ -14401,7 +14410,7 @@
     </row>
     <row r="389">
       <c r="A389" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B389" t="s">
         <v>1150</v>
@@ -14415,7 +14424,7 @@
     </row>
     <row r="390">
       <c r="A390" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B390" t="s">
         <v>1153</v>
@@ -14429,35 +14438,35 @@
     </row>
     <row r="391">
       <c r="A391" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B391" t="s">
         <v>1156</v>
       </c>
       <c r="C391" t="s">
-        <v>967</v>
+        <v>1157</v>
       </c>
       <c r="D391" t="s">
-        <v>968</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B392" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="C392" t="s">
-        <v>1158</v>
+        <v>970</v>
       </c>
       <c r="D392" t="s">
-        <v>1159</v>
+        <v>971</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B393" t="s">
         <v>1160</v>
@@ -14471,7 +14480,7 @@
     </row>
     <row r="394">
       <c r="A394" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B394" t="s">
         <v>1163</v>
@@ -14485,7 +14494,7 @@
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B395" t="s">
         <v>1166</v>
@@ -14499,7 +14508,7 @@
     </row>
     <row r="396">
       <c r="A396" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B396" t="s">
         <v>1169</v>
@@ -14513,27 +14522,27 @@
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B397" t="s">
         <v>1172</v>
       </c>
       <c r="C397" t="s">
-        <v>249</v>
+        <v>1173</v>
       </c>
       <c r="D397" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B398" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="C398" t="s">
-        <v>1175</v>
+        <v>249</v>
       </c>
       <c r="D398" t="s">
         <v>1176</v>
@@ -14541,7 +14550,7 @@
     </row>
     <row r="399">
       <c r="A399" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B399" t="s">
         <v>1177</v>
@@ -14555,7 +14564,7 @@
     </row>
     <row r="400">
       <c r="A400" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B400" t="s">
         <v>1180</v>
@@ -14569,7 +14578,7 @@
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B401" t="s">
         <v>1183</v>
@@ -14583,7 +14592,7 @@
     </row>
     <row r="402">
       <c r="A402" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B402" t="s">
         <v>1186</v>
@@ -14597,7 +14606,7 @@
     </row>
     <row r="403">
       <c r="A403" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B403" t="s">
         <v>1189</v>
@@ -14611,7 +14620,7 @@
     </row>
     <row r="404">
       <c r="A404" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B404" t="s">
         <v>1192</v>
@@ -14625,7 +14634,7 @@
     </row>
     <row r="405">
       <c r="A405" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B405" t="s">
         <v>1195</v>
@@ -14639,7 +14648,7 @@
     </row>
     <row r="406">
       <c r="A406" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B406" t="s">
         <v>1198</v>
@@ -14653,7 +14662,7 @@
     </row>
     <row r="407">
       <c r="A407" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B407" t="s">
         <v>1201</v>
@@ -14667,7 +14676,7 @@
     </row>
     <row r="408">
       <c r="A408" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B408" t="s">
         <v>1204</v>
@@ -14681,7 +14690,7 @@
     </row>
     <row r="409">
       <c r="A409" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B409" t="s">
         <v>1207</v>
@@ -14695,7 +14704,7 @@
     </row>
     <row r="410">
       <c r="A410" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B410" t="s">
         <v>1210</v>
@@ -14709,7 +14718,7 @@
     </row>
     <row r="411">
       <c r="A411" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B411" t="s">
         <v>1213</v>
@@ -14723,7 +14732,7 @@
     </row>
     <row r="412">
       <c r="A412" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B412" t="s">
         <v>1216</v>
@@ -14737,7 +14746,7 @@
     </row>
     <row r="413">
       <c r="A413" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B413" t="s">
         <v>1219</v>
@@ -14751,7 +14760,7 @@
     </row>
     <row r="414">
       <c r="A414" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B414" t="s">
         <v>1222</v>
@@ -14765,7 +14774,7 @@
     </row>
     <row r="415">
       <c r="A415" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B415" t="s">
         <v>1225</v>
@@ -14779,7 +14788,7 @@
     </row>
     <row r="416">
       <c r="A416" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B416" t="s">
         <v>1228</v>
@@ -14793,7 +14802,7 @@
     </row>
     <row r="417">
       <c r="A417" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B417" t="s">
         <v>1231</v>
@@ -14807,7 +14816,7 @@
     </row>
     <row r="418">
       <c r="A418" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B418" t="s">
         <v>1234</v>
@@ -14821,7 +14830,7 @@
     </row>
     <row r="419">
       <c r="A419" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B419" t="s">
         <v>1237</v>
@@ -14835,7 +14844,7 @@
     </row>
     <row r="420">
       <c r="A420" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B420" t="s">
         <v>1240</v>
@@ -14844,26 +14853,26 @@
         <v>1241</v>
       </c>
       <c r="D420" t="s">
-        <v>577</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B421" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="C421" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="D421" t="s">
-        <v>1244</v>
+        <v>580</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B422" t="s">
         <v>1245</v>
@@ -14877,7 +14886,7 @@
     </row>
     <row r="423">
       <c r="A423" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B423" t="s">
         <v>1248</v>
@@ -14891,7 +14900,7 @@
     </row>
     <row r="424">
       <c r="A424" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B424" t="s">
         <v>1251</v>
@@ -14905,7 +14914,7 @@
     </row>
     <row r="425">
       <c r="A425" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B425" t="s">
         <v>1254</v>
@@ -14919,7 +14928,7 @@
     </row>
     <row r="426">
       <c r="A426" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B426" t="s">
         <v>1257</v>
@@ -14933,7 +14942,7 @@
     </row>
     <row r="427">
       <c r="A427" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B427" t="s">
         <v>1260</v>
@@ -14947,49 +14956,49 @@
     </row>
     <row r="428">
       <c r="A428" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B428" t="s">
         <v>1263</v>
       </c>
       <c r="C428" t="s">
-        <v>6</v>
+        <v>1264</v>
       </c>
       <c r="D428" t="s">
-        <v>549</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B429" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="C429" t="s">
-        <v>1265</v>
+        <v>6</v>
       </c>
       <c r="D429" t="s">
-        <v>614</v>
+        <v>549</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B430" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="C430" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="D430" t="s">
-        <v>1268</v>
+        <v>617</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B431" t="s">
         <v>1269</v>
@@ -15003,7 +15012,7 @@
     </row>
     <row r="432">
       <c r="A432" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B432" t="s">
         <v>1272</v>
@@ -15017,7 +15026,7 @@
     </row>
     <row r="433">
       <c r="A433" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B433" t="s">
         <v>1275</v>
@@ -15031,7 +15040,7 @@
     </row>
     <row r="434">
       <c r="A434" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B434" t="s">
         <v>1278</v>
@@ -15045,7 +15054,7 @@
     </row>
     <row r="435">
       <c r="A435" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B435" t="s">
         <v>1281</v>
@@ -15059,7 +15068,7 @@
     </row>
     <row r="436">
       <c r="A436" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B436" t="s">
         <v>1284</v>
@@ -15073,7 +15082,7 @@
     </row>
     <row r="437">
       <c r="A437" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B437" t="s">
         <v>1287</v>
@@ -15087,7 +15096,7 @@
     </row>
     <row r="438">
       <c r="A438" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B438" t="s">
         <v>1290</v>
@@ -15096,82 +15105,82 @@
         <v>1291</v>
       </c>
       <c r="D438" t="s">
-        <v>989</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B439" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="C439" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="D439" t="s">
-        <v>1294</v>
+        <v>992</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B440" t="s">
         <v>1295</v>
       </c>
       <c r="C440" t="s">
-        <v>379</v>
+        <v>1296</v>
       </c>
       <c r="D440" t="s">
-        <v>380</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B441" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="C441" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D441" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B442" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="C442" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="D442" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B443" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="C443" t="s">
-        <v>1299</v>
+        <v>399</v>
       </c>
       <c r="D443" t="s">
-        <v>1300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B444" t="s">
         <v>1301</v>
@@ -15185,7 +15194,7 @@
     </row>
     <row r="445">
       <c r="A445" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B445" t="s">
         <v>1304</v>
@@ -15199,7 +15208,7 @@
     </row>
     <row r="446">
       <c r="A446" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B446" t="s">
         <v>1307</v>
@@ -15213,7 +15222,7 @@
     </row>
     <row r="447">
       <c r="A447" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B447" t="s">
         <v>1310</v>
@@ -15227,7 +15236,7 @@
     </row>
     <row r="448">
       <c r="A448" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B448" t="s">
         <v>1313</v>
@@ -15241,7 +15250,7 @@
     </row>
     <row r="449">
       <c r="A449" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B449" t="s">
         <v>1316</v>
@@ -15255,7 +15264,7 @@
     </row>
     <row r="450">
       <c r="A450" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B450" t="s">
         <v>1319</v>
@@ -15269,7 +15278,7 @@
     </row>
     <row r="451">
       <c r="A451" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B451" t="s">
         <v>1322</v>
@@ -15283,7 +15292,7 @@
     </row>
     <row r="452">
       <c r="A452" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B452" t="s">
         <v>1325</v>
@@ -15297,7 +15306,7 @@
     </row>
     <row r="453">
       <c r="A453" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B453" t="s">
         <v>1328</v>
@@ -15311,7 +15320,7 @@
     </row>
     <row r="454">
       <c r="A454" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B454" t="s">
         <v>1331</v>
@@ -15325,7 +15334,7 @@
     </row>
     <row r="455">
       <c r="A455" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B455" t="s">
         <v>1334</v>
@@ -15339,7 +15348,7 @@
     </row>
     <row r="456">
       <c r="A456" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B456" t="s">
         <v>1337</v>
@@ -15353,7 +15362,7 @@
     </row>
     <row r="457">
       <c r="A457" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B457" t="s">
         <v>1340</v>
@@ -15367,7 +15376,7 @@
     </row>
     <row r="458">
       <c r="A458" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B458" t="s">
         <v>1343</v>
@@ -15381,7 +15390,7 @@
     </row>
     <row r="459">
       <c r="A459" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B459" t="s">
         <v>1346</v>
@@ -15395,7 +15404,7 @@
     </row>
     <row r="460">
       <c r="A460" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B460" t="s">
         <v>1349</v>
@@ -15409,7 +15418,7 @@
     </row>
     <row r="461">
       <c r="A461" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B461" t="s">
         <v>1352</v>
@@ -15423,7 +15432,7 @@
     </row>
     <row r="462">
       <c r="A462" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B462" t="s">
         <v>1355</v>
@@ -15437,7 +15446,7 @@
     </row>
     <row r="463">
       <c r="A463" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B463" t="s">
         <v>1358</v>
@@ -15451,7 +15460,7 @@
     </row>
     <row r="464">
       <c r="A464" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B464" t="s">
         <v>1361</v>
@@ -15465,7 +15474,7 @@
     </row>
     <row r="465">
       <c r="A465" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B465" t="s">
         <v>1364</v>
@@ -15479,7 +15488,7 @@
     </row>
     <row r="466">
       <c r="A466" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B466" t="s">
         <v>1367</v>
@@ -15488,26 +15497,26 @@
         <v>1368</v>
       </c>
       <c r="D466" t="s">
-        <v>950</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B467" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="C467" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="D467" t="s">
-        <v>1371</v>
+        <v>953</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B468" t="s">
         <v>1372</v>
@@ -15521,7 +15530,7 @@
     </row>
     <row r="469">
       <c r="A469" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B469" t="s">
         <v>1375</v>
@@ -15535,7 +15544,7 @@
     </row>
     <row r="470">
       <c r="A470" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B470" t="s">
         <v>1378</v>
@@ -15549,7 +15558,7 @@
     </row>
     <row r="471">
       <c r="A471" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B471" t="s">
         <v>1381</v>
@@ -15563,7 +15572,7 @@
     </row>
     <row r="472">
       <c r="A472" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B472" t="s">
         <v>1384</v>
@@ -15577,7 +15586,7 @@
     </row>
     <row r="473">
       <c r="A473" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B473" t="s">
         <v>1387</v>
@@ -15591,7 +15600,7 @@
     </row>
     <row r="474">
       <c r="A474" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B474" t="s">
         <v>1390</v>
@@ -15605,7 +15614,7 @@
     </row>
     <row r="475">
       <c r="A475" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B475" t="s">
         <v>1393</v>
@@ -15619,7 +15628,7 @@
     </row>
     <row r="476">
       <c r="A476" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B476" t="s">
         <v>1396</v>
@@ -15633,7 +15642,7 @@
     </row>
     <row r="477">
       <c r="A477" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B477" t="s">
         <v>1399</v>
@@ -15647,7 +15656,7 @@
     </row>
     <row r="478">
       <c r="A478" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B478" t="s">
         <v>1402</v>
@@ -15661,7 +15670,7 @@
     </row>
     <row r="479">
       <c r="A479" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B479" t="s">
         <v>1405</v>
@@ -15675,7 +15684,7 @@
     </row>
     <row r="480">
       <c r="A480" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B480" t="s">
         <v>1408</v>
@@ -15689,27 +15698,27 @@
     </row>
     <row r="481">
       <c r="A481" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B481" t="s">
         <v>1411</v>
       </c>
       <c r="C481" t="s">
-        <v>467</v>
+        <v>1412</v>
       </c>
       <c r="D481" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B482" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="C482" t="s">
-        <v>1414</v>
+        <v>467</v>
       </c>
       <c r="D482" t="s">
         <v>1415</v>
@@ -15717,7 +15726,7 @@
     </row>
     <row r="483">
       <c r="A483" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B483" t="s">
         <v>1416</v>
@@ -15731,7 +15740,7 @@
     </row>
     <row r="484">
       <c r="A484" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B484" t="s">
         <v>1419</v>
@@ -15745,7 +15754,7 @@
     </row>
     <row r="485">
       <c r="A485" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B485" t="s">
         <v>1422</v>
@@ -15759,49 +15768,49 @@
     </row>
     <row r="486">
       <c r="A486" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B486" t="s">
         <v>1425</v>
       </c>
       <c r="C486" t="s">
-        <v>988</v>
+        <v>1426</v>
       </c>
       <c r="D486" t="s">
-        <v>989</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B487" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="C487" t="s">
-        <v>1427</v>
+        <v>991</v>
       </c>
       <c r="D487" t="s">
-        <v>462</v>
+        <v>992</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B488" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="C488" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="D488" t="s">
-        <v>1430</v>
+        <v>462</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B489" t="s">
         <v>1431</v>
@@ -15815,7 +15824,7 @@
     </row>
     <row r="490">
       <c r="A490" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B490" t="s">
         <v>1434</v>
@@ -15829,27 +15838,27 @@
     </row>
     <row r="491">
       <c r="A491" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B491" t="s">
         <v>1437</v>
       </c>
       <c r="C491" t="s">
-        <v>1235</v>
+        <v>1438</v>
       </c>
       <c r="D491" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B492" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="C492" t="s">
-        <v>1440</v>
+        <v>1238</v>
       </c>
       <c r="D492" t="s">
         <v>1441</v>
@@ -15857,35 +15866,35 @@
     </row>
     <row r="493">
       <c r="A493" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B493" t="s">
         <v>1442</v>
       </c>
       <c r="C493" t="s">
-        <v>521</v>
+        <v>1443</v>
       </c>
       <c r="D493" t="s">
-        <v>522</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B494" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="C494" t="s">
-        <v>1444</v>
+        <v>521</v>
       </c>
       <c r="D494" t="s">
-        <v>1445</v>
+        <v>522</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B495" t="s">
         <v>1446</v>
@@ -15899,7 +15908,7 @@
     </row>
     <row r="496">
       <c r="A496" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B496" t="s">
         <v>1449</v>
@@ -15913,7 +15922,7 @@
     </row>
     <row r="497">
       <c r="A497" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B497" t="s">
         <v>1452</v>
@@ -15927,7 +15936,7 @@
     </row>
     <row r="498">
       <c r="A498" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B498" t="s">
         <v>1455</v>
@@ -15941,7 +15950,7 @@
     </row>
     <row r="499">
       <c r="A499" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B499" t="s">
         <v>1458</v>
@@ -15955,7 +15964,7 @@
     </row>
     <row r="500">
       <c r="A500" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B500" t="s">
         <v>1461</v>
@@ -15969,7 +15978,7 @@
     </row>
     <row r="501">
       <c r="A501" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B501" t="s">
         <v>1464</v>
@@ -15983,7 +15992,7 @@
     </row>
     <row r="502">
       <c r="A502" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B502" t="s">
         <v>1467</v>
@@ -15997,7 +16006,7 @@
     </row>
     <row r="503">
       <c r="A503" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B503" t="s">
         <v>1470</v>
@@ -16011,7 +16020,7 @@
     </row>
     <row r="504">
       <c r="A504" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B504" t="s">
         <v>1473</v>
@@ -16025,7 +16034,7 @@
     </row>
     <row r="505">
       <c r="A505" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B505" t="s">
         <v>1476</v>
@@ -16039,7 +16048,7 @@
     </row>
     <row r="506">
       <c r="A506" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B506" t="s">
         <v>1479</v>
@@ -16053,7 +16062,7 @@
     </row>
     <row r="507">
       <c r="A507" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B507" t="s">
         <v>1482</v>
@@ -16067,7 +16076,7 @@
     </row>
     <row r="508">
       <c r="A508" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B508" t="s">
         <v>1485</v>
@@ -16081,7 +16090,7 @@
     </row>
     <row r="509">
       <c r="A509" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B509" t="s">
         <v>1488</v>
@@ -16095,7 +16104,7 @@
     </row>
     <row r="510">
       <c r="A510" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B510" t="s">
         <v>1491</v>
@@ -16109,7 +16118,7 @@
     </row>
     <row r="511">
       <c r="A511" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B511" t="s">
         <v>1494</v>
@@ -16123,7 +16132,7 @@
     </row>
     <row r="512">
       <c r="A512" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B512" t="s">
         <v>1497</v>
@@ -16137,7 +16146,7 @@
     </row>
     <row r="513">
       <c r="A513" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B513" t="s">
         <v>1500</v>
@@ -16151,69 +16160,69 @@
     </row>
     <row r="514">
       <c r="A514" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B514" t="s">
         <v>1503</v>
       </c>
       <c r="C514" t="s">
-        <v>1417</v>
+        <v>1504</v>
       </c>
       <c r="D514" t="s">
-        <v>1418</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B515" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="C515" t="s">
-        <v>1291</v>
+        <v>1420</v>
       </c>
       <c r="D515" t="s">
-        <v>989</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B516" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="C516" t="s">
-        <v>1506</v>
+        <v>1294</v>
       </c>
       <c r="D516" t="s">
-        <v>1507</v>
+        <v>992</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B517" t="s">
         <v>1508</v>
       </c>
       <c r="C517" t="s">
-        <v>1388</v>
+        <v>1509</v>
       </c>
       <c r="D517" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B518" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="C518" t="s">
-        <v>1511</v>
+        <v>1391</v>
       </c>
       <c r="D518" t="s">
         <v>1512</v>
@@ -16221,7 +16230,7 @@
     </row>
     <row r="519">
       <c r="A519" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B519" t="s">
         <v>1513</v>
@@ -16235,55 +16244,55 @@
     </row>
     <row r="520">
       <c r="A520" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B520" t="s">
         <v>1516</v>
       </c>
       <c r="C520" t="s">
-        <v>1417</v>
+        <v>1517</v>
       </c>
       <c r="D520" t="s">
-        <v>1418</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B521" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="C521" t="s">
-        <v>1518</v>
+        <v>1420</v>
       </c>
       <c r="D521" t="s">
-        <v>1519</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B522" t="s">
         <v>1520</v>
       </c>
       <c r="C522" t="s">
-        <v>1238</v>
+        <v>1521</v>
       </c>
       <c r="D522" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B523" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="C523" t="s">
-        <v>1523</v>
+        <v>1241</v>
       </c>
       <c r="D523" t="s">
         <v>1524</v>
@@ -16291,7 +16300,7 @@
     </row>
     <row r="524">
       <c r="A524" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B524" t="s">
         <v>1525</v>
@@ -16305,7 +16314,7 @@
     </row>
     <row r="525">
       <c r="A525" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B525" t="s">
         <v>1528</v>
@@ -16319,7 +16328,7 @@
     </row>
     <row r="526">
       <c r="A526" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B526" t="s">
         <v>1531</v>
@@ -16333,7 +16342,7 @@
     </row>
     <row r="527">
       <c r="A527" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B527" t="s">
         <v>1534</v>
@@ -16347,7 +16356,7 @@
     </row>
     <row r="528">
       <c r="A528" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B528" t="s">
         <v>1537</v>
@@ -16361,7 +16370,7 @@
     </row>
     <row r="529">
       <c r="A529" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B529" t="s">
         <v>1540</v>
@@ -16375,7 +16384,7 @@
     </row>
     <row r="530">
       <c r="A530" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B530" t="s">
         <v>1543</v>
@@ -16389,7 +16398,7 @@
     </row>
     <row r="531">
       <c r="A531" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B531" t="s">
         <v>1546</v>
@@ -16403,7 +16412,7 @@
     </row>
     <row r="532">
       <c r="A532" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B532" t="s">
         <v>1549</v>
@@ -16417,35 +16426,35 @@
     </row>
     <row r="533">
       <c r="A533" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B533" t="s">
         <v>1552</v>
       </c>
       <c r="C533" t="s">
-        <v>1547</v>
+        <v>1553</v>
       </c>
       <c r="D533" t="s">
-        <v>1548</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B534" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="C534" t="s">
-        <v>1554</v>
+        <v>1550</v>
       </c>
       <c r="D534" t="s">
-        <v>1555</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B535" t="s">
         <v>1556</v>
@@ -16459,7 +16468,7 @@
     </row>
     <row r="536">
       <c r="A536" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B536" t="s">
         <v>1559</v>
@@ -16473,7 +16482,7 @@
     </row>
     <row r="537">
       <c r="A537" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B537" t="s">
         <v>1562</v>
@@ -16487,7 +16496,7 @@
     </row>
     <row r="538">
       <c r="A538" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B538" t="s">
         <v>1565</v>
@@ -16501,7 +16510,7 @@
     </row>
     <row r="539">
       <c r="A539" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B539" t="s">
         <v>1568</v>
@@ -16515,35 +16524,35 @@
     </row>
     <row r="540">
       <c r="A540" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B540" t="s">
         <v>1571</v>
       </c>
       <c r="C540" t="s">
-        <v>4</v>
+        <v>1572</v>
       </c>
       <c r="D540" t="s">
-        <v>31</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B541" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="C541" t="s">
-        <v>1573</v>
+        <v>4</v>
       </c>
       <c r="D541" t="s">
-        <v>1574</v>
+        <v>31</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B542" t="s">
         <v>1575</v>
@@ -16557,7 +16566,7 @@
     </row>
     <row r="543">
       <c r="A543" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B543" t="s">
         <v>1578</v>
@@ -16571,7 +16580,7 @@
     </row>
     <row r="544">
       <c r="A544" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B544" t="s">
         <v>1581</v>
@@ -16585,7 +16594,7 @@
     </row>
     <row r="545">
       <c r="A545" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B545" t="s">
         <v>1584</v>
@@ -16599,7 +16608,7 @@
     </row>
     <row r="546">
       <c r="A546" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B546" t="s">
         <v>1587</v>
@@ -16613,35 +16622,35 @@
     </row>
     <row r="547">
       <c r="A547" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B547" t="s">
         <v>1590</v>
       </c>
       <c r="C547" t="s">
-        <v>252</v>
+        <v>1591</v>
       </c>
       <c r="D547" t="s">
-        <v>253</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B548" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="C548" t="s">
-        <v>1592</v>
+        <v>252</v>
       </c>
       <c r="D548" t="s">
-        <v>1593</v>
+        <v>253</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B549" t="s">
         <v>1594</v>
@@ -16655,7 +16664,7 @@
     </row>
     <row r="550">
       <c r="A550" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B550" t="s">
         <v>1597</v>
@@ -16669,7 +16678,7 @@
     </row>
     <row r="551">
       <c r="A551" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B551" t="s">
         <v>1600</v>
@@ -16683,7 +16692,7 @@
     </row>
     <row r="552">
       <c r="A552" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B552" t="s">
         <v>1603</v>
@@ -16697,35 +16706,35 @@
     </row>
     <row r="553">
       <c r="A553" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B553" t="s">
         <v>1606</v>
       </c>
       <c r="C553" t="s">
-        <v>1579</v>
+        <v>1607</v>
       </c>
       <c r="D553" t="s">
-        <v>1580</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B554" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="C554" t="s">
-        <v>1608</v>
+        <v>1582</v>
       </c>
       <c r="D554" t="s">
-        <v>1609</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B555" t="s">
         <v>1610</v>
@@ -16739,7 +16748,7 @@
     </row>
     <row r="556">
       <c r="A556" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B556" t="s">
         <v>1613</v>
@@ -16753,7 +16762,7 @@
     </row>
     <row r="557">
       <c r="A557" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="B557" t="s">
         <v>1616</v>
@@ -16767,35 +16776,35 @@
     </row>
     <row r="558">
       <c r="A558" t="s">
+        <v>914</v>
+      </c>
+      <c r="B558" t="s">
         <v>1619</v>
       </c>
-      <c r="B558" t="s">
+      <c r="C558" t="s">
         <v>1620</v>
       </c>
-      <c r="C558" t="s">
-        <v>921</v>
-      </c>
       <c r="D558" t="s">
-        <v>923</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B559" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="C559" t="s">
-        <v>1622</v>
+        <v>924</v>
       </c>
       <c r="D559" t="s">
-        <v>1623</v>
+        <v>926</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B560" t="s">
         <v>1624</v>
@@ -16809,35 +16818,35 @@
     </row>
     <row r="561">
       <c r="A561" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B561" t="s">
         <v>1627</v>
       </c>
       <c r="C561" t="s">
-        <v>7</v>
+        <v>1628</v>
       </c>
       <c r="D561" t="s">
-        <v>1451</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B562" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="C562" t="s">
-        <v>1629</v>
+        <v>7</v>
       </c>
       <c r="D562" t="s">
-        <v>1630</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B563" t="s">
         <v>1631</v>
@@ -16851,7 +16860,7 @@
     </row>
     <row r="564">
       <c r="A564" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B564" t="s">
         <v>1634</v>
@@ -16865,7 +16874,7 @@
     </row>
     <row r="565">
       <c r="A565" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B565" t="s">
         <v>1637</v>
@@ -16879,7 +16888,7 @@
     </row>
     <row r="566">
       <c r="A566" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B566" t="s">
         <v>1640</v>
@@ -16893,7 +16902,7 @@
     </row>
     <row r="567">
       <c r="A567" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B567" t="s">
         <v>1643</v>
@@ -16907,7 +16916,7 @@
     </row>
     <row r="568">
       <c r="A568" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B568" t="s">
         <v>1646</v>
@@ -16921,7 +16930,7 @@
     </row>
     <row r="569">
       <c r="A569" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B569" t="s">
         <v>1649</v>
@@ -16935,7 +16944,7 @@
     </row>
     <row r="570">
       <c r="A570" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B570" t="s">
         <v>1652</v>
@@ -16949,7 +16958,7 @@
     </row>
     <row r="571">
       <c r="A571" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B571" t="s">
         <v>1655</v>
@@ -16963,7 +16972,7 @@
     </row>
     <row r="572">
       <c r="A572" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B572" t="s">
         <v>1658</v>
@@ -16977,7 +16986,7 @@
     </row>
     <row r="573">
       <c r="A573" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B573" t="s">
         <v>1661</v>
@@ -16991,7 +17000,7 @@
     </row>
     <row r="574">
       <c r="A574" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B574" t="s">
         <v>1664</v>
@@ -17005,7 +17014,7 @@
     </row>
     <row r="575">
       <c r="A575" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B575" t="s">
         <v>1667</v>
@@ -17019,7 +17028,7 @@
     </row>
     <row r="576">
       <c r="A576" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B576" t="s">
         <v>1670</v>
@@ -17033,7 +17042,7 @@
     </row>
     <row r="577">
       <c r="A577" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B577" t="s">
         <v>1673</v>
@@ -17047,7 +17056,7 @@
     </row>
     <row r="578">
       <c r="A578" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B578" t="s">
         <v>1676</v>
@@ -17061,7 +17070,7 @@
     </row>
     <row r="579">
       <c r="A579" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B579" t="s">
         <v>1679</v>
@@ -17075,7 +17084,7 @@
     </row>
     <row r="580">
       <c r="A580" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B580" t="s">
         <v>1682</v>
@@ -17089,7 +17098,7 @@
     </row>
     <row r="581">
       <c r="A581" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B581" t="s">
         <v>1685</v>
@@ -17103,7 +17112,7 @@
     </row>
     <row r="582">
       <c r="A582" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B582" t="s">
         <v>1688</v>
@@ -17117,7 +17126,7 @@
     </row>
     <row r="583">
       <c r="A583" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B583" t="s">
         <v>1691</v>
@@ -17131,27 +17140,27 @@
     </row>
     <row r="584">
       <c r="A584" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B584" t="s">
         <v>1694</v>
       </c>
       <c r="C584" t="s">
-        <v>874</v>
+        <v>1695</v>
       </c>
       <c r="D584" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B585" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="C585" t="s">
-        <v>1697</v>
+        <v>877</v>
       </c>
       <c r="D585" t="s">
         <v>1698</v>
@@ -17159,7 +17168,7 @@
     </row>
     <row r="586">
       <c r="A586" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B586" t="s">
         <v>1699</v>
@@ -17173,7 +17182,7 @@
     </row>
     <row r="587">
       <c r="A587" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B587" t="s">
         <v>1702</v>
@@ -17187,7 +17196,7 @@
     </row>
     <row r="588">
       <c r="A588" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B588" t="s">
         <v>1705</v>
@@ -17201,7 +17210,7 @@
     </row>
     <row r="589">
       <c r="A589" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B589" t="s">
         <v>1708</v>
@@ -17215,7 +17224,7 @@
     </row>
     <row r="590">
       <c r="A590" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B590" t="s">
         <v>1711</v>
@@ -17229,7 +17238,7 @@
     </row>
     <row r="591">
       <c r="A591" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B591" t="s">
         <v>1714</v>
@@ -17243,7 +17252,7 @@
     </row>
     <row r="592">
       <c r="A592" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B592" t="s">
         <v>1717</v>
@@ -17257,7 +17266,7 @@
     </row>
     <row r="593">
       <c r="A593" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B593" t="s">
         <v>1720</v>
@@ -17271,7 +17280,7 @@
     </row>
     <row r="594">
       <c r="A594" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B594" t="s">
         <v>1723</v>
@@ -17285,7 +17294,7 @@
     </row>
     <row r="595">
       <c r="A595" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B595" t="s">
         <v>1726</v>
@@ -17299,7 +17308,7 @@
     </row>
     <row r="596">
       <c r="A596" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B596" t="s">
         <v>1729</v>
@@ -17313,7 +17322,7 @@
     </row>
     <row r="597">
       <c r="A597" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B597" t="s">
         <v>1732</v>
@@ -17327,7 +17336,7 @@
     </row>
     <row r="598">
       <c r="A598" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B598" t="s">
         <v>1735</v>
@@ -17341,7 +17350,7 @@
     </row>
     <row r="599">
       <c r="A599" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B599" t="s">
         <v>1738</v>
@@ -17355,7 +17364,7 @@
     </row>
     <row r="600">
       <c r="A600" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B600" t="s">
         <v>1741</v>
@@ -17369,7 +17378,7 @@
     </row>
     <row r="601">
       <c r="A601" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B601" t="s">
         <v>1744</v>
@@ -17383,7 +17392,7 @@
     </row>
     <row r="602">
       <c r="A602" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B602" t="s">
         <v>1747</v>
@@ -17397,7 +17406,7 @@
     </row>
     <row r="603">
       <c r="A603" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B603" t="s">
         <v>1750</v>
@@ -17411,7 +17420,7 @@
     </row>
     <row r="604">
       <c r="A604" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B604" t="s">
         <v>1753</v>
@@ -17425,55 +17434,55 @@
     </row>
     <row r="605">
       <c r="A605" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B605" t="s">
         <v>1756</v>
       </c>
       <c r="C605" t="s">
-        <v>934</v>
+        <v>1757</v>
       </c>
       <c r="D605" t="s">
-        <v>935</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B606" t="s">
-        <v>1757</v>
+        <v>1759</v>
       </c>
       <c r="C606" t="s">
-        <v>132</v>
+        <v>937</v>
       </c>
       <c r="D606" t="s">
-        <v>133</v>
+        <v>938</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B607" t="s">
-        <v>1758</v>
+        <v>1760</v>
       </c>
       <c r="C607" t="s">
-        <v>605</v>
+        <v>132</v>
       </c>
       <c r="D607" t="s">
-        <v>1759</v>
+        <v>133</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B608" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="C608" t="s">
-        <v>1761</v>
+        <v>608</v>
       </c>
       <c r="D608" t="s">
         <v>1762</v>
@@ -17481,27 +17490,27 @@
     </row>
     <row r="609">
       <c r="A609" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B609" t="s">
         <v>1763</v>
       </c>
       <c r="C609" t="s">
-        <v>336</v>
+        <v>1764</v>
       </c>
       <c r="D609" t="s">
-        <v>337</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B610" t="s">
-        <v>1764</v>
+        <v>1766</v>
       </c>
       <c r="C610" t="s">
-        <v>1765</v>
+        <v>336</v>
       </c>
       <c r="D610" t="s">
         <v>337</v>
@@ -17509,21 +17518,21 @@
     </row>
     <row r="611">
       <c r="A611" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B611" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="C611" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="D611" t="s">
-        <v>1768</v>
+        <v>337</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B612" t="s">
         <v>1769</v>
@@ -17537,7 +17546,7 @@
     </row>
     <row r="613">
       <c r="A613" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B613" t="s">
         <v>1772</v>
@@ -17551,7 +17560,7 @@
     </row>
     <row r="614">
       <c r="A614" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B614" t="s">
         <v>1775</v>
@@ -17560,26 +17569,26 @@
         <v>1776</v>
       </c>
       <c r="D614" t="s">
-        <v>549</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B615" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="C615" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="D615" t="s">
-        <v>1779</v>
+        <v>549</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B616" t="s">
         <v>1780</v>
@@ -17593,7 +17602,7 @@
     </row>
     <row r="617">
       <c r="A617" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B617" t="s">
         <v>1783</v>
@@ -17607,7 +17616,7 @@
     </row>
     <row r="618">
       <c r="A618" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B618" t="s">
         <v>1786</v>
@@ -17621,7 +17630,7 @@
     </row>
     <row r="619">
       <c r="A619" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B619" t="s">
         <v>1789</v>
@@ -17635,7 +17644,7 @@
     </row>
     <row r="620">
       <c r="A620" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B620" t="s">
         <v>1792</v>
@@ -17649,7 +17658,7 @@
     </row>
     <row r="621">
       <c r="A621" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B621" t="s">
         <v>1795</v>
@@ -17663,7 +17672,7 @@
     </row>
     <row r="622">
       <c r="A622" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B622" t="s">
         <v>1798</v>
@@ -17677,7 +17686,7 @@
     </row>
     <row r="623">
       <c r="A623" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B623" t="s">
         <v>1801</v>
@@ -17691,7 +17700,7 @@
     </row>
     <row r="624">
       <c r="A624" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B624" t="s">
         <v>1804</v>
@@ -17705,7 +17714,7 @@
     </row>
     <row r="625">
       <c r="A625" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B625" t="s">
         <v>1807</v>
@@ -17719,7 +17728,7 @@
     </row>
     <row r="626">
       <c r="A626" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B626" t="s">
         <v>1810</v>
@@ -17733,7 +17742,7 @@
     </row>
     <row r="627">
       <c r="A627" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B627" t="s">
         <v>1813</v>
@@ -17747,7 +17756,7 @@
     </row>
     <row r="628">
       <c r="A628" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B628" t="s">
         <v>1816</v>
@@ -17761,35 +17770,35 @@
     </row>
     <row r="629">
       <c r="A629" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B629" t="s">
         <v>1819</v>
       </c>
       <c r="C629" t="s">
-        <v>1269</v>
+        <v>1820</v>
       </c>
       <c r="D629" t="s">
-        <v>1271</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B630" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="C630" t="s">
-        <v>1821</v>
+        <v>1272</v>
       </c>
       <c r="D630" t="s">
-        <v>1822</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B631" t="s">
         <v>1823</v>
@@ -17803,7 +17812,7 @@
     </row>
     <row r="632">
       <c r="A632" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B632" t="s">
         <v>1826</v>
@@ -17817,7 +17826,7 @@
     </row>
     <row r="633">
       <c r="A633" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B633" t="s">
         <v>1829</v>
@@ -17831,7 +17840,7 @@
     </row>
     <row r="634">
       <c r="A634" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B634" t="s">
         <v>1832</v>
@@ -17845,7 +17854,7 @@
     </row>
     <row r="635">
       <c r="A635" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B635" t="s">
         <v>1835</v>
@@ -17859,7 +17868,7 @@
     </row>
     <row r="636">
       <c r="A636" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B636" t="s">
         <v>1838</v>
@@ -17873,7 +17882,7 @@
     </row>
     <row r="637">
       <c r="A637" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B637" t="s">
         <v>1841</v>
@@ -17887,7 +17896,7 @@
     </row>
     <row r="638">
       <c r="A638" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B638" t="s">
         <v>1844</v>
@@ -17901,7 +17910,7 @@
     </row>
     <row r="639">
       <c r="A639" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B639" t="s">
         <v>1847</v>
@@ -17915,7 +17924,7 @@
     </row>
     <row r="640">
       <c r="A640" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B640" t="s">
         <v>1850</v>
@@ -17929,7 +17938,7 @@
     </row>
     <row r="641">
       <c r="A641" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B641" t="s">
         <v>1853</v>
@@ -17943,27 +17952,27 @@
     </row>
     <row r="642">
       <c r="A642" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B642" t="s">
         <v>1856</v>
       </c>
       <c r="C642" t="s">
-        <v>1619</v>
+        <v>1857</v>
       </c>
       <c r="D642" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B643" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="C643" t="s">
-        <v>1859</v>
+        <v>1622</v>
       </c>
       <c r="D643" t="s">
         <v>1860</v>
@@ -17971,7 +17980,7 @@
     </row>
     <row r="644">
       <c r="A644" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B644" t="s">
         <v>1861</v>
@@ -17985,7 +17994,7 @@
     </row>
     <row r="645">
       <c r="A645" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B645" t="s">
         <v>1864</v>
@@ -17999,7 +18008,7 @@
     </row>
     <row r="646">
       <c r="A646" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B646" t="s">
         <v>1867</v>
@@ -18013,7 +18022,7 @@
     </row>
     <row r="647">
       <c r="A647" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B647" t="s">
         <v>1870</v>
@@ -18027,7 +18036,7 @@
     </row>
     <row r="648">
       <c r="A648" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B648" t="s">
         <v>1873</v>
@@ -18041,7 +18050,7 @@
     </row>
     <row r="649">
       <c r="A649" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B649" t="s">
         <v>1876</v>
@@ -18055,49 +18064,49 @@
     </row>
     <row r="650">
       <c r="A650" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B650" t="s">
         <v>1879</v>
       </c>
       <c r="C650" t="s">
-        <v>1547</v>
+        <v>1880</v>
       </c>
       <c r="D650" t="s">
-        <v>1548</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B651" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="C651" t="s">
-        <v>1341</v>
+        <v>1550</v>
       </c>
       <c r="D651" t="s">
-        <v>1342</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B652" t="s">
-        <v>1881</v>
+        <v>1883</v>
       </c>
       <c r="C652" t="s">
-        <v>1882</v>
+        <v>1344</v>
       </c>
       <c r="D652" t="s">
-        <v>1883</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B653" t="s">
         <v>1884</v>
@@ -18111,7 +18120,7 @@
     </row>
     <row r="654">
       <c r="A654" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B654" t="s">
         <v>1887</v>
@@ -18125,7 +18134,7 @@
     </row>
     <row r="655">
       <c r="A655" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B655" t="s">
         <v>1890</v>
@@ -18139,63 +18148,63 @@
     </row>
     <row r="656">
       <c r="A656" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B656" t="s">
         <v>1893</v>
       </c>
-      <c r="B656" t="s">
+      <c r="C656" t="s">
         <v>1894</v>
       </c>
-      <c r="C656" t="s">
+      <c r="D656" t="s">
         <v>1895</v>
-      </c>
-      <c r="D656" t="s">
-        <v>1896</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="s">
-        <v>1893</v>
+        <v>1896</v>
       </c>
       <c r="B657" t="s">
         <v>1897</v>
       </c>
       <c r="C657" t="s">
-        <v>1893</v>
+        <v>1898</v>
       </c>
       <c r="D657" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="s">
-        <v>1899</v>
+        <v>1896</v>
       </c>
       <c r="B658" t="s">
         <v>1900</v>
       </c>
       <c r="C658" t="s">
-        <v>7</v>
+        <v>1896</v>
       </c>
       <c r="D658" t="s">
-        <v>1451</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="B659" t="s">
-        <v>1901</v>
+        <v>1903</v>
       </c>
       <c r="C659" t="s">
-        <v>1902</v>
+        <v>7</v>
       </c>
       <c r="D659" t="s">
-        <v>1903</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="B660" t="s">
         <v>1904</v>
@@ -18209,41 +18218,41 @@
     </row>
     <row r="661">
       <c r="A661" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="B661" t="s">
         <v>1907</v>
       </c>
       <c r="C661" t="s">
-        <v>299</v>
+        <v>1908</v>
       </c>
       <c r="D661" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="B662" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="C662" t="s">
-        <v>1506</v>
+        <v>299</v>
       </c>
       <c r="D662" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="B663" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="C663" t="s">
-        <v>1912</v>
+        <v>1509</v>
       </c>
       <c r="D663" t="s">
         <v>1913</v>
@@ -18251,7 +18260,7 @@
     </row>
     <row r="664">
       <c r="A664" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="B664" t="s">
         <v>1914</v>
@@ -18265,7 +18274,7 @@
     </row>
     <row r="665">
       <c r="A665" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="B665" t="s">
         <v>1917</v>
@@ -18279,7 +18288,7 @@
     </row>
     <row r="666">
       <c r="A666" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="B666" t="s">
         <v>1920</v>
@@ -18293,7 +18302,7 @@
     </row>
     <row r="667">
       <c r="A667" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="B667" t="s">
         <v>1923</v>
@@ -18307,7 +18316,7 @@
     </row>
     <row r="668">
       <c r="A668" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="B668" t="s">
         <v>1926</v>
@@ -18321,7 +18330,7 @@
     </row>
     <row r="669">
       <c r="A669" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="B669" t="s">
         <v>1929</v>
@@ -18335,49 +18344,49 @@
     </row>
     <row r="670">
       <c r="A670" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="B670" t="s">
         <v>1932</v>
       </c>
       <c r="C670" t="s">
-        <v>453</v>
+        <v>1933</v>
       </c>
       <c r="D670" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="B671" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="C671" t="s">
-        <v>1842</v>
+        <v>453</v>
       </c>
       <c r="D671" t="s">
-        <v>1843</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="B672" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="C672" t="s">
-        <v>1936</v>
+        <v>1845</v>
       </c>
       <c r="D672" t="s">
-        <v>1937</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="B673" t="s">
         <v>1938</v>
@@ -18391,7 +18400,7 @@
     </row>
     <row r="674">
       <c r="A674" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="B674" t="s">
         <v>1941</v>
@@ -18405,7 +18414,7 @@
     </row>
     <row r="675">
       <c r="A675" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="B675" t="s">
         <v>1944</v>
@@ -18419,21 +18428,21 @@
     </row>
     <row r="676">
       <c r="A676" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B676" t="s">
         <v>1947</v>
       </c>
-      <c r="B676" t="s">
+      <c r="C676" t="s">
         <v>1948</v>
       </c>
-      <c r="C676" t="s">
+      <c r="D676" t="s">
         <v>1949</v>
-      </c>
-      <c r="D676" t="s">
-        <v>1950</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="s">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="B677" t="s">
         <v>1951</v>
@@ -18447,7 +18456,7 @@
     </row>
     <row r="678">
       <c r="A678" t="s">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="B678" t="s">
         <v>1954</v>
@@ -18461,7 +18470,7 @@
     </row>
     <row r="679">
       <c r="A679" t="s">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="B679" t="s">
         <v>1957</v>
@@ -18475,41 +18484,41 @@
     </row>
     <row r="680">
       <c r="A680" t="s">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="B680" t="s">
         <v>1960</v>
       </c>
       <c r="C680" t="s">
-        <v>451</v>
+        <v>1961</v>
       </c>
       <c r="D680" t="s">
-        <v>452</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="s">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="B681" t="s">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="C681" t="s">
-        <v>1947</v>
+        <v>451</v>
       </c>
       <c r="D681" t="s">
-        <v>1962</v>
+        <v>452</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="s">
-        <v>1506</v>
+        <v>1950</v>
       </c>
       <c r="B682" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="C682" t="s">
-        <v>1964</v>
+        <v>1950</v>
       </c>
       <c r="D682" t="s">
         <v>1965</v>
@@ -18517,7 +18526,7 @@
     </row>
     <row r="683">
       <c r="A683" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B683" t="s">
         <v>1966</v>
@@ -18531,7 +18540,7 @@
     </row>
     <row r="684">
       <c r="A684" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B684" t="s">
         <v>1969</v>
@@ -18545,7 +18554,7 @@
     </row>
     <row r="685">
       <c r="A685" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B685" t="s">
         <v>1972</v>
@@ -18559,7 +18568,7 @@
     </row>
     <row r="686">
       <c r="A686" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B686" t="s">
         <v>1975</v>
@@ -18573,7 +18582,7 @@
     </row>
     <row r="687">
       <c r="A687" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B687" t="s">
         <v>1978</v>
@@ -18587,7 +18596,7 @@
     </row>
     <row r="688">
       <c r="A688" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B688" t="s">
         <v>1981</v>
@@ -18596,26 +18605,26 @@
         <v>1982</v>
       </c>
       <c r="D688" t="s">
-        <v>938</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B689" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="C689" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="D689" t="s">
-        <v>1985</v>
+        <v>941</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B690" t="s">
         <v>1986</v>
@@ -18629,7 +18638,7 @@
     </row>
     <row r="691">
       <c r="A691" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B691" t="s">
         <v>1989</v>
@@ -18643,7 +18652,7 @@
     </row>
     <row r="692">
       <c r="A692" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B692" t="s">
         <v>1992</v>
@@ -18657,7 +18666,7 @@
     </row>
     <row r="693">
       <c r="A693" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B693" t="s">
         <v>1995</v>
@@ -18671,35 +18680,35 @@
     </row>
     <row r="694">
       <c r="A694" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B694" t="s">
         <v>1998</v>
       </c>
       <c r="C694" t="s">
-        <v>376</v>
+        <v>1999</v>
       </c>
       <c r="D694" t="s">
-        <v>377</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B695" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="C695" t="s">
-        <v>2000</v>
+        <v>376</v>
       </c>
       <c r="D695" t="s">
-        <v>2001</v>
+        <v>377</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B696" t="s">
         <v>2002</v>
@@ -18713,7 +18722,7 @@
     </row>
     <row r="697">
       <c r="A697" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B697" t="s">
         <v>2005</v>
@@ -18727,7 +18736,7 @@
     </row>
     <row r="698">
       <c r="A698" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B698" t="s">
         <v>2008</v>
@@ -18741,7 +18750,7 @@
     </row>
     <row r="699">
       <c r="A699" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B699" t="s">
         <v>2011</v>
@@ -18755,7 +18764,7 @@
     </row>
     <row r="700">
       <c r="A700" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B700" t="s">
         <v>2014</v>
@@ -18769,7 +18778,7 @@
     </row>
     <row r="701">
       <c r="A701" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B701" t="s">
         <v>2017</v>
@@ -18783,7 +18792,7 @@
     </row>
     <row r="702">
       <c r="A702" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B702" t="s">
         <v>2020</v>
@@ -18792,68 +18801,68 @@
         <v>2021</v>
       </c>
       <c r="D702" t="s">
-        <v>2019</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B703" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C703" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D703" t="s">
         <v>2022</v>
-      </c>
-      <c r="C703" t="s">
-        <v>2023</v>
-      </c>
-      <c r="D703" t="s">
-        <v>2024</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B704" t="s">
         <v>2025</v>
       </c>
       <c r="C704" t="s">
-        <v>379</v>
+        <v>2026</v>
       </c>
       <c r="D704" t="s">
-        <v>380</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B705" t="s">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="C705" t="s">
-        <v>2027</v>
+        <v>379</v>
       </c>
       <c r="D705" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B706" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="C706" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="D706" t="s">
-        <v>2030</v>
+        <v>383</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B707" t="s">
         <v>2031</v>
@@ -18862,40 +18871,40 @@
         <v>2032</v>
       </c>
       <c r="D707" t="s">
-        <v>334</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B708" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="C708" t="s">
-        <v>1506</v>
+        <v>2035</v>
       </c>
       <c r="D708" t="s">
-        <v>1910</v>
+        <v>334</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B709" t="s">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="C709" t="s">
-        <v>2035</v>
+        <v>1509</v>
       </c>
       <c r="D709" t="s">
-        <v>2036</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B710" t="s">
         <v>2037</v>
@@ -18909,63 +18918,63 @@
     </row>
     <row r="711">
       <c r="A711" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B711" t="s">
         <v>2040</v>
       </c>
       <c r="C711" t="s">
-        <v>1547</v>
+        <v>2041</v>
       </c>
       <c r="D711" t="s">
-        <v>1548</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B712" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="C712" t="s">
-        <v>1601</v>
+        <v>1550</v>
       </c>
       <c r="D712" t="s">
-        <v>1602</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="B713" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="C713" t="s">
-        <v>2043</v>
+        <v>1604</v>
       </c>
       <c r="D713" t="s">
-        <v>2044</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B714" t="s">
         <v>2045</v>
       </c>
-      <c r="B714" t="s">
+      <c r="C714" t="s">
         <v>2046</v>
       </c>
-      <c r="C714" t="s">
+      <c r="D714" t="s">
         <v>2047</v>
-      </c>
-      <c r="D714" t="s">
-        <v>2048</v>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="s">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="B715" t="s">
         <v>2049</v>
@@ -18979,27 +18988,27 @@
     </row>
     <row r="716">
       <c r="A716" t="s">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="B716" t="s">
         <v>2052</v>
       </c>
       <c r="C716" t="s">
-        <v>2045</v>
+        <v>2053</v>
       </c>
       <c r="D716" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="s">
-        <v>1930</v>
+        <v>2048</v>
       </c>
       <c r="B717" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="C717" t="s">
-        <v>2055</v>
+        <v>2048</v>
       </c>
       <c r="D717" t="s">
         <v>2056</v>
@@ -19007,7 +19016,7 @@
     </row>
     <row r="718">
       <c r="A718" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B718" t="s">
         <v>2057</v>
@@ -19021,27 +19030,27 @@
     </row>
     <row r="719">
       <c r="A719" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B719" t="s">
         <v>2060</v>
       </c>
       <c r="C719" t="s">
-        <v>1982</v>
+        <v>2061</v>
       </c>
       <c r="D719" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B720" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="C720" t="s">
-        <v>2063</v>
+        <v>1985</v>
       </c>
       <c r="D720" t="s">
         <v>2064</v>
@@ -19049,7 +19058,7 @@
     </row>
     <row r="721">
       <c r="A721" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B721" t="s">
         <v>2065</v>
@@ -19063,7 +19072,7 @@
     </row>
     <row r="722">
       <c r="A722" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B722" t="s">
         <v>2068</v>
@@ -19077,7 +19086,7 @@
     </row>
     <row r="723">
       <c r="A723" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B723" t="s">
         <v>2071</v>
@@ -19091,7 +19100,7 @@
     </row>
     <row r="724">
       <c r="A724" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B724" t="s">
         <v>2074</v>
@@ -19105,7 +19114,7 @@
     </row>
     <row r="725">
       <c r="A725" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B725" t="s">
         <v>2077</v>
@@ -19119,7 +19128,7 @@
     </row>
     <row r="726">
       <c r="A726" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B726" t="s">
         <v>2080</v>
@@ -19133,7 +19142,7 @@
     </row>
     <row r="727">
       <c r="A727" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B727" t="s">
         <v>2083</v>
@@ -19147,7 +19156,7 @@
     </row>
     <row r="728">
       <c r="A728" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B728" t="s">
         <v>2086</v>
@@ -19161,7 +19170,7 @@
     </row>
     <row r="729">
       <c r="A729" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B729" t="s">
         <v>2089</v>
@@ -19175,7 +19184,7 @@
     </row>
     <row r="730">
       <c r="A730" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B730" t="s">
         <v>2092</v>
@@ -19189,7 +19198,7 @@
     </row>
     <row r="731">
       <c r="A731" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B731" t="s">
         <v>2095</v>
@@ -19203,7 +19212,7 @@
     </row>
     <row r="732">
       <c r="A732" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B732" t="s">
         <v>2098</v>
@@ -19217,7 +19226,7 @@
     </row>
     <row r="733">
       <c r="A733" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B733" t="s">
         <v>2101</v>
@@ -19231,7 +19240,7 @@
     </row>
     <row r="734">
       <c r="A734" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B734" t="s">
         <v>2104</v>
@@ -19245,7 +19254,7 @@
     </row>
     <row r="735">
       <c r="A735" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B735" t="s">
         <v>2107</v>
@@ -19259,7 +19268,7 @@
     </row>
     <row r="736">
       <c r="A736" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B736" t="s">
         <v>2110</v>
@@ -19273,7 +19282,7 @@
     </row>
     <row r="737">
       <c r="A737" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B737" t="s">
         <v>2113</v>
@@ -19287,7 +19296,7 @@
     </row>
     <row r="738">
       <c r="A738" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B738" t="s">
         <v>2116</v>
@@ -19301,27 +19310,27 @@
     </row>
     <row r="739">
       <c r="A739" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B739" t="s">
         <v>2119</v>
       </c>
       <c r="C739" t="s">
-        <v>1982</v>
+        <v>2120</v>
       </c>
       <c r="D739" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B740" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="C740" t="s">
-        <v>2122</v>
+        <v>1985</v>
       </c>
       <c r="D740" t="s">
         <v>2123</v>
@@ -19329,7 +19338,7 @@
     </row>
     <row r="741">
       <c r="A741" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B741" t="s">
         <v>2124</v>
@@ -19343,7 +19352,7 @@
     </row>
     <row r="742">
       <c r="A742" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B742" t="s">
         <v>2127</v>
@@ -19357,7 +19366,7 @@
     </row>
     <row r="743">
       <c r="A743" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B743" t="s">
         <v>2130</v>
@@ -19371,7 +19380,7 @@
     </row>
     <row r="744">
       <c r="A744" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B744" t="s">
         <v>2133</v>
@@ -19385,49 +19394,49 @@
     </row>
     <row r="745">
       <c r="A745" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B745" t="s">
         <v>2136</v>
       </c>
       <c r="C745" t="s">
-        <v>6</v>
+        <v>2137</v>
       </c>
       <c r="D745" t="s">
-        <v>549</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B746" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="C746" t="s">
-        <v>2138</v>
+        <v>6</v>
       </c>
       <c r="D746" t="s">
-        <v>391</v>
+        <v>549</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B747" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="C747" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="D747" t="s">
-        <v>2141</v>
+        <v>391</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B748" t="s">
         <v>2142</v>
@@ -19436,26 +19445,26 @@
         <v>2143</v>
       </c>
       <c r="D748" t="s">
-        <v>2141</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B749" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C749" t="s">
+        <v>2146</v>
+      </c>
+      <c r="D749" t="s">
         <v>2144</v>
-      </c>
-      <c r="C749" t="s">
-        <v>2145</v>
-      </c>
-      <c r="D749" t="s">
-        <v>2146</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B750" t="s">
         <v>2147</v>
@@ -19464,68 +19473,68 @@
         <v>2148</v>
       </c>
       <c r="D750" t="s">
-        <v>1931</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B751" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="C751" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="D751" t="s">
-        <v>349</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B752" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="C752" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="D752" t="s">
-        <v>2153</v>
+        <v>349</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B753" t="s">
         <v>2154</v>
       </c>
       <c r="C753" t="s">
-        <v>285</v>
+        <v>2155</v>
       </c>
       <c r="D753" t="s">
-        <v>286</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B754" t="s">
-        <v>2155</v>
+        <v>2157</v>
       </c>
       <c r="C754" t="s">
-        <v>2156</v>
+        <v>285</v>
       </c>
       <c r="D754" t="s">
-        <v>2157</v>
+        <v>286</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B755" t="s">
         <v>2158</v>
@@ -19539,7 +19548,7 @@
     </row>
     <row r="756">
       <c r="A756" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B756" t="s">
         <v>2161</v>
@@ -19553,7 +19562,7 @@
     </row>
     <row r="757">
       <c r="A757" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B757" t="s">
         <v>2164</v>
@@ -19567,7 +19576,7 @@
     </row>
     <row r="758">
       <c r="A758" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B758" t="s">
         <v>2167</v>
@@ -19581,35 +19590,35 @@
     </row>
     <row r="759">
       <c r="A759" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B759" t="s">
         <v>2170</v>
       </c>
       <c r="C759" t="s">
-        <v>1902</v>
+        <v>2171</v>
       </c>
       <c r="D759" t="s">
-        <v>1903</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B760" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="C760" t="s">
-        <v>2172</v>
+        <v>1905</v>
       </c>
       <c r="D760" t="s">
-        <v>2173</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B761" t="s">
         <v>2174</v>
@@ -19623,7 +19632,7 @@
     </row>
     <row r="762">
       <c r="A762" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B762" t="s">
         <v>2177</v>
@@ -19637,7 +19646,7 @@
     </row>
     <row r="763">
       <c r="A763" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B763" t="s">
         <v>2180</v>
@@ -19646,26 +19655,26 @@
         <v>2181</v>
       </c>
       <c r="D763" t="s">
-        <v>968</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="s">
-        <v>2150</v>
+        <v>1933</v>
       </c>
       <c r="B764" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="C764" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="D764" t="s">
-        <v>2184</v>
+        <v>971</v>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="s">
-        <v>2150</v>
+        <v>2153</v>
       </c>
       <c r="B765" t="s">
         <v>2185</v>
@@ -19679,7 +19688,7 @@
     </row>
     <row r="766">
       <c r="A766" t="s">
-        <v>2150</v>
+        <v>2153</v>
       </c>
       <c r="B766" t="s">
         <v>2188</v>
@@ -19693,49 +19702,49 @@
     </row>
     <row r="767">
       <c r="A767" t="s">
-        <v>2150</v>
+        <v>2153</v>
       </c>
       <c r="B767" t="s">
         <v>2191</v>
       </c>
       <c r="C767" t="s">
-        <v>411</v>
+        <v>2192</v>
       </c>
       <c r="D767" t="s">
-        <v>412</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="s">
-        <v>2150</v>
+        <v>2153</v>
       </c>
       <c r="B768" t="s">
-        <v>2192</v>
+        <v>2194</v>
       </c>
       <c r="C768" t="s">
-        <v>2193</v>
+        <v>411</v>
       </c>
       <c r="D768" t="s">
-        <v>2024</v>
+        <v>412</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="s">
-        <v>2150</v>
+        <v>2153</v>
       </c>
       <c r="B769" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="C769" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="D769" t="s">
-        <v>2196</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="s">
-        <v>1842</v>
+        <v>2153</v>
       </c>
       <c r="B770" t="s">
         <v>2197</v>
@@ -19749,35 +19758,35 @@
     </row>
     <row r="771">
       <c r="A771" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B771" t="s">
         <v>2200</v>
       </c>
       <c r="C771" t="s">
-        <v>461</v>
+        <v>2201</v>
       </c>
       <c r="D771" t="s">
-        <v>462</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B772" t="s">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="C772" t="s">
-        <v>2202</v>
+        <v>461</v>
       </c>
       <c r="D772" t="s">
-        <v>2203</v>
+        <v>462</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B773" t="s">
         <v>2204</v>
@@ -19791,7 +19800,7 @@
     </row>
     <row r="774">
       <c r="A774" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B774" t="s">
         <v>2207</v>
@@ -19805,35 +19814,35 @@
     </row>
     <row r="775">
       <c r="A775" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B775" t="s">
         <v>2210</v>
       </c>
       <c r="C775" t="s">
-        <v>491</v>
+        <v>2211</v>
       </c>
       <c r="D775" t="s">
-        <v>492</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B776" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
       <c r="C776" t="s">
-        <v>2212</v>
+        <v>491</v>
       </c>
       <c r="D776" t="s">
-        <v>2213</v>
+        <v>492</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B777" t="s">
         <v>2214</v>
@@ -19847,35 +19856,35 @@
     </row>
     <row r="778">
       <c r="A778" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B778" t="s">
         <v>2217</v>
       </c>
       <c r="C778" t="s">
-        <v>328</v>
+        <v>2218</v>
       </c>
       <c r="D778" t="s">
-        <v>185</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B779" t="s">
-        <v>2218</v>
+        <v>2220</v>
       </c>
       <c r="C779" t="s">
-        <v>2219</v>
+        <v>328</v>
       </c>
       <c r="D779" t="s">
-        <v>2220</v>
+        <v>185</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B780" t="s">
         <v>2221</v>
@@ -19889,7 +19898,7 @@
     </row>
     <row r="781">
       <c r="A781" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B781" t="s">
         <v>2224</v>
@@ -19903,7 +19912,7 @@
     </row>
     <row r="782">
       <c r="A782" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B782" t="s">
         <v>2227</v>
@@ -19917,7 +19926,7 @@
     </row>
     <row r="783">
       <c r="A783" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B783" t="s">
         <v>2230</v>
@@ -19931,7 +19940,7 @@
     </row>
     <row r="784">
       <c r="A784" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B784" t="s">
         <v>2233</v>
@@ -19945,7 +19954,7 @@
     </row>
     <row r="785">
       <c r="A785" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B785" t="s">
         <v>2236</v>
@@ -19959,7 +19968,7 @@
     </row>
     <row r="786">
       <c r="A786" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B786" t="s">
         <v>2239</v>
@@ -19973,7 +19982,7 @@
     </row>
     <row r="787">
       <c r="A787" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B787" t="s">
         <v>2242</v>
@@ -19982,32 +19991,32 @@
         <v>2243</v>
       </c>
       <c r="D787" t="s">
-        <v>483</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B788" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="C788" t="s">
-        <v>291</v>
+        <v>2246</v>
       </c>
       <c r="D788" t="s">
-        <v>2245</v>
+        <v>483</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B789" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="C789" t="s">
-        <v>2247</v>
+        <v>291</v>
       </c>
       <c r="D789" t="s">
         <v>2248</v>
@@ -20015,7 +20024,7 @@
     </row>
     <row r="790">
       <c r="A790" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B790" t="s">
         <v>2249</v>
@@ -20029,7 +20038,7 @@
     </row>
     <row r="791">
       <c r="A791" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B791" t="s">
         <v>2252</v>
@@ -20043,7 +20052,7 @@
     </row>
     <row r="792">
       <c r="A792" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B792" t="s">
         <v>2255</v>
@@ -20057,35 +20066,35 @@
     </row>
     <row r="793">
       <c r="A793" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B793" t="s">
         <v>2258</v>
       </c>
       <c r="C793" t="s">
-        <v>6</v>
+        <v>2259</v>
       </c>
       <c r="D793" t="s">
-        <v>549</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B794" t="s">
-        <v>2259</v>
+        <v>2261</v>
       </c>
       <c r="C794" t="s">
-        <v>2260</v>
+        <v>6</v>
       </c>
       <c r="D794" t="s">
-        <v>2261</v>
+        <v>549</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B795" t="s">
         <v>2262</v>
@@ -20099,7 +20108,7 @@
     </row>
     <row r="796">
       <c r="A796" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B796" t="s">
         <v>2265</v>
@@ -20113,7 +20122,7 @@
     </row>
     <row r="797">
       <c r="A797" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B797" t="s">
         <v>2268</v>
@@ -20127,7 +20136,7 @@
     </row>
     <row r="798">
       <c r="A798" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="B798" t="s">
         <v>2271</v>
@@ -20141,7 +20150,7 @@
     </row>
     <row r="799">
       <c r="A799" t="s">
-        <v>1936</v>
+        <v>1845</v>
       </c>
       <c r="B799" t="s">
         <v>2274</v>
@@ -20155,7 +20164,7 @@
     </row>
     <row r="800">
       <c r="A800" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B800" t="s">
         <v>2277</v>
@@ -20169,7 +20178,7 @@
     </row>
     <row r="801">
       <c r="A801" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B801" t="s">
         <v>2280</v>
@@ -20183,7 +20192,7 @@
     </row>
     <row r="802">
       <c r="A802" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B802" t="s">
         <v>2283</v>
@@ -20197,7 +20206,7 @@
     </row>
     <row r="803">
       <c r="A803" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B803" t="s">
         <v>2286</v>
@@ -20211,7 +20220,7 @@
     </row>
     <row r="804">
       <c r="A804" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B804" t="s">
         <v>2289</v>
@@ -20225,7 +20234,7 @@
     </row>
     <row r="805">
       <c r="A805" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B805" t="s">
         <v>2292</v>
@@ -20239,27 +20248,27 @@
     </row>
     <row r="806">
       <c r="A806" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B806" t="s">
         <v>2295</v>
       </c>
       <c r="C806" t="s">
-        <v>2018</v>
+        <v>2296</v>
       </c>
       <c r="D806" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B807" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
       <c r="C807" t="s">
-        <v>2298</v>
+        <v>2021</v>
       </c>
       <c r="D807" t="s">
         <v>2299</v>
@@ -20267,7 +20276,7 @@
     </row>
     <row r="808">
       <c r="A808" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B808" t="s">
         <v>2300</v>
@@ -20281,7 +20290,7 @@
     </row>
     <row r="809">
       <c r="A809" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B809" t="s">
         <v>2303</v>
@@ -20295,7 +20304,7 @@
     </row>
     <row r="810">
       <c r="A810" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B810" t="s">
         <v>2306</v>
@@ -20309,7 +20318,7 @@
     </row>
     <row r="811">
       <c r="A811" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B811" t="s">
         <v>2309</v>
@@ -20323,7 +20332,7 @@
     </row>
     <row r="812">
       <c r="A812" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B812" t="s">
         <v>2312</v>
@@ -20337,7 +20346,7 @@
     </row>
     <row r="813">
       <c r="A813" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B813" t="s">
         <v>2315</v>
@@ -20351,35 +20360,35 @@
     </row>
     <row r="814">
       <c r="A814" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B814" t="s">
         <v>2318</v>
       </c>
       <c r="C814" t="s">
-        <v>376</v>
+        <v>2319</v>
       </c>
       <c r="D814" t="s">
-        <v>377</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B815" t="s">
-        <v>2319</v>
+        <v>2321</v>
       </c>
       <c r="C815" t="s">
-        <v>2320</v>
+        <v>376</v>
       </c>
       <c r="D815" t="s">
-        <v>2321</v>
+        <v>377</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B816" t="s">
         <v>2322</v>
@@ -20393,7 +20402,7 @@
     </row>
     <row r="817">
       <c r="A817" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B817" t="s">
         <v>2325</v>
@@ -20407,7 +20416,7 @@
     </row>
     <row r="818">
       <c r="A818" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B818" t="s">
         <v>2328</v>
@@ -20421,7 +20430,7 @@
     </row>
     <row r="819">
       <c r="A819" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B819" t="s">
         <v>2331</v>
@@ -20435,7 +20444,7 @@
     </row>
     <row r="820">
       <c r="A820" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B820" t="s">
         <v>2334</v>
@@ -20449,7 +20458,7 @@
     </row>
     <row r="821">
       <c r="A821" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B821" t="s">
         <v>2337</v>
@@ -20463,27 +20472,27 @@
     </row>
     <row r="822">
       <c r="A822" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B822" t="s">
         <v>2340</v>
       </c>
       <c r="C822" t="s">
-        <v>21</v>
+        <v>2341</v>
       </c>
       <c r="D822" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B823" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="C823" t="s">
-        <v>2343</v>
+        <v>21</v>
       </c>
       <c r="D823" t="s">
         <v>2344</v>
@@ -20491,7 +20500,7 @@
     </row>
     <row r="824">
       <c r="A824" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B824" t="s">
         <v>2345</v>
@@ -20505,7 +20514,7 @@
     </row>
     <row r="825">
       <c r="A825" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B825" t="s">
         <v>2348</v>
@@ -20519,7 +20528,7 @@
     </row>
     <row r="826">
       <c r="A826" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B826" t="s">
         <v>2351</v>
@@ -20528,26 +20537,26 @@
         <v>2352</v>
       </c>
       <c r="D826" t="s">
-        <v>2308</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B827" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="C827" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="D827" t="s">
-        <v>2355</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B828" t="s">
         <v>2356</v>
@@ -20561,7 +20570,7 @@
     </row>
     <row r="829">
       <c r="A829" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B829" t="s">
         <v>2359</v>
@@ -20575,7 +20584,7 @@
     </row>
     <row r="830">
       <c r="A830" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B830" t="s">
         <v>2362</v>
@@ -20589,7 +20598,7 @@
     </row>
     <row r="831">
       <c r="A831" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B831" t="s">
         <v>2365</v>
@@ -20603,27 +20612,27 @@
     </row>
     <row r="832">
       <c r="A832" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B832" t="s">
         <v>2368</v>
       </c>
       <c r="C832" t="s">
-        <v>1261</v>
+        <v>2369</v>
       </c>
       <c r="D832" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B833" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
       <c r="C833" t="s">
-        <v>2371</v>
+        <v>1264</v>
       </c>
       <c r="D833" t="s">
         <v>2372</v>
@@ -20631,27 +20640,27 @@
     </row>
     <row r="834">
       <c r="A834" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B834" t="s">
         <v>2373</v>
       </c>
       <c r="C834" t="s">
-        <v>387</v>
+        <v>2374</v>
       </c>
       <c r="D834" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B835" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="C835" t="s">
-        <v>2376</v>
+        <v>387</v>
       </c>
       <c r="D835" t="s">
         <v>2377</v>
@@ -20659,7 +20668,7 @@
     </row>
     <row r="836">
       <c r="A836" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B836" t="s">
         <v>2378</v>
@@ -20673,7 +20682,7 @@
     </row>
     <row r="837">
       <c r="A837" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B837" t="s">
         <v>2381</v>
@@ -20687,7 +20696,7 @@
     </row>
     <row r="838">
       <c r="A838" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B838" t="s">
         <v>2384</v>
@@ -20701,7 +20710,7 @@
     </row>
     <row r="839">
       <c r="A839" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B839" t="s">
         <v>2387</v>
@@ -20715,7 +20724,7 @@
     </row>
     <row r="840">
       <c r="A840" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B840" t="s">
         <v>2390</v>
@@ -20729,63 +20738,63 @@
     </row>
     <row r="841">
       <c r="A841" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B841" t="s">
         <v>2393</v>
       </c>
       <c r="C841" t="s">
-        <v>382</v>
+        <v>2394</v>
       </c>
       <c r="D841" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B842" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="C842" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="D842" t="s">
-        <v>400</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B843" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="C843" t="s">
-        <v>2397</v>
+        <v>399</v>
       </c>
       <c r="D843" t="s">
-        <v>2394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B844" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="C844" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="D844" t="s">
-        <v>2400</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B845" t="s">
         <v>2401</v>
@@ -20799,7 +20808,7 @@
     </row>
     <row r="846">
       <c r="A846" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B846" t="s">
         <v>2404</v>
@@ -20813,7 +20822,7 @@
     </row>
     <row r="847">
       <c r="A847" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B847" t="s">
         <v>2407</v>
@@ -20827,7 +20836,7 @@
     </row>
     <row r="848">
       <c r="A848" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B848" t="s">
         <v>2410</v>
@@ -20841,7 +20850,7 @@
     </row>
     <row r="849">
       <c r="A849" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B849" t="s">
         <v>2413</v>
@@ -20855,7 +20864,7 @@
     </row>
     <row r="850">
       <c r="A850" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B850" t="s">
         <v>2416</v>
@@ -20864,26 +20873,26 @@
         <v>2417</v>
       </c>
       <c r="D850" t="s">
-        <v>2347</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B851" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="C851" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="D851" t="s">
-        <v>2420</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B852" t="s">
         <v>2421</v>
@@ -20892,26 +20901,26 @@
         <v>2422</v>
       </c>
       <c r="D852" t="s">
-        <v>1548</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B853" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="C853" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="D853" t="s">
-        <v>2425</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B854" t="s">
         <v>2426</v>
@@ -20925,7 +20934,7 @@
     </row>
     <row r="855">
       <c r="A855" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B855" t="s">
         <v>2429</v>
@@ -20939,7 +20948,7 @@
     </row>
     <row r="856">
       <c r="A856" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B856" t="s">
         <v>2432</v>
@@ -20948,68 +20957,68 @@
         <v>2433</v>
       </c>
       <c r="D856" t="s">
-        <v>1451</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B857" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="C857" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="D857" t="s">
-        <v>2436</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B858" t="s">
         <v>2437</v>
       </c>
       <c r="C858" t="s">
-        <v>1947</v>
+        <v>2438</v>
       </c>
       <c r="D858" t="s">
-        <v>1962</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B859" t="s">
-        <v>2438</v>
+        <v>2440</v>
       </c>
       <c r="C859" t="s">
-        <v>54</v>
+        <v>1950</v>
       </c>
       <c r="D859" t="s">
-        <v>55</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B860" t="s">
-        <v>2439</v>
+        <v>2441</v>
       </c>
       <c r="C860" t="s">
-        <v>2440</v>
+        <v>54</v>
       </c>
       <c r="D860" t="s">
-        <v>2441</v>
+        <v>55</v>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B861" t="s">
         <v>2442</v>
@@ -21023,7 +21032,7 @@
     </row>
     <row r="862">
       <c r="A862" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B862" t="s">
         <v>2445</v>
@@ -21037,7 +21046,7 @@
     </row>
     <row r="863">
       <c r="A863" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B863" t="s">
         <v>2448</v>
@@ -21051,7 +21060,7 @@
     </row>
     <row r="864">
       <c r="A864" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B864" t="s">
         <v>2451</v>
@@ -21065,7 +21074,7 @@
     </row>
     <row r="865">
       <c r="A865" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B865" t="s">
         <v>2454</v>
@@ -21079,7 +21088,7 @@
     </row>
     <row r="866">
       <c r="A866" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B866" t="s">
         <v>2457</v>
@@ -21093,7 +21102,7 @@
     </row>
     <row r="867">
       <c r="A867" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B867" t="s">
         <v>2460</v>
@@ -21107,7 +21116,7 @@
     </row>
     <row r="868">
       <c r="A868" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B868" t="s">
         <v>2463</v>
@@ -21121,7 +21130,7 @@
     </row>
     <row r="869">
       <c r="A869" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B869" t="s">
         <v>2466</v>
@@ -21135,7 +21144,7 @@
     </row>
     <row r="870">
       <c r="A870" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B870" t="s">
         <v>2469</v>
@@ -21149,7 +21158,7 @@
     </row>
     <row r="871">
       <c r="A871" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B871" t="s">
         <v>2472</v>
@@ -21163,7 +21172,7 @@
     </row>
     <row r="872">
       <c r="A872" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B872" t="s">
         <v>2475</v>
@@ -21177,7 +21186,7 @@
     </row>
     <row r="873">
       <c r="A873" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B873" t="s">
         <v>2478</v>
@@ -21191,21 +21200,21 @@
     </row>
     <row r="874">
       <c r="A874" t="s">
+        <v>1939</v>
+      </c>
+      <c r="B874" t="s">
         <v>2481</v>
       </c>
-      <c r="B874" t="s">
+      <c r="C874" t="s">
         <v>2482</v>
       </c>
-      <c r="C874" t="s">
+      <c r="D874" t="s">
         <v>2483</v>
-      </c>
-      <c r="D874" t="s">
-        <v>2484</v>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="s">
-        <v>2481</v>
+        <v>2484</v>
       </c>
       <c r="B875" t="s">
         <v>2485</v>
@@ -21219,7 +21228,7 @@
     </row>
     <row r="876">
       <c r="A876" t="s">
-        <v>2481</v>
+        <v>2484</v>
       </c>
       <c r="B876" t="s">
         <v>2488</v>
@@ -21233,7 +21242,7 @@
     </row>
     <row r="877">
       <c r="A877" t="s">
-        <v>2481</v>
+        <v>2484</v>
       </c>
       <c r="B877" t="s">
         <v>2491</v>
@@ -21247,7 +21256,7 @@
     </row>
     <row r="878">
       <c r="A878" t="s">
-        <v>1554</v>
+        <v>2484</v>
       </c>
       <c r="B878" t="s">
         <v>2494</v>
@@ -21261,7 +21270,7 @@
     </row>
     <row r="879">
       <c r="A879" t="s">
-        <v>1554</v>
+        <v>1557</v>
       </c>
       <c r="B879" t="s">
         <v>2497</v>
@@ -21275,7 +21284,7 @@
     </row>
     <row r="880">
       <c r="A880" t="s">
-        <v>1554</v>
+        <v>1557</v>
       </c>
       <c r="B880" t="s">
         <v>2500</v>
@@ -21289,7 +21298,7 @@
     </row>
     <row r="881">
       <c r="A881" t="s">
-        <v>1927</v>
+        <v>1557</v>
       </c>
       <c r="B881" t="s">
         <v>2503</v>
@@ -21303,7 +21312,7 @@
     </row>
     <row r="882">
       <c r="A882" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B882" t="s">
         <v>2506</v>
@@ -21317,7 +21326,7 @@
     </row>
     <row r="883">
       <c r="A883" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B883" t="s">
         <v>2509</v>
@@ -21331,7 +21340,7 @@
     </row>
     <row r="884">
       <c r="A884" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B884" t="s">
         <v>2512</v>
@@ -21345,7 +21354,7 @@
     </row>
     <row r="885">
       <c r="A885" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B885" t="s">
         <v>2515</v>
@@ -21359,7 +21368,7 @@
     </row>
     <row r="886">
       <c r="A886" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B886" t="s">
         <v>2518</v>
@@ -21373,7 +21382,7 @@
     </row>
     <row r="887">
       <c r="A887" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B887" t="s">
         <v>2521</v>
@@ -21387,7 +21396,7 @@
     </row>
     <row r="888">
       <c r="A888" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B888" t="s">
         <v>2524</v>
@@ -21401,7 +21410,7 @@
     </row>
     <row r="889">
       <c r="A889" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B889" t="s">
         <v>2527</v>
@@ -21415,7 +21424,7 @@
     </row>
     <row r="890">
       <c r="A890" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B890" t="s">
         <v>2530</v>
@@ -21429,7 +21438,7 @@
     </row>
     <row r="891">
       <c r="A891" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B891" t="s">
         <v>2533</v>
@@ -21443,7 +21452,7 @@
     </row>
     <row r="892">
       <c r="A892" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B892" t="s">
         <v>2536</v>
@@ -21457,7 +21466,7 @@
     </row>
     <row r="893">
       <c r="A893" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B893" t="s">
         <v>2539</v>
@@ -21471,7 +21480,7 @@
     </row>
     <row r="894">
       <c r="A894" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B894" t="s">
         <v>2542</v>
@@ -21485,7 +21494,7 @@
     </row>
     <row r="895">
       <c r="A895" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B895" t="s">
         <v>2545</v>
@@ -21499,7 +21508,7 @@
     </row>
     <row r="896">
       <c r="A896" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B896" t="s">
         <v>2548</v>
@@ -21513,7 +21522,7 @@
     </row>
     <row r="897">
       <c r="A897" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B897" t="s">
         <v>2551</v>
@@ -21527,7 +21536,7 @@
     </row>
     <row r="898">
       <c r="A898" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B898" t="s">
         <v>2554</v>
@@ -21541,7 +21550,7 @@
     </row>
     <row r="899">
       <c r="A899" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B899" t="s">
         <v>2557</v>
@@ -21555,7 +21564,7 @@
     </row>
     <row r="900">
       <c r="A900" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B900" t="s">
         <v>2560</v>
@@ -21569,7 +21578,7 @@
     </row>
     <row r="901">
       <c r="A901" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B901" t="s">
         <v>2563</v>
@@ -21583,7 +21592,7 @@
     </row>
     <row r="902">
       <c r="A902" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B902" t="s">
         <v>2566</v>
@@ -21597,7 +21606,7 @@
     </row>
     <row r="903">
       <c r="A903" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B903" t="s">
         <v>2569</v>
@@ -21611,7 +21620,7 @@
     </row>
     <row r="904">
       <c r="A904" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B904" t="s">
         <v>2572</v>
@@ -21625,7 +21634,7 @@
     </row>
     <row r="905">
       <c r="A905" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B905" t="s">
         <v>2575</v>
@@ -21639,7 +21648,7 @@
     </row>
     <row r="906">
       <c r="A906" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B906" t="s">
         <v>2578</v>
@@ -21653,7 +21662,7 @@
     </row>
     <row r="907">
       <c r="A907" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B907" t="s">
         <v>2581</v>
@@ -21667,35 +21676,35 @@
     </row>
     <row r="908">
       <c r="A908" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B908" t="s">
         <v>2584</v>
       </c>
       <c r="C908" t="s">
-        <v>1532</v>
+        <v>2585</v>
       </c>
       <c r="D908" t="s">
-        <v>1533</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B909" t="s">
-        <v>2585</v>
+        <v>2587</v>
       </c>
       <c r="C909" t="s">
-        <v>2586</v>
+        <v>1535</v>
       </c>
       <c r="D909" t="s">
-        <v>2587</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B910" t="s">
         <v>2588</v>
@@ -21709,7 +21718,7 @@
     </row>
     <row r="911">
       <c r="A911" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B911" t="s">
         <v>2591</v>
@@ -21723,7 +21732,7 @@
     </row>
     <row r="912">
       <c r="A912" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B912" t="s">
         <v>2594</v>
@@ -21737,7 +21746,7 @@
     </row>
     <row r="913">
       <c r="A913" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B913" t="s">
         <v>2597</v>
@@ -21751,7 +21760,7 @@
     </row>
     <row r="914">
       <c r="A914" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B914" t="s">
         <v>2600</v>
@@ -21765,7 +21774,7 @@
     </row>
     <row r="915">
       <c r="A915" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B915" t="s">
         <v>2603</v>
@@ -21779,7 +21788,7 @@
     </row>
     <row r="916">
       <c r="A916" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B916" t="s">
         <v>2606</v>
@@ -21793,7 +21802,7 @@
     </row>
     <row r="917">
       <c r="A917" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B917" t="s">
         <v>2609</v>
@@ -21807,35 +21816,35 @@
     </row>
     <row r="918">
       <c r="A918" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B918" t="s">
         <v>2612</v>
       </c>
       <c r="C918" t="s">
-        <v>1020</v>
+        <v>2613</v>
       </c>
       <c r="D918" t="s">
-        <v>2403</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="919">
       <c r="A919" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B919" t="s">
-        <v>2613</v>
+        <v>2615</v>
       </c>
       <c r="C919" t="s">
-        <v>2614</v>
+        <v>1023</v>
       </c>
       <c r="D919" t="s">
-        <v>2615</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="920">
       <c r="A920" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B920" t="s">
         <v>2616</v>
@@ -21849,7 +21858,7 @@
     </row>
     <row r="921">
       <c r="A921" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B921" t="s">
         <v>2619</v>
@@ -21863,7 +21872,7 @@
     </row>
     <row r="922">
       <c r="A922" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B922" t="s">
         <v>2622</v>
@@ -21877,7 +21886,7 @@
     </row>
     <row r="923">
       <c r="A923" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B923" t="s">
         <v>2625</v>
@@ -21891,7 +21900,7 @@
     </row>
     <row r="924">
       <c r="A924" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B924" t="s">
         <v>2628</v>
@@ -21905,7 +21914,7 @@
     </row>
     <row r="925">
       <c r="A925" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B925" t="s">
         <v>2631</v>
@@ -21919,7 +21928,7 @@
     </row>
     <row r="926">
       <c r="A926" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B926" t="s">
         <v>2634</v>
@@ -21933,7 +21942,7 @@
     </row>
     <row r="927">
       <c r="A927" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B927" t="s">
         <v>2637</v>
@@ -21947,7 +21956,7 @@
     </row>
     <row r="928">
       <c r="A928" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B928" t="s">
         <v>2640</v>
@@ -21961,7 +21970,7 @@
     </row>
     <row r="929">
       <c r="A929" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B929" t="s">
         <v>2643</v>
@@ -21975,7 +21984,7 @@
     </row>
     <row r="930">
       <c r="A930" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B930" t="s">
         <v>2646</v>
@@ -21989,7 +21998,7 @@
     </row>
     <row r="931">
       <c r="A931" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B931" t="s">
         <v>2649</v>
@@ -22003,7 +22012,7 @@
     </row>
     <row r="932">
       <c r="A932" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B932" t="s">
         <v>2652</v>
@@ -22017,7 +22026,7 @@
     </row>
     <row r="933">
       <c r="A933" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B933" t="s">
         <v>2655</v>
@@ -22031,7 +22040,7 @@
     </row>
     <row r="934">
       <c r="A934" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B934" t="s">
         <v>2658</v>
@@ -22045,7 +22054,7 @@
     </row>
     <row r="935">
       <c r="A935" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B935" t="s">
         <v>2661</v>
@@ -22059,7 +22068,7 @@
     </row>
     <row r="936">
       <c r="A936" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B936" t="s">
         <v>2664</v>
@@ -22073,35 +22082,35 @@
     </row>
     <row r="937">
       <c r="A937" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B937" t="s">
         <v>2667</v>
       </c>
       <c r="C937" t="s">
-        <v>336</v>
+        <v>2668</v>
       </c>
       <c r="D937" t="s">
-        <v>337</v>
+        <v>2669</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B938" t="s">
-        <v>2668</v>
+        <v>2670</v>
       </c>
       <c r="C938" t="s">
-        <v>2669</v>
+        <v>336</v>
       </c>
       <c r="D938" t="s">
-        <v>2670</v>
+        <v>337</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B939" t="s">
         <v>2671</v>
@@ -22115,7 +22124,7 @@
     </row>
     <row r="940">
       <c r="A940" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B940" t="s">
         <v>2674</v>
@@ -22129,7 +22138,7 @@
     </row>
     <row r="941">
       <c r="A941" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B941" t="s">
         <v>2677</v>
@@ -22143,35 +22152,35 @@
     </row>
     <row r="942">
       <c r="A942" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B942" t="s">
         <v>2680</v>
       </c>
       <c r="C942" t="s">
-        <v>566</v>
+        <v>2681</v>
       </c>
       <c r="D942" t="s">
-        <v>567</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B943" t="s">
-        <v>2681</v>
+        <v>2683</v>
       </c>
       <c r="C943" t="s">
-        <v>2682</v>
+        <v>566</v>
       </c>
       <c r="D943" t="s">
-        <v>2683</v>
+        <v>567</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B944" t="s">
         <v>2684</v>
@@ -22185,35 +22194,35 @@
     </row>
     <row r="945">
       <c r="A945" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B945" t="s">
         <v>2687</v>
       </c>
       <c r="C945" t="s">
-        <v>828</v>
+        <v>2688</v>
       </c>
       <c r="D945" t="s">
-        <v>829</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B946" t="s">
-        <v>2688</v>
+        <v>2690</v>
       </c>
       <c r="C946" t="s">
-        <v>2689</v>
+        <v>831</v>
       </c>
       <c r="D946" t="s">
-        <v>2690</v>
+        <v>832</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B947" t="s">
         <v>2691</v>
@@ -22227,7 +22236,7 @@
     </row>
     <row r="948">
       <c r="A948" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B948" t="s">
         <v>2694</v>
@@ -22241,7 +22250,7 @@
     </row>
     <row r="949">
       <c r="A949" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B949" t="s">
         <v>2697</v>
@@ -22255,7 +22264,7 @@
     </row>
     <row r="950">
       <c r="A950" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B950" t="s">
         <v>2700</v>
@@ -22269,7 +22278,7 @@
     </row>
     <row r="951">
       <c r="A951" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B951" t="s">
         <v>2703</v>
@@ -22283,7 +22292,7 @@
     </row>
     <row r="952">
       <c r="A952" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B952" t="s">
         <v>2706</v>
@@ -22297,7 +22306,7 @@
     </row>
     <row r="953">
       <c r="A953" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B953" t="s">
         <v>2709</v>
@@ -22311,7 +22320,7 @@
     </row>
     <row r="954">
       <c r="A954" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B954" t="s">
         <v>2712</v>
@@ -22325,7 +22334,7 @@
     </row>
     <row r="955">
       <c r="A955" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B955" t="s">
         <v>2715</v>
@@ -22339,7 +22348,7 @@
     </row>
     <row r="956">
       <c r="A956" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B956" t="s">
         <v>2718</v>
@@ -22348,26 +22357,26 @@
         <v>2719</v>
       </c>
       <c r="D956" t="s">
-        <v>817</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B957" t="s">
-        <v>2720</v>
+        <v>2721</v>
       </c>
       <c r="C957" t="s">
-        <v>2721</v>
+        <v>2722</v>
       </c>
       <c r="D957" t="s">
-        <v>2722</v>
+        <v>820</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B958" t="s">
         <v>2723</v>
@@ -22381,7 +22390,7 @@
     </row>
     <row r="959">
       <c r="A959" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B959" t="s">
         <v>2726</v>
@@ -22395,7 +22404,7 @@
     </row>
     <row r="960">
       <c r="A960" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B960" t="s">
         <v>2729</v>
@@ -22409,7 +22418,7 @@
     </row>
     <row r="961">
       <c r="A961" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B961" t="s">
         <v>2732</v>
@@ -22423,7 +22432,7 @@
     </row>
     <row r="962">
       <c r="A962" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B962" t="s">
         <v>2735</v>
@@ -22437,7 +22446,7 @@
     </row>
     <row r="963">
       <c r="A963" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B963" t="s">
         <v>2738</v>
@@ -22451,7 +22460,7 @@
     </row>
     <row r="964">
       <c r="A964" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B964" t="s">
         <v>2741</v>
@@ -22465,7 +22474,7 @@
     </row>
     <row r="965">
       <c r="A965" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B965" t="s">
         <v>2744</v>
@@ -22474,54 +22483,54 @@
         <v>2745</v>
       </c>
       <c r="D965" t="s">
-        <v>172</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B966" t="s">
-        <v>2746</v>
+        <v>2747</v>
       </c>
       <c r="C966" t="s">
-        <v>2747</v>
+        <v>2748</v>
       </c>
       <c r="D966" t="s">
-        <v>1548</v>
+        <v>172</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B967" t="s">
-        <v>2748</v>
+        <v>2749</v>
       </c>
       <c r="C967" t="s">
-        <v>2749</v>
+        <v>2750</v>
       </c>
       <c r="D967" t="s">
-        <v>1548</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B968" t="s">
-        <v>2750</v>
+        <v>2751</v>
       </c>
       <c r="C968" t="s">
-        <v>2751</v>
+        <v>2752</v>
       </c>
       <c r="D968" t="s">
-        <v>2752</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B969" t="s">
         <v>2753</v>
@@ -22535,7 +22544,7 @@
     </row>
     <row r="970">
       <c r="A970" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B970" t="s">
         <v>2756</v>
@@ -22549,7 +22558,7 @@
     </row>
     <row r="971">
       <c r="A971" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B971" t="s">
         <v>2759</v>
@@ -22563,7 +22572,7 @@
     </row>
     <row r="972">
       <c r="A972" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B972" t="s">
         <v>2762</v>
@@ -22577,7 +22586,7 @@
     </row>
     <row r="973">
       <c r="A973" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B973" t="s">
         <v>2765</v>
@@ -22591,7 +22600,7 @@
     </row>
     <row r="974">
       <c r="A974" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B974" t="s">
         <v>2768</v>
@@ -22605,7 +22614,7 @@
     </row>
     <row r="975">
       <c r="A975" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B975" t="s">
         <v>2771</v>
@@ -22619,7 +22628,7 @@
     </row>
     <row r="976">
       <c r="A976" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B976" t="s">
         <v>2774</v>
@@ -22633,7 +22642,7 @@
     </row>
     <row r="977">
       <c r="A977" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B977" t="s">
         <v>2777</v>
@@ -22647,7 +22656,7 @@
     </row>
     <row r="978">
       <c r="A978" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B978" t="s">
         <v>2780</v>
@@ -22661,7 +22670,7 @@
     </row>
     <row r="979">
       <c r="A979" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B979" t="s">
         <v>2783</v>
@@ -22675,7 +22684,7 @@
     </row>
     <row r="980">
       <c r="A980" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B980" t="s">
         <v>2786</v>
@@ -22689,7 +22698,7 @@
     </row>
     <row r="981">
       <c r="A981" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B981" t="s">
         <v>2789</v>
@@ -22703,7 +22712,7 @@
     </row>
     <row r="982">
       <c r="A982" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B982" t="s">
         <v>2792</v>
@@ -22717,91 +22726,91 @@
     </row>
     <row r="983">
       <c r="A983" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B983" t="s">
         <v>2795</v>
       </c>
       <c r="C983" t="s">
-        <v>2592</v>
+        <v>2796</v>
       </c>
       <c r="D983" t="s">
-        <v>2593</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B984" t="s">
-        <v>2796</v>
+        <v>2798</v>
       </c>
       <c r="C984" t="s">
-        <v>2797</v>
+        <v>2595</v>
       </c>
       <c r="D984" t="s">
-        <v>2798</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B985" t="s">
         <v>2799</v>
       </c>
       <c r="C985" t="s">
-        <v>2601</v>
+        <v>2800</v>
       </c>
       <c r="D985" t="s">
-        <v>2602</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B986" t="s">
-        <v>2800</v>
+        <v>2802</v>
       </c>
       <c r="C986" t="s">
-        <v>2801</v>
+        <v>2604</v>
       </c>
       <c r="D986" t="s">
-        <v>2802</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B987" t="s">
         <v>2803</v>
       </c>
       <c r="C987" t="s">
-        <v>2604</v>
+        <v>2804</v>
       </c>
       <c r="D987" t="s">
-        <v>2605</v>
+        <v>2805</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B988" t="s">
-        <v>2804</v>
+        <v>2806</v>
       </c>
       <c r="C988" t="s">
-        <v>2805</v>
+        <v>2607</v>
       </c>
       <c r="D988" t="s">
-        <v>2806</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="989">
       <c r="A989" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B989" t="s">
         <v>2807</v>
@@ -22815,7 +22824,7 @@
     </row>
     <row r="990">
       <c r="A990" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B990" t="s">
         <v>2810</v>
@@ -22829,7 +22838,7 @@
     </row>
     <row r="991">
       <c r="A991" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B991" t="s">
         <v>2813</v>
@@ -22843,7 +22852,7 @@
     </row>
     <row r="992">
       <c r="A992" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B992" t="s">
         <v>2816</v>
@@ -22857,7 +22866,7 @@
     </row>
     <row r="993">
       <c r="A993" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B993" t="s">
         <v>2819</v>
@@ -22871,35 +22880,35 @@
     </row>
     <row r="994">
       <c r="A994" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B994" t="s">
         <v>2822</v>
       </c>
       <c r="C994" t="s">
-        <v>2243</v>
+        <v>2823</v>
       </c>
       <c r="D994" t="s">
-        <v>483</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="995">
       <c r="A995" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B995" t="s">
-        <v>2823</v>
+        <v>2825</v>
       </c>
       <c r="C995" t="s">
-        <v>2824</v>
+        <v>2246</v>
       </c>
       <c r="D995" t="s">
-        <v>2825</v>
+        <v>483</v>
       </c>
     </row>
     <row r="996">
       <c r="A996" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B996" t="s">
         <v>2826</v>
@@ -22913,7 +22922,7 @@
     </row>
     <row r="997">
       <c r="A997" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B997" t="s">
         <v>2829</v>
@@ -22927,69 +22936,69 @@
     </row>
     <row r="998">
       <c r="A998" t="s">
-        <v>1942</v>
+        <v>1930</v>
       </c>
       <c r="B998" t="s">
         <v>2832</v>
       </c>
       <c r="C998" t="s">
-        <v>922</v>
+        <v>2833</v>
       </c>
       <c r="D998" t="s">
-        <v>923</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="999">
       <c r="A999" t="s">
-        <v>1942</v>
+        <v>1945</v>
       </c>
       <c r="B999" t="s">
-        <v>2833</v>
+        <v>2835</v>
       </c>
       <c r="C999" t="s">
-        <v>2834</v>
+        <v>925</v>
       </c>
       <c r="D999" t="s">
-        <v>2835</v>
+        <v>926</v>
       </c>
     </row>
     <row r="1000">
       <c r="A1000" t="s">
-        <v>1942</v>
+        <v>1945</v>
       </c>
       <c r="B1000" t="s">
         <v>2836</v>
       </c>
       <c r="C1000" t="s">
-        <v>1417</v>
+        <v>2837</v>
       </c>
       <c r="D1000" t="s">
-        <v>1418</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="1001">
       <c r="A1001" t="s">
-        <v>2837</v>
+        <v>1945</v>
       </c>
       <c r="B1001" t="s">
-        <v>2838</v>
+        <v>2839</v>
       </c>
       <c r="C1001" t="s">
-        <v>2837</v>
+        <v>1420</v>
       </c>
       <c r="D1001" t="s">
-        <v>2839</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="1002">
       <c r="A1002" t="s">
-        <v>2837</v>
+        <v>2840</v>
       </c>
       <c r="B1002" t="s">
+        <v>2841</v>
+      </c>
+      <c r="C1002" t="s">
         <v>2840</v>
-      </c>
-      <c r="C1002" t="s">
-        <v>2841</v>
       </c>
       <c r="D1002" t="s">
         <v>2842</v>
@@ -22997,7 +23006,7 @@
     </row>
     <row r="1003">
       <c r="A1003" t="s">
-        <v>2837</v>
+        <v>2840</v>
       </c>
       <c r="B1003" t="s">
         <v>2843</v>
@@ -23011,7 +23020,7 @@
     </row>
     <row r="1004">
       <c r="A1004" t="s">
-        <v>2837</v>
+        <v>2840</v>
       </c>
       <c r="B1004" t="s">
         <v>2846</v>
@@ -23025,7 +23034,7 @@
     </row>
     <row r="1005">
       <c r="A1005" t="s">
-        <v>1945</v>
+        <v>2840</v>
       </c>
       <c r="B1005" t="s">
         <v>2849</v>
@@ -23039,7 +23048,7 @@
     </row>
     <row r="1006">
       <c r="A1006" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1006" t="s">
         <v>2852</v>
@@ -23053,7 +23062,7 @@
     </row>
     <row r="1007">
       <c r="A1007" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1007" t="s">
         <v>2855</v>
@@ -23067,49 +23076,49 @@
     </row>
     <row r="1008">
       <c r="A1008" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1008" t="s">
         <v>2858</v>
       </c>
       <c r="C1008" t="s">
-        <v>310</v>
+        <v>2859</v>
       </c>
       <c r="D1008" t="s">
-        <v>311</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="1009">
       <c r="A1009" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1009" t="s">
-        <v>2859</v>
+        <v>2861</v>
       </c>
       <c r="C1009" t="s">
-        <v>2860</v>
+        <v>310</v>
       </c>
       <c r="D1009" t="s">
-        <v>2097</v>
+        <v>311</v>
       </c>
     </row>
     <row r="1010">
       <c r="A1010" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1010" t="s">
-        <v>2861</v>
+        <v>2862</v>
       </c>
       <c r="C1010" t="s">
-        <v>2862</v>
+        <v>2863</v>
       </c>
       <c r="D1010" t="s">
-        <v>2863</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="1011">
       <c r="A1011" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1011" t="s">
         <v>2864</v>
@@ -23123,7 +23132,7 @@
     </row>
     <row r="1012">
       <c r="A1012" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1012" t="s">
         <v>2867</v>
@@ -23137,7 +23146,7 @@
     </row>
     <row r="1013">
       <c r="A1013" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1013" t="s">
         <v>2870</v>
@@ -23151,7 +23160,7 @@
     </row>
     <row r="1014">
       <c r="A1014" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1014" t="s">
         <v>2873</v>
@@ -23165,7 +23174,7 @@
     </row>
     <row r="1015">
       <c r="A1015" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1015" t="s">
         <v>2876</v>
@@ -23179,7 +23188,7 @@
     </row>
     <row r="1016">
       <c r="A1016" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1016" t="s">
         <v>2879</v>
@@ -23193,7 +23202,7 @@
     </row>
     <row r="1017">
       <c r="A1017" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1017" t="s">
         <v>2882</v>
@@ -23207,7 +23216,7 @@
     </row>
     <row r="1018">
       <c r="A1018" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1018" t="s">
         <v>2885</v>
@@ -23221,7 +23230,7 @@
     </row>
     <row r="1019">
       <c r="A1019" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1019" t="s">
         <v>2888</v>
@@ -23235,7 +23244,7 @@
     </row>
     <row r="1020">
       <c r="A1020" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1020" t="s">
         <v>2891</v>
@@ -23249,7 +23258,7 @@
     </row>
     <row r="1021">
       <c r="A1021" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1021" t="s">
         <v>2894</v>
@@ -23263,35 +23272,35 @@
     </row>
     <row r="1022">
       <c r="A1022" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1022" t="s">
         <v>2897</v>
       </c>
       <c r="C1022" t="s">
-        <v>2871</v>
+        <v>2898</v>
       </c>
       <c r="D1022" t="s">
-        <v>2872</v>
+        <v>2899</v>
       </c>
     </row>
     <row r="1023">
       <c r="A1023" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1023" t="s">
-        <v>2898</v>
+        <v>2900</v>
       </c>
       <c r="C1023" t="s">
-        <v>2899</v>
+        <v>2874</v>
       </c>
       <c r="D1023" t="s">
-        <v>2900</v>
+        <v>2875</v>
       </c>
     </row>
     <row r="1024">
       <c r="A1024" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1024" t="s">
         <v>2901</v>
@@ -23305,7 +23314,7 @@
     </row>
     <row r="1025">
       <c r="A1025" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1025" t="s">
         <v>2904</v>
@@ -23319,7 +23328,7 @@
     </row>
     <row r="1026">
       <c r="A1026" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1026" t="s">
         <v>2907</v>
@@ -23333,7 +23342,7 @@
     </row>
     <row r="1027">
       <c r="A1027" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1027" t="s">
         <v>2910</v>
@@ -23347,7 +23356,7 @@
     </row>
     <row r="1028">
       <c r="A1028" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1028" t="s">
         <v>2913</v>
@@ -23361,7 +23370,7 @@
     </row>
     <row r="1029">
       <c r="A1029" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1029" t="s">
         <v>2916</v>
@@ -23375,7 +23384,7 @@
     </row>
     <row r="1030">
       <c r="A1030" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1030" t="s">
         <v>2919</v>
@@ -23389,35 +23398,35 @@
     </row>
     <row r="1031">
       <c r="A1031" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1031" t="s">
         <v>2922</v>
       </c>
       <c r="C1031" t="s">
-        <v>2862</v>
+        <v>2923</v>
       </c>
       <c r="D1031" t="s">
-        <v>2863</v>
+        <v>2924</v>
       </c>
     </row>
     <row r="1032">
       <c r="A1032" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1032" t="s">
-        <v>2923</v>
+        <v>2925</v>
       </c>
       <c r="C1032" t="s">
-        <v>2924</v>
+        <v>2865</v>
       </c>
       <c r="D1032" t="s">
-        <v>2925</v>
+        <v>2866</v>
       </c>
     </row>
     <row r="1033">
       <c r="A1033" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1033" t="s">
         <v>2926</v>
@@ -23431,7 +23440,7 @@
     </row>
     <row r="1034">
       <c r="A1034" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1034" t="s">
         <v>2929</v>
@@ -23445,7 +23454,7 @@
     </row>
     <row r="1035">
       <c r="A1035" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1035" t="s">
         <v>2932</v>
@@ -23459,7 +23468,7 @@
     </row>
     <row r="1036">
       <c r="A1036" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1036" t="s">
         <v>2935</v>
@@ -23473,7 +23482,7 @@
     </row>
     <row r="1037">
       <c r="A1037" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1037" t="s">
         <v>2938</v>
@@ -23487,7 +23496,7 @@
     </row>
     <row r="1038">
       <c r="A1038" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1038" t="s">
         <v>2941</v>
@@ -23501,7 +23510,7 @@
     </row>
     <row r="1039">
       <c r="A1039" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1039" t="s">
         <v>2944</v>
@@ -23515,7 +23524,7 @@
     </row>
     <row r="1040">
       <c r="A1040" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1040" t="s">
         <v>2947</v>
@@ -23529,35 +23538,35 @@
     </row>
     <row r="1041">
       <c r="A1041" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1041" t="s">
         <v>2950</v>
       </c>
       <c r="C1041" t="s">
-        <v>1335</v>
+        <v>2951</v>
       </c>
       <c r="D1041" t="s">
-        <v>1336</v>
+        <v>2952</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1042" t="s">
-        <v>2951</v>
+        <v>2953</v>
       </c>
       <c r="C1042" t="s">
-        <v>2952</v>
+        <v>1338</v>
       </c>
       <c r="D1042" t="s">
-        <v>2953</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="1043">
       <c r="A1043" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1043" t="s">
         <v>2954</v>
@@ -23571,7 +23580,7 @@
     </row>
     <row r="1044">
       <c r="A1044" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1044" t="s">
         <v>2957</v>
@@ -23585,7 +23594,7 @@
     </row>
     <row r="1045">
       <c r="A1045" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B1045" t="s">
         <v>2960</v>
@@ -23595,6 +23604,20 @@
       </c>
       <c r="D1045" t="s">
         <v>2962</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B1046" t="s">
+        <v>2963</v>
+      </c>
+      <c r="C1046" t="s">
+        <v>2964</v>
+      </c>
+      <c r="D1046" t="s">
+        <v>2965</v>
       </c>
     </row>
   </sheetData>

--- a/docs/amharic-review.xlsx
+++ b/docs/amharic-review.xlsx
@@ -8801,6 +8801,15 @@
   </si>
   <si>
     <t>users.active</t>
+  </si>
+  <si>
+    <t>users.manage</t>
+  </si>
+  <si>
+    <t>Manage access</t>
+  </si>
+  <si>
+    <t>መዳረሻ አስተዳድር</t>
   </si>
   <si>
     <t>users.roles</t>
@@ -23722,35 +23731,35 @@
         <v>2932</v>
       </c>
       <c r="C1034" t="s">
-        <v>1513</v>
+        <v>2933</v>
       </c>
       <c r="D1034" t="s">
-        <v>1514</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="1035">
       <c r="A1035" t="s">
-        <v>2933</v>
+        <v>2038</v>
       </c>
       <c r="B1035" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="C1035" t="s">
-        <v>2933</v>
+        <v>1513</v>
       </c>
       <c r="D1035" t="s">
-        <v>2935</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="1036">
       <c r="A1036" t="s">
-        <v>2933</v>
+        <v>2936</v>
       </c>
       <c r="B1036" t="s">
+        <v>2937</v>
+      </c>
+      <c r="C1036" t="s">
         <v>2936</v>
-      </c>
-      <c r="C1036" t="s">
-        <v>2937</v>
       </c>
       <c r="D1036" t="s">
         <v>2938</v>
@@ -23758,7 +23767,7 @@
     </row>
     <row r="1037">
       <c r="A1037" t="s">
-        <v>2933</v>
+        <v>2936</v>
       </c>
       <c r="B1037" t="s">
         <v>2939</v>
@@ -23772,7 +23781,7 @@
     </row>
     <row r="1038">
       <c r="A1038" t="s">
-        <v>2933</v>
+        <v>2936</v>
       </c>
       <c r="B1038" t="s">
         <v>2942</v>
@@ -23786,7 +23795,7 @@
     </row>
     <row r="1039">
       <c r="A1039" t="s">
-        <v>2041</v>
+        <v>2936</v>
       </c>
       <c r="B1039" t="s">
         <v>2945</v>
@@ -23834,10 +23843,10 @@
         <v>2954</v>
       </c>
       <c r="C1042" t="s">
-        <v>310</v>
+        <v>2955</v>
       </c>
       <c r="D1042" t="s">
-        <v>311</v>
+        <v>2956</v>
       </c>
     </row>
     <row r="1043">
@@ -23845,13 +23854,13 @@
         <v>2041</v>
       </c>
       <c r="B1043" t="s">
-        <v>2955</v>
+        <v>2957</v>
       </c>
       <c r="C1043" t="s">
-        <v>2956</v>
+        <v>310</v>
       </c>
       <c r="D1043" t="s">
-        <v>2193</v>
+        <v>311</v>
       </c>
     </row>
     <row r="1044">
@@ -23859,13 +23868,13 @@
         <v>2041</v>
       </c>
       <c r="B1044" t="s">
-        <v>2957</v>
+        <v>2958</v>
       </c>
       <c r="C1044" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="D1044" t="s">
-        <v>2959</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="1045">
@@ -23974,10 +23983,10 @@
         <v>2981</v>
       </c>
       <c r="C1052" t="s">
-        <v>993</v>
+        <v>2982</v>
       </c>
       <c r="D1052" t="s">
-        <v>2982</v>
+        <v>2983</v>
       </c>
     </row>
     <row r="1053">
@@ -23985,10 +23994,10 @@
         <v>2041</v>
       </c>
       <c r="B1053" t="s">
-        <v>2983</v>
+        <v>2984</v>
       </c>
       <c r="C1053" t="s">
-        <v>2984</v>
+        <v>993</v>
       </c>
       <c r="D1053" t="s">
         <v>2985</v>
@@ -24030,10 +24039,10 @@
         <v>2992</v>
       </c>
       <c r="C1056" t="s">
-        <v>2967</v>
+        <v>2993</v>
       </c>
       <c r="D1056" t="s">
-        <v>2968</v>
+        <v>2994</v>
       </c>
     </row>
     <row r="1057">
@@ -24041,13 +24050,13 @@
         <v>2041</v>
       </c>
       <c r="B1057" t="s">
-        <v>2993</v>
+        <v>2995</v>
       </c>
       <c r="C1057" t="s">
-        <v>2994</v>
+        <v>2970</v>
       </c>
       <c r="D1057" t="s">
-        <v>2995</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="1058">
@@ -24156,10 +24165,10 @@
         <v>3017</v>
       </c>
       <c r="C1065" t="s">
-        <v>2958</v>
+        <v>3018</v>
       </c>
       <c r="D1065" t="s">
-        <v>2959</v>
+        <v>3019</v>
       </c>
     </row>
     <row r="1066">
@@ -24167,13 +24176,13 @@
         <v>2041</v>
       </c>
       <c r="B1066" t="s">
-        <v>3018</v>
+        <v>3020</v>
       </c>
       <c r="C1066" t="s">
-        <v>3019</v>
+        <v>2961</v>
       </c>
       <c r="D1066" t="s">
-        <v>3020</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="1067">
@@ -24296,10 +24305,10 @@
         <v>3045</v>
       </c>
       <c r="C1075" t="s">
-        <v>1415</v>
+        <v>3046</v>
       </c>
       <c r="D1075" t="s">
-        <v>1416</v>
+        <v>3047</v>
       </c>
     </row>
     <row r="1076">
@@ -24307,13 +24316,13 @@
         <v>2041</v>
       </c>
       <c r="B1076" t="s">
-        <v>3046</v>
+        <v>3048</v>
       </c>
       <c r="C1076" t="s">
-        <v>3047</v>
+        <v>1415</v>
       </c>
       <c r="D1076" t="s">
-        <v>3048</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="1077">
@@ -24358,6 +24367,20 @@
         <v>3057</v>
       </c>
     </row>
+    <row r="1080">
+      <c r="A1080" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B1080" t="s">
+        <v>3058</v>
+      </c>
+      <c r="C1080" t="s">
+        <v>3059</v>
+      </c>
+      <c r="D1080" t="s">
+        <v>3060</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/docs/amharic-review.xlsx
+++ b/docs/amharic-review.xlsx
@@ -8242,10 +8242,10 @@
     <t>contract.draft</t>
   </si>
   <si>
-    <t>Draft template. Dire Mall's lawyer should check the wording against Proclamation No. 1320/2024 before it is signed.</t>
-  </si>
-  <si>
-    <t>ረቂቅ ቅጽ። ከመፈረሙ በፊት የድሬ ሞል ጠበቃ ጽሑፉን ከአዋጅ ቁጥር 1320/2024 ጋር ማመሳከር አለበት።</t>
+    <t>Draft template. A lawyer should check the wording against Proclamation No. 1320/2024 before it is signed.</t>
+  </si>
+  <si>
+    <t>ረቂቅ ቅጽ። ከመፈረሙ በፊት ጠበቃ ጽሑፉን ከአዋጅ ቁጥር 1320/2024 ጋር ማመሳከር አለበት።</t>
   </si>
   <si>
     <t>contract.title</t>
@@ -10036,10 +10036,10 @@
     <t>first.title</t>
   </si>
   <si>
-    <t>Set up Dire Mall</t>
-  </si>
-  <si>
-    <t>ድሬ ሞልን ያዘጋጁ</t>
+    <t>Set up {c}</t>
+  </si>
+  <si>
+    <t>{c}ን ያዘጋጁ</t>
   </si>
   <si>
     <t>pw.hide</t>
@@ -10324,6 +10324,15 @@
     <t>መተላለፊያው ተገናኝቷል። መልዕክቶች እንደ {s} ይላካሉ።</t>
   </si>
   <si>
+    <t>sms.gatewayTest</t>
+  </si>
+  <si>
+    <t>Gateway status and test message</t>
+  </si>
+  <si>
+    <t>የመተላለፊያ ሁኔታና የሙከራ መልዕክት</t>
+  </si>
+  <si>
     <t>sms.inAmharic</t>
   </si>
   <si>
@@ -10480,10 +10489,10 @@
     <t>sms.noGateway</t>
   </si>
   <si>
-    <t>No SMS gateway is connected yet. Reminders and receipts are prepared and listed here, but they stay queued and nothing is sent until the gateway details are added (see the README, SMS).</t>
-  </si>
-  <si>
-    <t>እስካሁን የSMS መተላለፊያ አልተገናኘም። ማስታወሻዎችና ደረሰኞች ተዘጋጅተው እዚህ ይዘረዘራሉ፣ ነገር ግን የመተላለፊያው ዝርዝር እስኪጨመር ድረስ በወረፋ ይቆያሉ፤ ምንም አይላክም።</t>
+    <t>No SMS gateway is connected yet. Reminders and receipts are prepared and listed here, but they stay queued and nothing is sent until the gateway details are added Add your gateway in the box above.</t>
+  </si>
+  <si>
+    <t>እስካሁን የSMS መተላለፊያ አልተገናኘም። ማስታወሻዎችና ደረሰኞች ተዘጋጅተው እዚህ ይዘረዘራሉ፣ ነገር ግን የመተላለፊያው ዝርዝር እስኪጨመር ድረስ በወረፋ ይቆያሉ፤ ምንም አይላክም። መተላለፊያዎን ከላይ ባለው ሳጥን ውስጥ ያክሉ።</t>
   </si>
   <si>
     <t>sms.optIssued</t>
@@ -28596,10 +28605,10 @@
         <v>3454</v>
       </c>
       <c r="C1221" t="s">
-        <v>1832</v>
+        <v>3455</v>
       </c>
       <c r="D1221" t="s">
-        <v>3455</v>
+        <v>3456</v>
       </c>
     </row>
     <row r="1222">
@@ -28607,10 +28616,10 @@
         <v>2771</v>
       </c>
       <c r="B1222" t="s">
-        <v>3456</v>
+        <v>3457</v>
       </c>
       <c r="C1222" t="s">
-        <v>3457</v>
+        <v>1832</v>
       </c>
       <c r="D1222" t="s">
         <v>3458</v>
@@ -28624,10 +28633,10 @@
         <v>3459</v>
       </c>
       <c r="C1223" t="s">
-        <v>1429</v>
+        <v>3460</v>
       </c>
       <c r="D1223" t="s">
-        <v>3251</v>
+        <v>3461</v>
       </c>
     </row>
     <row r="1224">
@@ -28635,13 +28644,13 @@
         <v>2771</v>
       </c>
       <c r="B1224" t="s">
-        <v>3460</v>
+        <v>3462</v>
       </c>
       <c r="C1224" t="s">
-        <v>3461</v>
+        <v>1429</v>
       </c>
       <c r="D1224" t="s">
-        <v>3462</v>
+        <v>3251</v>
       </c>
     </row>
     <row r="1225">
@@ -28890,10 +28899,10 @@
         <v>3514</v>
       </c>
       <c r="C1242" t="s">
-        <v>336</v>
+        <v>3515</v>
       </c>
       <c r="D1242" t="s">
-        <v>337</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="1243">
@@ -28901,13 +28910,13 @@
         <v>2771</v>
       </c>
       <c r="B1243" t="s">
-        <v>3515</v>
+        <v>3517</v>
       </c>
       <c r="C1243" t="s">
-        <v>3516</v>
+        <v>336</v>
       </c>
       <c r="D1243" t="s">
-        <v>3517</v>
+        <v>337</v>
       </c>
     </row>
     <row r="1244">
@@ -28918,10 +28927,10 @@
         <v>3518</v>
       </c>
       <c r="C1244" t="s">
-        <v>1767</v>
+        <v>3519</v>
       </c>
       <c r="D1244" t="s">
-        <v>1768</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="1245">
@@ -28929,13 +28938,13 @@
         <v>2771</v>
       </c>
       <c r="B1245" t="s">
-        <v>3519</v>
+        <v>3521</v>
       </c>
       <c r="C1245" t="s">
-        <v>3520</v>
+        <v>1767</v>
       </c>
       <c r="D1245" t="s">
-        <v>3521</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="1246">
@@ -28960,10 +28969,10 @@
         <v>3525</v>
       </c>
       <c r="C1247" t="s">
-        <v>566</v>
+        <v>3526</v>
       </c>
       <c r="D1247" t="s">
-        <v>567</v>
+        <v>3527</v>
       </c>
     </row>
     <row r="1248">
@@ -28971,13 +28980,13 @@
         <v>2771</v>
       </c>
       <c r="B1248" t="s">
-        <v>3526</v>
+        <v>3528</v>
       </c>
       <c r="C1248" t="s">
-        <v>3527</v>
+        <v>566</v>
       </c>
       <c r="D1248" t="s">
-        <v>3528</v>
+        <v>567</v>
       </c>
     </row>
     <row r="1249">
@@ -29002,10 +29011,10 @@
         <v>3532</v>
       </c>
       <c r="C1250" t="s">
-        <v>1089</v>
+        <v>3533</v>
       </c>
       <c r="D1250" t="s">
-        <v>1090</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="1251">
@@ -29013,13 +29022,13 @@
         <v>2771</v>
       </c>
       <c r="B1251" t="s">
-        <v>3533</v>
+        <v>3535</v>
       </c>
       <c r="C1251" t="s">
-        <v>3534</v>
+        <v>1089</v>
       </c>
       <c r="D1251" t="s">
-        <v>3535</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="1252">
@@ -29159,7 +29168,7 @@
         <v>3564</v>
       </c>
       <c r="D1261" t="s">
-        <v>1060</v>
+        <v>3565</v>
       </c>
     </row>
     <row r="1262">
@@ -29167,13 +29176,13 @@
         <v>2771</v>
       </c>
       <c r="B1262" t="s">
-        <v>3565</v>
+        <v>3566</v>
       </c>
       <c r="C1262" t="s">
-        <v>3566</v>
+        <v>3567</v>
       </c>
       <c r="D1262" t="s">
-        <v>3567</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="1263">
@@ -29285,7 +29294,7 @@
         <v>3590</v>
       </c>
       <c r="D1270" t="s">
-        <v>172</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="1271">
@@ -29293,13 +29302,13 @@
         <v>2771</v>
       </c>
       <c r="B1271" t="s">
-        <v>3591</v>
+        <v>3592</v>
       </c>
       <c r="C1271" t="s">
-        <v>3592</v>
+        <v>3593</v>
       </c>
       <c r="D1271" t="s">
-        <v>1851</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1272">
@@ -29307,10 +29316,10 @@
         <v>2771</v>
       </c>
       <c r="B1272" t="s">
-        <v>3593</v>
+        <v>3594</v>
       </c>
       <c r="C1272" t="s">
-        <v>3594</v>
+        <v>3595</v>
       </c>
       <c r="D1272" t="s">
         <v>1851</v>
@@ -29321,13 +29330,13 @@
         <v>2771</v>
       </c>
       <c r="B1273" t="s">
-        <v>3595</v>
+        <v>3596</v>
       </c>
       <c r="C1273" t="s">
-        <v>3596</v>
+        <v>3597</v>
       </c>
       <c r="D1273" t="s">
-        <v>3597</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="1274">
@@ -29534,10 +29543,10 @@
         <v>3640</v>
       </c>
       <c r="C1288" t="s">
-        <v>3440</v>
+        <v>3641</v>
       </c>
       <c r="D1288" t="s">
-        <v>3441</v>
+        <v>3642</v>
       </c>
     </row>
     <row r="1289">
@@ -29545,13 +29554,13 @@
         <v>2771</v>
       </c>
       <c r="B1289" t="s">
-        <v>3641</v>
+        <v>3643</v>
       </c>
       <c r="C1289" t="s">
-        <v>3642</v>
+        <v>3443</v>
       </c>
       <c r="D1289" t="s">
-        <v>3643</v>
+        <v>3444</v>
       </c>
     </row>
     <row r="1290">
@@ -29562,10 +29571,10 @@
         <v>3644</v>
       </c>
       <c r="C1290" t="s">
-        <v>3449</v>
+        <v>3645</v>
       </c>
       <c r="D1290" t="s">
-        <v>3450</v>
+        <v>3646</v>
       </c>
     </row>
     <row r="1291">
@@ -29573,13 +29582,13 @@
         <v>2771</v>
       </c>
       <c r="B1291" t="s">
-        <v>3645</v>
+        <v>3647</v>
       </c>
       <c r="C1291" t="s">
-        <v>3646</v>
+        <v>3452</v>
       </c>
       <c r="D1291" t="s">
-        <v>3647</v>
+        <v>3453</v>
       </c>
     </row>
     <row r="1292">
@@ -29590,10 +29599,10 @@
         <v>3648</v>
       </c>
       <c r="C1292" t="s">
-        <v>3452</v>
+        <v>3649</v>
       </c>
       <c r="D1292" t="s">
-        <v>3453</v>
+        <v>3650</v>
       </c>
     </row>
     <row r="1293">
@@ -29601,13 +29610,13 @@
         <v>2771</v>
       </c>
       <c r="B1293" t="s">
-        <v>3649</v>
+        <v>3651</v>
       </c>
       <c r="C1293" t="s">
-        <v>3650</v>
+        <v>3455</v>
       </c>
       <c r="D1293" t="s">
-        <v>3651</v>
+        <v>3456</v>
       </c>
     </row>
     <row r="1294">
@@ -29688,10 +29697,10 @@
         <v>3667</v>
       </c>
       <c r="C1299" t="s">
-        <v>3091</v>
+        <v>3668</v>
       </c>
       <c r="D1299" t="s">
-        <v>483</v>
+        <v>3669</v>
       </c>
     </row>
     <row r="1300">
@@ -29699,13 +29708,13 @@
         <v>2771</v>
       </c>
       <c r="B1300" t="s">
-        <v>3668</v>
+        <v>3670</v>
       </c>
       <c r="C1300" t="s">
-        <v>3669</v>
+        <v>3091</v>
       </c>
       <c r="D1300" t="s">
-        <v>3670</v>
+        <v>483</v>
       </c>
     </row>
     <row r="1301">
@@ -29738,16 +29747,16 @@
     </row>
     <row r="1303">
       <c r="A1303" t="s">
-        <v>2786</v>
+        <v>2771</v>
       </c>
       <c r="B1303" t="s">
         <v>3677</v>
       </c>
       <c r="C1303" t="s">
-        <v>1281</v>
+        <v>3678</v>
       </c>
       <c r="D1303" t="s">
-        <v>1282</v>
+        <v>3679</v>
       </c>
     </row>
     <row r="1304">
@@ -29755,13 +29764,13 @@
         <v>2786</v>
       </c>
       <c r="B1304" t="s">
-        <v>3678</v>
+        <v>3680</v>
       </c>
       <c r="C1304" t="s">
-        <v>3679</v>
+        <v>1281</v>
       </c>
       <c r="D1304" t="s">
-        <v>3680</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="1305">
@@ -29786,35 +29795,35 @@
         <v>3684</v>
       </c>
       <c r="C1306" t="s">
-        <v>2164</v>
+        <v>3685</v>
       </c>
       <c r="D1306" t="s">
-        <v>2165</v>
+        <v>3686</v>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="s">
-        <v>3685</v>
+        <v>2786</v>
       </c>
       <c r="B1307" t="s">
-        <v>3686</v>
+        <v>3687</v>
       </c>
       <c r="C1307" t="s">
-        <v>3685</v>
+        <v>2164</v>
       </c>
       <c r="D1307" t="s">
-        <v>3687</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="1308">
       <c r="A1308" t="s">
-        <v>3685</v>
+        <v>3688</v>
       </c>
       <c r="B1308" t="s">
+        <v>3689</v>
+      </c>
+      <c r="C1308" t="s">
         <v>3688</v>
-      </c>
-      <c r="C1308" t="s">
-        <v>3689</v>
       </c>
       <c r="D1308" t="s">
         <v>3690</v>
@@ -29822,7 +29831,7 @@
     </row>
     <row r="1309">
       <c r="A1309" t="s">
-        <v>3685</v>
+        <v>3688</v>
       </c>
       <c r="B1309" t="s">
         <v>3691</v>
@@ -29836,7 +29845,7 @@
     </row>
     <row r="1310">
       <c r="A1310" t="s">
-        <v>3685</v>
+        <v>3688</v>
       </c>
       <c r="B1310" t="s">
         <v>3694</v>
@@ -29850,7 +29859,7 @@
     </row>
     <row r="1311">
       <c r="A1311" t="s">
-        <v>2789</v>
+        <v>3688</v>
       </c>
       <c r="B1311" t="s">
         <v>3697</v>
@@ -29898,10 +29907,10 @@
         <v>3706</v>
       </c>
       <c r="C1314" t="s">
-        <v>310</v>
+        <v>3707</v>
       </c>
       <c r="D1314" t="s">
-        <v>311</v>
+        <v>3708</v>
       </c>
     </row>
     <row r="1315">
@@ -29909,13 +29918,13 @@
         <v>2789</v>
       </c>
       <c r="B1315" t="s">
-        <v>3707</v>
+        <v>3709</v>
       </c>
       <c r="C1315" t="s">
-        <v>3708</v>
+        <v>310</v>
       </c>
       <c r="D1315" t="s">
-        <v>2941</v>
+        <v>311</v>
       </c>
     </row>
     <row r="1316">
@@ -29923,13 +29932,13 @@
         <v>2789</v>
       </c>
       <c r="B1316" t="s">
-        <v>3709</v>
+        <v>3710</v>
       </c>
       <c r="C1316" t="s">
-        <v>3710</v>
+        <v>3711</v>
       </c>
       <c r="D1316" t="s">
-        <v>3711</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="1317">
@@ -30038,10 +30047,10 @@
         <v>3733</v>
       </c>
       <c r="C1324" t="s">
-        <v>1272</v>
+        <v>3734</v>
       </c>
       <c r="D1324" t="s">
-        <v>3734</v>
+        <v>3735</v>
       </c>
     </row>
     <row r="1325">
@@ -30049,10 +30058,10 @@
         <v>2789</v>
       </c>
       <c r="B1325" t="s">
-        <v>3735</v>
+        <v>3736</v>
       </c>
       <c r="C1325" t="s">
-        <v>3736</v>
+        <v>1272</v>
       </c>
       <c r="D1325" t="s">
         <v>3737</v>
@@ -30094,10 +30103,10 @@
         <v>3744</v>
       </c>
       <c r="C1328" t="s">
-        <v>3719</v>
+        <v>3745</v>
       </c>
       <c r="D1328" t="s">
-        <v>3720</v>
+        <v>3746</v>
       </c>
     </row>
     <row r="1329">
@@ -30105,13 +30114,13 @@
         <v>2789</v>
       </c>
       <c r="B1329" t="s">
-        <v>3745</v>
+        <v>3747</v>
       </c>
       <c r="C1329" t="s">
-        <v>3746</v>
+        <v>3722</v>
       </c>
       <c r="D1329" t="s">
-        <v>3747</v>
+        <v>3723</v>
       </c>
     </row>
     <row r="1330">
@@ -30220,10 +30229,10 @@
         <v>3769</v>
       </c>
       <c r="C1337" t="s">
-        <v>3710</v>
+        <v>3770</v>
       </c>
       <c r="D1337" t="s">
-        <v>3711</v>
+        <v>3771</v>
       </c>
     </row>
     <row r="1338">
@@ -30231,13 +30240,13 @@
         <v>2789</v>
       </c>
       <c r="B1338" t="s">
-        <v>3770</v>
+        <v>3772</v>
       </c>
       <c r="C1338" t="s">
-        <v>3771</v>
+        <v>3713</v>
       </c>
       <c r="D1338" t="s">
-        <v>3772</v>
+        <v>3714</v>
       </c>
     </row>
     <row r="1339">
@@ -30360,10 +30369,10 @@
         <v>3797</v>
       </c>
       <c r="C1347" t="s">
-        <v>1730</v>
+        <v>3798</v>
       </c>
       <c r="D1347" t="s">
-        <v>1845</v>
+        <v>3799</v>
       </c>
     </row>
     <row r="1348">
@@ -30371,13 +30380,13 @@
         <v>2789</v>
       </c>
       <c r="B1348" t="s">
-        <v>3798</v>
+        <v>3800</v>
       </c>
       <c r="C1348" t="s">
-        <v>3799</v>
+        <v>1730</v>
       </c>
       <c r="D1348" t="s">
-        <v>3800</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="1349">
@@ -30422,6 +30431,20 @@
         <v>3809</v>
       </c>
     </row>
+    <row r="1352">
+      <c r="A1352" t="s">
+        <v>2789</v>
+      </c>
+      <c r="B1352" t="s">
+        <v>3810</v>
+      </c>
+      <c r="C1352" t="s">
+        <v>3811</v>
+      </c>
+      <c r="D1352" t="s">
+        <v>3812</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>